--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_drugs_pharmaceutical.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="adx_julphar" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0891</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.1763468013468013</v>
+        <v>0.0778642936596218</v>
       </c>
       <c r="H2">
-        <v>-0.1763468013468013</v>
+        <v>0.0778642936596218</v>
       </c>
       <c r="I2">
-        <v>-0.242003367003367</v>
+        <v>0.01343715239154616</v>
       </c>
       <c r="J2">
-        <v>-0.242003367003367</v>
+        <v>0.01343715239154616</v>
       </c>
       <c r="K2">
-        <v>-24.8</v>
+        <v>-7.73</v>
       </c>
       <c r="L2">
-        <v>-0.1043771043771044</v>
+        <v>-0.01719688542825362</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>43.6</v>
+        <v>31.4</v>
       </c>
       <c r="V2">
-        <v>0.07534128218420598</v>
+        <v>0.08607456140350876</v>
       </c>
       <c r="W2">
-        <v>-0.08299866131191433</v>
+        <v>-0.028481945467944</v>
       </c>
       <c r="X2">
-        <v>0.068771250889591</v>
+        <v>0.1516052572206546</v>
       </c>
       <c r="Y2">
-        <v>-0.1517699122015053</v>
+        <v>-0.1800872026885986</v>
       </c>
       <c r="Z2">
-        <v>0.5407373691397359</v>
+        <v>1.0006678539626</v>
       </c>
       <c r="AA2">
-        <v>-0.1308602639963587</v>
+        <v>0.01344612644701692</v>
       </c>
       <c r="AB2">
-        <v>0.05374902536622503</v>
+        <v>0.1152187198377018</v>
       </c>
       <c r="AC2">
-        <v>-0.1846092893625837</v>
+        <v>-0.1017725933906849</v>
       </c>
       <c r="AD2">
-        <v>221.4</v>
+        <v>245</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>221.4</v>
+        <v>245</v>
       </c>
       <c r="AG2">
-        <v>177.8</v>
+        <v>213.6</v>
       </c>
       <c r="AH2">
-        <v>0.2767154105736783</v>
+        <v>0.4017710724827813</v>
       </c>
       <c r="AI2">
-        <v>0.447092084006462</v>
+        <v>0.4802979807880807</v>
       </c>
       <c r="AJ2">
-        <v>0.2350297422339722</v>
+        <v>0.3692946058091287</v>
       </c>
       <c r="AK2">
-        <v>0.3937112488928255</v>
+        <v>0.4462084813035304</v>
       </c>
       <c r="AL2">
-        <v>5.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AM2">
-        <v>5.554</v>
+        <v>7.945999999999999</v>
       </c>
       <c r="AN2">
-        <v>-6.099173553719009</v>
+        <v>7.18475073313783</v>
       </c>
       <c r="AO2">
-        <v>-9.599332220367279</v>
+        <v>0.6871444823663254</v>
       </c>
       <c r="AP2">
-        <v>-4.898071625344353</v>
+        <v>6.263929618768328</v>
       </c>
       <c r="AQ2">
-        <v>-10.35289881166727</v>
+        <v>0.7601308834633779</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0891</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.1763468013468013</v>
+        <v>0.0778642936596218</v>
       </c>
       <c r="H3">
-        <v>-0.1763468013468013</v>
+        <v>0.0778642936596218</v>
       </c>
       <c r="I3">
-        <v>-0.242003367003367</v>
+        <v>0.01343715239154616</v>
       </c>
       <c r="J3">
-        <v>-0.242003367003367</v>
+        <v>0.01343715239154616</v>
       </c>
       <c r="K3">
-        <v>-24.8</v>
+        <v>-7.73</v>
       </c>
       <c r="L3">
-        <v>-0.1043771043771044</v>
+        <v>-0.01719688542825362</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>43.6</v>
+        <v>31.4</v>
       </c>
       <c r="V3">
-        <v>0.07534128218420598</v>
+        <v>0.08607456140350876</v>
       </c>
       <c r="W3">
-        <v>-0.08299866131191433</v>
+        <v>-0.028481945467944</v>
       </c>
       <c r="X3">
-        <v>0.068771250889591</v>
+        <v>0.1516052572206546</v>
       </c>
       <c r="Y3">
-        <v>-0.1517699122015053</v>
+        <v>-0.1800872026885986</v>
       </c>
       <c r="Z3">
-        <v>0.5407373691397359</v>
+        <v>1.0006678539626</v>
       </c>
       <c r="AA3">
-        <v>-0.1308602639963587</v>
+        <v>0.01344612644701692</v>
       </c>
       <c r="AB3">
-        <v>0.05374902536622503</v>
+        <v>0.1152187198377018</v>
       </c>
       <c r="AC3">
-        <v>-0.1846092893625837</v>
+        <v>-0.1017725933906849</v>
       </c>
       <c r="AD3">
-        <v>221.4</v>
+        <v>245</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>221.4</v>
+        <v>245</v>
       </c>
       <c r="AG3">
-        <v>177.8</v>
+        <v>213.6</v>
       </c>
       <c r="AH3">
-        <v>0.2767154105736783</v>
+        <v>0.4017710724827813</v>
       </c>
       <c r="AI3">
-        <v>0.447092084006462</v>
+        <v>0.4802979807880807</v>
       </c>
       <c r="AJ3">
-        <v>0.2350297422339722</v>
+        <v>0.3692946058091287</v>
       </c>
       <c r="AK3">
-        <v>0.3937112488928255</v>
+        <v>0.4462084813035304</v>
       </c>
       <c r="AL3">
-        <v>5.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AM3">
-        <v>5.554</v>
+        <v>7.945999999999999</v>
       </c>
       <c r="AN3">
-        <v>-6.099173553719009</v>
+        <v>7.18475073313783</v>
       </c>
       <c r="AO3">
-        <v>-9.599332220367279</v>
+        <v>0.6871444823663254</v>
       </c>
       <c r="AP3">
-        <v>-4.898071625344353</v>
+        <v>6.263929618768328</v>
       </c>
       <c r="AQ3">
-        <v>-10.35289881166727</v>
+        <v>0.7601308834633779</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gulf Pharmaceutical Industries P.S.C. (ADX:JULPHAR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADX:JULPHAR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Drugs (Pharmaceutical)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.401771072482781</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>364.8</v>
+      </c>
+      <c r="H2">
+        <v>686.384907160825</v>
+      </c>
+      <c r="I2">
+        <v>578.4</v>
+      </c>
+      <c r="J2">
+        <v>654.9849071608249</v>
+      </c>
+      <c r="K2">
+        <v>245</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.115218719837702</v>
+      </c>
+      <c r="N2">
+        <v>0.106283368045416</v>
+      </c>
+      <c r="O2">
+        <v>0.0610399082568807</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.151605257220655</v>
+      </c>
+      <c r="T2">
+        <v>0.106283368045416</v>
+      </c>
+      <c r="U2">
+        <v>1.66717674919825</v>
+      </c>
+      <c r="V2">
+        <v>0.997353358654514</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>364.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.06766244627325971</v>
+      </c>
+      <c r="AC2">
+        <v>0.06103990825688074</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>34.1</v>
+      </c>
+      <c r="AH2">
+        <v>28.06</v>
+      </c>
+      <c r="AI2">
+        <v>44.76000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>245</v>
+      </c>
+      <c r="AK2">
+        <v>245</v>
+      </c>
+      <c r="AL2">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="AM2">
+        <v>245</v>
+      </c>
+      <c r="AN2">
+        <v>31.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1062833680454162</v>
+      </c>
+      <c r="C2">
+        <v>686.3849071608254</v>
+      </c>
+      <c r="D2">
+        <v>654.9849071608254</v>
+      </c>
+      <c r="E2">
+        <v>-245</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>31.4</v>
+      </c>
+      <c r="H2">
+        <v>364.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>34.1</v>
+      </c>
+      <c r="K2">
+        <v>28.06</v>
+      </c>
+      <c r="L2">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>34.1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1062833680454162</v>
+      </c>
+      <c r="T2">
+        <v>0.9973533586545144</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1063523680454162</v>
+      </c>
+      <c r="C3">
+        <v>679.617886075381</v>
+      </c>
+      <c r="D3">
+        <v>654.3158860753809</v>
+      </c>
+      <c r="E3">
+        <v>-238.902</v>
+      </c>
+      <c r="F3">
+        <v>6.098</v>
+      </c>
+      <c r="G3">
+        <v>31.4</v>
+      </c>
+      <c r="H3">
+        <v>364.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>34.1</v>
+      </c>
+      <c r="K3">
+        <v>28.06</v>
+      </c>
+      <c r="L3">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M3">
+        <v>0.2786786</v>
+      </c>
+      <c r="N3">
+        <v>5.761321399999999</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>5.761321399999999</v>
+      </c>
+      <c r="Q3">
+        <v>33.8213214</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1069650182276931</v>
+      </c>
+      <c r="T3">
+        <v>1.00742763500456</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>21.6737130156388</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1064533680454162</v>
+      </c>
+      <c r="C4">
+        <v>672.5430551148107</v>
+      </c>
+      <c r="D4">
+        <v>653.3390551148108</v>
+      </c>
+      <c r="E4">
+        <v>-232.804</v>
+      </c>
+      <c r="F4">
+        <v>12.196</v>
+      </c>
+      <c r="G4">
+        <v>31.4</v>
+      </c>
+      <c r="H4">
+        <v>364.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>34.1</v>
+      </c>
+      <c r="K4">
+        <v>28.06</v>
+      </c>
+      <c r="L4">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.5768708</v>
+      </c>
+      <c r="N4">
+        <v>5.463129199999999</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>5.463129199999999</v>
+      </c>
+      <c r="Q4">
+        <v>33.5231292</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1076605796381798</v>
+      </c>
+      <c r="T4">
+        <v>1.017707508831137</v>
+      </c>
+      <c r="U4">
+        <v>0.0473</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0473</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>10.47028208049359</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1067093680454162</v>
+      </c>
+      <c r="C5">
+        <v>663.9821431054171</v>
+      </c>
+      <c r="D5">
+        <v>650.8761431054171</v>
+      </c>
+      <c r="E5">
+        <v>-226.706</v>
+      </c>
+      <c r="F5">
+        <v>18.294</v>
+      </c>
+      <c r="G5">
+        <v>31.4</v>
+      </c>
+      <c r="H5">
+        <v>364.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>34.1</v>
+      </c>
+      <c r="K5">
+        <v>28.06</v>
+      </c>
+      <c r="L5">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M5">
+        <v>0.9695819999999999</v>
+      </c>
+      <c r="N5">
+        <v>5.070417999999999</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>5.070417999999999</v>
+      </c>
+      <c r="Q5">
+        <v>33.130418</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1083704825210476</v>
+      </c>
+      <c r="T5">
+        <v>1.028199338819087</v>
+      </c>
+      <c r="U5">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>6.229488583740209</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1069313680454162</v>
+      </c>
+      <c r="C6">
+        <v>655.7633211123363</v>
+      </c>
+      <c r="D6">
+        <v>648.7553211123363</v>
+      </c>
+      <c r="E6">
+        <v>-220.608</v>
+      </c>
+      <c r="F6">
+        <v>24.392</v>
+      </c>
+      <c r="G6">
+        <v>31.4</v>
+      </c>
+      <c r="H6">
+        <v>364.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>34.1</v>
+      </c>
+      <c r="K6">
+        <v>28.06</v>
+      </c>
+      <c r="L6">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M6">
+        <v>1.34156</v>
+      </c>
+      <c r="N6">
+        <v>4.698439999999999</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>4.698439999999999</v>
+      </c>
+      <c r="Q6">
+        <v>32.75844</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1090951750473085</v>
+      </c>
+      <c r="T6">
+        <v>1.038909748598452</v>
+      </c>
+      <c r="U6">
+        <v>0.055</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.055</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>4.502221294612241</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1089133680454162</v>
+      </c>
+      <c r="C7">
+        <v>631.3259789541938</v>
+      </c>
+      <c r="D7">
+        <v>630.4159789541939</v>
+      </c>
+      <c r="E7">
+        <v>-214.51</v>
+      </c>
+      <c r="F7">
+        <v>30.49</v>
+      </c>
+      <c r="G7">
+        <v>31.4</v>
+      </c>
+      <c r="H7">
+        <v>364.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>34.1</v>
+      </c>
+      <c r="K7">
+        <v>28.06</v>
+      </c>
+      <c r="L7">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M7">
+        <v>2.786786</v>
+      </c>
+      <c r="N7">
+        <v>3.253213999999999</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>3.253213999999999</v>
+      </c>
+      <c r="Q7">
+        <v>31.313214</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1098351242583328</v>
+      </c>
+      <c r="T7">
+        <v>1.049845640688962</v>
+      </c>
+      <c r="U7">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>2.16737130156388</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1157513680454162</v>
+      </c>
+      <c r="C8">
+        <v>569.2083840648012</v>
+      </c>
+      <c r="D8">
+        <v>574.3963840648012</v>
+      </c>
+      <c r="E8">
+        <v>-208.412</v>
+      </c>
+      <c r="F8">
+        <v>36.58799999999999</v>
+      </c>
+      <c r="G8">
+        <v>31.4</v>
+      </c>
+      <c r="H8">
+        <v>364.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>34.1</v>
+      </c>
+      <c r="K8">
+        <v>28.06</v>
+      </c>
+      <c r="L8">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M8">
+        <v>7.193200799999999</v>
+      </c>
+      <c r="N8">
+        <v>-1.1532008</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-1.1532008</v>
+      </c>
+      <c r="Q8">
+        <v>26.9067992</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1105908170695917</v>
+      </c>
+      <c r="T8">
+        <v>1.06101421133459</v>
+      </c>
+      <c r="U8">
+        <v>0.1966</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.1966</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.8396818284288685</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1185333680454162</v>
+      </c>
+      <c r="C9">
+        <v>543.0689537371862</v>
+      </c>
+      <c r="D9">
+        <v>554.3549537371863</v>
+      </c>
+      <c r="E9">
+        <v>-202.314</v>
+      </c>
+      <c r="F9">
+        <v>42.686</v>
+      </c>
+      <c r="G9">
+        <v>31.4</v>
+      </c>
+      <c r="H9">
+        <v>364.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>34.1</v>
+      </c>
+      <c r="K9">
+        <v>28.06</v>
+      </c>
+      <c r="L9">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M9">
+        <v>9.1262668</v>
+      </c>
+      <c r="N9">
+        <v>-3.086266800000001</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-3.086266800000001</v>
+      </c>
+      <c r="Q9">
+        <v>24.9737332</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1113627613391572</v>
+      </c>
+      <c r="T9">
+        <v>1.072422966295177</v>
+      </c>
+      <c r="U9">
+        <v>0.2138</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.2138</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.6618259286480644</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1202833680454162</v>
+      </c>
+      <c r="C10">
+        <v>525.065196865436</v>
+      </c>
+      <c r="D10">
+        <v>542.449196865436</v>
+      </c>
+      <c r="E10">
+        <v>-196.216</v>
+      </c>
+      <c r="F10">
+        <v>48.784</v>
+      </c>
+      <c r="G10">
+        <v>31.4</v>
+      </c>
+      <c r="H10">
+        <v>364.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>34.1</v>
+      </c>
+      <c r="K10">
+        <v>28.06</v>
+      </c>
+      <c r="L10">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M10">
+        <v>10.4300192</v>
+      </c>
+      <c r="N10">
+        <v>-4.390019199999999</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-4.390019199999999</v>
+      </c>
+      <c r="Q10">
+        <v>23.6699808</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1121514870058872</v>
+      </c>
+      <c r="T10">
+        <v>1.08407973766795</v>
+      </c>
+      <c r="U10">
+        <v>0.2138</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.2138</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.5790976875670564</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1220333680454162</v>
+      </c>
+      <c r="C11">
+        <v>507.5620823445801</v>
+      </c>
+      <c r="D11">
+        <v>531.0440823445801</v>
+      </c>
+      <c r="E11">
+        <v>-190.118</v>
+      </c>
+      <c r="F11">
+        <v>54.88199999999999</v>
+      </c>
+      <c r="G11">
+        <v>31.4</v>
+      </c>
+      <c r="H11">
+        <v>364.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>34.1</v>
+      </c>
+      <c r="K11">
+        <v>28.06</v>
+      </c>
+      <c r="L11">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M11">
+        <v>11.7337716</v>
+      </c>
+      <c r="N11">
+        <v>-5.693771599999998</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-5.693771599999998</v>
+      </c>
+      <c r="Q11">
+        <v>22.3662284</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1129575473026552</v>
+      </c>
+      <c r="T11">
+        <v>1.095992701818148</v>
+      </c>
+      <c r="U11">
+        <v>0.2138</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.2138</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.5147535000596057</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1262833680454162</v>
+      </c>
+      <c r="C12">
+        <v>475.665608870253</v>
+      </c>
+      <c r="D12">
+        <v>505.245608870253</v>
+      </c>
+      <c r="E12">
+        <v>-184.02</v>
+      </c>
+      <c r="F12">
+        <v>60.98</v>
+      </c>
+      <c r="G12">
+        <v>31.4</v>
+      </c>
+      <c r="H12">
+        <v>364.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>34.1</v>
+      </c>
+      <c r="K12">
+        <v>28.06</v>
+      </c>
+      <c r="L12">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M12">
+        <v>14.562024</v>
+      </c>
+      <c r="N12">
+        <v>-8.522024</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-8.522024</v>
+      </c>
+      <c r="Q12">
+        <v>19.537976</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1137815200504625</v>
+      </c>
+      <c r="T12">
+        <v>1.108170398505016</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.2388</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.4147775062038079</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1282833680454162</v>
+      </c>
+      <c r="C13">
+        <v>458.2751056954994</v>
+      </c>
+      <c r="D13">
+        <v>493.9531056954994</v>
+      </c>
+      <c r="E13">
+        <v>-177.922</v>
+      </c>
+      <c r="F13">
+        <v>67.07799999999999</v>
+      </c>
+      <c r="G13">
+        <v>31.4</v>
+      </c>
+      <c r="H13">
+        <v>364.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>34.1</v>
+      </c>
+      <c r="K13">
+        <v>28.06</v>
+      </c>
+      <c r="L13">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M13">
+        <v>16.0182264</v>
+      </c>
+      <c r="N13">
+        <v>-9.9782264</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-9.9782264</v>
+      </c>
+      <c r="Q13">
+        <v>18.0817736</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1146240090397935</v>
+      </c>
+      <c r="T13">
+        <v>1.120621751297207</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.2388</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.3770704601852799</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1302833680454162</v>
+      </c>
+      <c r="C14">
+        <v>441.3783536108522</v>
+      </c>
+      <c r="D14">
+        <v>483.1543536108522</v>
+      </c>
+      <c r="E14">
+        <v>-171.824</v>
+      </c>
+      <c r="F14">
+        <v>73.17599999999999</v>
+      </c>
+      <c r="G14">
+        <v>31.4</v>
+      </c>
+      <c r="H14">
+        <v>364.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>34.1</v>
+      </c>
+      <c r="K14">
+        <v>28.06</v>
+      </c>
+      <c r="L14">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M14">
+        <v>17.4744288</v>
+      </c>
+      <c r="N14">
+        <v>-11.4344288</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-11.4344288</v>
+      </c>
+      <c r="Q14">
+        <v>16.6255712</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1154856455061548</v>
+      </c>
+      <c r="T14">
+        <v>1.13335608938013</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.2388</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.3456479218365066</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1322833680454162</v>
+      </c>
+      <c r="C15">
+        <v>424.9436624172674</v>
+      </c>
+      <c r="D15">
+        <v>472.8176624172674</v>
+      </c>
+      <c r="E15">
+        <v>-165.726</v>
+      </c>
+      <c r="F15">
+        <v>79.274</v>
+      </c>
+      <c r="G15">
+        <v>31.4</v>
+      </c>
+      <c r="H15">
+        <v>364.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>34.1</v>
+      </c>
+      <c r="K15">
+        <v>28.06</v>
+      </c>
+      <c r="L15">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M15">
+        <v>18.9306312</v>
+      </c>
+      <c r="N15">
+        <v>-12.8906312</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-12.8906312</v>
+      </c>
+      <c r="Q15">
+        <v>15.1693688</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1163670897073749</v>
+      </c>
+      <c r="T15">
+        <v>1.146383170867258</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.2388</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.3190596201567752</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1342833680454162</v>
+      </c>
+      <c r="C16">
+        <v>408.9419970544708</v>
+      </c>
+      <c r="D16">
+        <v>462.9139970544709</v>
+      </c>
+      <c r="E16">
+        <v>-159.628</v>
+      </c>
+      <c r="F16">
+        <v>85.372</v>
+      </c>
+      <c r="G16">
+        <v>31.4</v>
+      </c>
+      <c r="H16">
+        <v>364.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>34.1</v>
+      </c>
+      <c r="K16">
+        <v>28.06</v>
+      </c>
+      <c r="L16">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M16">
+        <v>20.3868336</v>
+      </c>
+      <c r="N16">
+        <v>-14.3468336</v>
+      </c>
+      <c r="O16">
+        <v>-0</v>
+      </c>
+      <c r="P16">
+        <v>-14.3468336</v>
+      </c>
+      <c r="Q16">
+        <v>13.7131664</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1172690326109491</v>
+      </c>
+      <c r="T16">
+        <v>1.159713207737807</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.2388</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.2962696472884342</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1362833680454162</v>
+      </c>
+      <c r="C17">
+        <v>393.3467052325715</v>
+      </c>
+      <c r="D17">
+        <v>453.4167052325715</v>
+      </c>
+      <c r="E17">
+        <v>-153.53</v>
+      </c>
+      <c r="F17">
+        <v>91.46999999999998</v>
+      </c>
+      <c r="G17">
+        <v>31.4</v>
+      </c>
+      <c r="H17">
+        <v>364.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>34.1</v>
+      </c>
+      <c r="K17">
+        <v>28.06</v>
+      </c>
+      <c r="L17">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M17">
+        <v>21.843036</v>
+      </c>
+      <c r="N17">
+        <v>-15.803036</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-15.803036</v>
+      </c>
+      <c r="Q17">
+        <v>12.256964</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1181921977004897</v>
+      </c>
+      <c r="T17">
+        <v>1.173356892534723</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.2388</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.2765183374692053</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1382833680454162</v>
+      </c>
+      <c r="C18">
+        <v>378.1332779176141</v>
+      </c>
+      <c r="D18">
+        <v>444.3012779176141</v>
+      </c>
+      <c r="E18">
+        <v>-147.432</v>
+      </c>
+      <c r="F18">
+        <v>97.568</v>
+      </c>
+      <c r="G18">
+        <v>31.4</v>
+      </c>
+      <c r="H18">
+        <v>364.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>34.1</v>
+      </c>
+      <c r="K18">
+        <v>28.06</v>
+      </c>
+      <c r="L18">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M18">
+        <v>23.2992384</v>
+      </c>
+      <c r="N18">
+        <v>-17.2592384</v>
+      </c>
+      <c r="O18">
+        <v>-0</v>
+      </c>
+      <c r="P18">
+        <v>-17.2592384</v>
+      </c>
+      <c r="Q18">
+        <v>10.8007616</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1191373429112098</v>
+      </c>
+      <c r="T18">
+        <v>1.18732542696966</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.2388</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.2592359413773799</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1402833680454162</v>
+      </c>
+      <c r="C19">
+        <v>363.2791381387534</v>
+      </c>
+      <c r="D19">
+        <v>435.5451381387534</v>
+      </c>
+      <c r="E19">
+        <v>-141.334</v>
+      </c>
+      <c r="F19">
+        <v>103.666</v>
+      </c>
+      <c r="G19">
+        <v>31.4</v>
+      </c>
+      <c r="H19">
+        <v>364.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>34.1</v>
+      </c>
+      <c r="K19">
+        <v>28.06</v>
+      </c>
+      <c r="L19">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M19">
+        <v>24.7554408</v>
+      </c>
+      <c r="N19">
+        <v>-18.7154408</v>
+      </c>
+      <c r="O19">
+        <v>-0</v>
+      </c>
+      <c r="P19">
+        <v>-18.7154408</v>
+      </c>
+      <c r="Q19">
+        <v>9.344559200000003</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1201052627053207</v>
+      </c>
+      <c r="T19">
+        <v>1.2016305525958</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.2388</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.2439867683551811</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1422833680454162</v>
+      </c>
+      <c r="C20">
+        <v>348.763454285487</v>
+      </c>
+      <c r="D20">
+        <v>427.127454285487</v>
+      </c>
+      <c r="E20">
+        <v>-135.236</v>
+      </c>
+      <c r="F20">
+        <v>109.764</v>
+      </c>
+      <c r="G20">
+        <v>31.4</v>
+      </c>
+      <c r="H20">
+        <v>364.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>34.1</v>
+      </c>
+      <c r="K20">
+        <v>28.06</v>
+      </c>
+      <c r="L20">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M20">
+        <v>26.2116432</v>
+      </c>
+      <c r="N20">
+        <v>-20.1716432</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-20.1716432</v>
+      </c>
+      <c r="Q20">
+        <v>7.888356800000004</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.121096790299288</v>
+      </c>
+      <c r="T20">
+        <v>1.216284583725018</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.2388</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.2304319478910044</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1442833680454162</v>
+      </c>
+      <c r="C21">
+        <v>334.5669746445719</v>
+      </c>
+      <c r="D21">
+        <v>419.0289746445719</v>
+      </c>
+      <c r="E21">
+        <v>-129.138</v>
+      </c>
+      <c r="F21">
+        <v>115.862</v>
+      </c>
+      <c r="G21">
+        <v>31.4</v>
+      </c>
+      <c r="H21">
+        <v>364.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>34.1</v>
+      </c>
+      <c r="K21">
+        <v>28.06</v>
+      </c>
+      <c r="L21">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M21">
+        <v>27.6678456</v>
+      </c>
+      <c r="N21">
+        <v>-21.6278456</v>
+      </c>
+      <c r="O21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-21.6278456</v>
+      </c>
+      <c r="Q21">
+        <v>6.432154400000002</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1221128000560694</v>
+      </c>
+      <c r="T21">
+        <v>1.231300442783351</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.2388</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.2183039506335831</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1462833680454162</v>
+      </c>
+      <c r="C22">
+        <v>320.6718804100943</v>
+      </c>
+      <c r="D22">
+        <v>411.2318804100943</v>
+      </c>
+      <c r="E22">
+        <v>-123.04</v>
+      </c>
+      <c r="F22">
+        <v>121.96</v>
+      </c>
+      <c r="G22">
+        <v>31.4</v>
+      </c>
+      <c r="H22">
+        <v>364.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>34.1</v>
+      </c>
+      <c r="K22">
+        <v>28.06</v>
+      </c>
+      <c r="L22">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M22">
+        <v>29.124048</v>
+      </c>
+      <c r="N22">
+        <v>-23.084048</v>
+      </c>
+      <c r="O22">
+        <v>-0</v>
+      </c>
+      <c r="P22">
+        <v>-23.084048</v>
+      </c>
+      <c r="Q22">
+        <v>4.975952000000003</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1231542100567702</v>
+      </c>
+      <c r="T22">
+        <v>1.246691698318143</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.2388</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.207388753101904</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1482833680454162</v>
+      </c>
+      <c r="C23">
+        <v>307.0616548044753</v>
+      </c>
+      <c r="D23">
+        <v>403.7196548044753</v>
+      </c>
+      <c r="E23">
+        <v>-116.942</v>
+      </c>
+      <c r="F23">
+        <v>128.058</v>
+      </c>
+      <c r="G23">
+        <v>31.4</v>
+      </c>
+      <c r="H23">
+        <v>364.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>34.1</v>
+      </c>
+      <c r="K23">
+        <v>28.06</v>
+      </c>
+      <c r="L23">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M23">
+        <v>30.5802504</v>
+      </c>
+      <c r="N23">
+        <v>-24.5402504</v>
+      </c>
+      <c r="O23">
+        <v>-0</v>
+      </c>
+      <c r="P23">
+        <v>-24.5402504</v>
+      </c>
+      <c r="Q23">
+        <v>3.519749600000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1242219848676154</v>
+      </c>
+      <c r="T23">
+        <v>1.26247260589179</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.2388</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.1975130981922895</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1502833680454162</v>
+      </c>
+      <c r="C24">
+        <v>293.7209662872068</v>
+      </c>
+      <c r="D24">
+        <v>396.4769662872068</v>
+      </c>
+      <c r="E24">
+        <v>-110.844</v>
+      </c>
+      <c r="F24">
+        <v>134.156</v>
+      </c>
+      <c r="G24">
+        <v>31.4</v>
+      </c>
+      <c r="H24">
+        <v>364.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>34.1</v>
+      </c>
+      <c r="K24">
+        <v>28.06</v>
+      </c>
+      <c r="L24">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M24">
+        <v>32.0364528</v>
+      </c>
+      <c r="N24">
+        <v>-25.9964528</v>
+      </c>
+      <c r="O24">
+        <v>-0</v>
+      </c>
+      <c r="P24">
+        <v>-25.9964528</v>
+      </c>
+      <c r="Q24">
+        <v>2.063547200000002</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1253171385197643</v>
+      </c>
+      <c r="T24">
+        <v>1.278658152121172</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.2388</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.1885352300926399</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1522833680454162</v>
+      </c>
+      <c r="C25">
+        <v>280.6355641133739</v>
+      </c>
+      <c r="D25">
+        <v>389.4895641133739</v>
+      </c>
+      <c r="E25">
+        <v>-104.746</v>
+      </c>
+      <c r="F25">
+        <v>140.254</v>
+      </c>
+      <c r="G25">
+        <v>31.4</v>
+      </c>
+      <c r="H25">
+        <v>364.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>34.1</v>
+      </c>
+      <c r="K25">
+        <v>28.06</v>
+      </c>
+      <c r="L25">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M25">
+        <v>33.4926552</v>
+      </c>
+      <c r="N25">
+        <v>-27.4526552</v>
+      </c>
+      <c r="O25">
+        <v>-0</v>
+      </c>
+      <c r="P25">
+        <v>-27.4526552</v>
+      </c>
+      <c r="Q25">
+        <v>0.6073447999999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1264407377213198</v>
+      </c>
+      <c r="T25">
+        <v>1.29526410214872</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.2388</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.1803380461755686</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1542833680454162</v>
+      </c>
+      <c r="C26">
+        <v>267.7921847448021</v>
+      </c>
+      <c r="D26">
+        <v>382.7441847448021</v>
+      </c>
+      <c r="E26">
+        <v>-98.64800000000002</v>
+      </c>
+      <c r="F26">
+        <v>146.352</v>
+      </c>
+      <c r="G26">
+        <v>31.4</v>
+      </c>
+      <c r="H26">
+        <v>364.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>34.1</v>
+      </c>
+      <c r="K26">
+        <v>28.06</v>
+      </c>
+      <c r="L26">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M26">
+        <v>34.9488576</v>
+      </c>
+      <c r="N26">
+        <v>-28.9088576</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-28.9088576</v>
+      </c>
+      <c r="Q26">
+        <v>-0.8488575999999952</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.127593905322916</v>
+      </c>
+      <c r="T26">
+        <v>1.312307050861203</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.2388</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.1728239609182532</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1562833680454162</v>
+      </c>
+      <c r="C27">
+        <v>255.1784678205674</v>
+      </c>
+      <c r="D27">
+        <v>376.2284678205675</v>
+      </c>
+      <c r="E27">
+        <v>-92.55000000000001</v>
+      </c>
+      <c r="F27">
+        <v>152.45</v>
+      </c>
+      <c r="G27">
+        <v>31.4</v>
+      </c>
+      <c r="H27">
+        <v>364.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>34.1</v>
+      </c>
+      <c r="K27">
+        <v>28.06</v>
+      </c>
+      <c r="L27">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M27">
+        <v>36.40506</v>
+      </c>
+      <c r="N27">
+        <v>-30.36506</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-30.36506</v>
+      </c>
+      <c r="Q27">
+        <v>-2.305059999999997</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1287778240605549</v>
+      </c>
+      <c r="T27">
+        <v>1.329804478206019</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.2388</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.1659110024815231</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1582833680454162</v>
+      </c>
+      <c r="C28">
+        <v>242.7828805667905</v>
+      </c>
+      <c r="D28">
+        <v>369.9308805667906</v>
+      </c>
+      <c r="E28">
+        <v>-86.452</v>
+      </c>
+      <c r="F28">
+        <v>158.548</v>
+      </c>
+      <c r="G28">
+        <v>31.4</v>
+      </c>
+      <c r="H28">
+        <v>364.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>34.1</v>
+      </c>
+      <c r="K28">
+        <v>28.06</v>
+      </c>
+      <c r="L28">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M28">
+        <v>37.8612624</v>
+      </c>
+      <c r="N28">
+        <v>-31.8212624</v>
+      </c>
+      <c r="O28">
+        <v>-0</v>
+      </c>
+      <c r="P28">
+        <v>-31.8212624</v>
+      </c>
+      <c r="Q28">
+        <v>-3.7612624</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1299937406019138</v>
+      </c>
+      <c r="T28">
+        <v>1.347774808992587</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.2388</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.1595298100783876</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1602833680454162</v>
+      </c>
+      <c r="C29">
+        <v>230.594649673151</v>
+      </c>
+      <c r="D29">
+        <v>363.840649673151</v>
+      </c>
+      <c r="E29">
+        <v>-80.35400000000001</v>
+      </c>
+      <c r="F29">
+        <v>164.646</v>
+      </c>
+      <c r="G29">
+        <v>31.4</v>
+      </c>
+      <c r="H29">
+        <v>364.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>34.1</v>
+      </c>
+      <c r="K29">
+        <v>28.06</v>
+      </c>
+      <c r="L29">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M29">
+        <v>39.3174648</v>
+      </c>
+      <c r="N29">
+        <v>-33.2774648</v>
+      </c>
+      <c r="O29">
+        <v>-0</v>
+      </c>
+      <c r="P29">
+        <v>-33.2774648</v>
+      </c>
+      <c r="Q29">
+        <v>-5.217464799999995</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1312429699252277</v>
+      </c>
+      <c r="T29">
+        <v>1.366237477608924</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.2388</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.153621298594003</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1622833680454162</v>
+      </c>
+      <c r="C30">
+        <v>218.6036997895791</v>
+      </c>
+      <c r="D30">
+        <v>357.9476997895791</v>
+      </c>
+      <c r="E30">
+        <v>-74.256</v>
+      </c>
+      <c r="F30">
+        <v>170.744</v>
+      </c>
+      <c r="G30">
+        <v>31.4</v>
+      </c>
+      <c r="H30">
+        <v>364.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>34.1</v>
+      </c>
+      <c r="K30">
+        <v>28.06</v>
+      </c>
+      <c r="L30">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M30">
+        <v>40.77366720000001</v>
+      </c>
+      <c r="N30">
+        <v>-34.73366720000001</v>
+      </c>
+      <c r="O30">
+        <v>-0</v>
+      </c>
+      <c r="P30">
+        <v>-34.73366720000001</v>
+      </c>
+      <c r="Q30">
+        <v>-6.673667200000004</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.132526900063078</v>
+      </c>
+      <c r="T30">
+        <v>1.38521299813127</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.2388</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.148134823644217</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1642833680454162</v>
+      </c>
+      <c r="C31">
+        <v>206.8005979045226</v>
+      </c>
+      <c r="D31">
+        <v>352.2425979045226</v>
+      </c>
+      <c r="E31">
+        <v>-68.15800000000002</v>
+      </c>
+      <c r="F31">
+        <v>176.842</v>
+      </c>
+      <c r="G31">
+        <v>31.4</v>
+      </c>
+      <c r="H31">
+        <v>364.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>34.1</v>
+      </c>
+      <c r="K31">
+        <v>28.06</v>
+      </c>
+      <c r="L31">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M31">
+        <v>42.2298696</v>
+      </c>
+      <c r="N31">
+        <v>-36.1898696</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-36.1898696</v>
+      </c>
+      <c r="Q31">
+        <v>-8.129869599999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1338469972470651</v>
+      </c>
+      <c r="T31">
+        <v>1.404723040358471</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.2388</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.1430267262771752</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1662833680454162</v>
+      </c>
+      <c r="C32">
+        <v>195.1765029588817</v>
+      </c>
+      <c r="D32">
+        <v>346.7165029588817</v>
+      </c>
+      <c r="E32">
+        <v>-62.06000000000003</v>
+      </c>
+      <c r="F32">
+        <v>182.94</v>
+      </c>
+      <c r="G32">
+        <v>31.4</v>
+      </c>
+      <c r="H32">
+        <v>364.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>34.1</v>
+      </c>
+      <c r="K32">
+        <v>28.06</v>
+      </c>
+      <c r="L32">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M32">
+        <v>43.686072</v>
+      </c>
+      <c r="N32">
+        <v>-37.646072</v>
+      </c>
+      <c r="O32">
+        <v>-0</v>
+      </c>
+      <c r="P32">
+        <v>-37.646072</v>
+      </c>
+      <c r="Q32">
+        <v>-9.586071999999994</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1352048114934517</v>
+      </c>
+      <c r="T32">
+        <v>1.424790512363592</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.2388</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.1382591687346026</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1682833680454162</v>
+      </c>
+      <c r="C33">
+        <v>183.7231201295245</v>
+      </c>
+      <c r="D33">
+        <v>341.3611201295245</v>
+      </c>
+      <c r="E33">
+        <v>-55.96200000000002</v>
+      </c>
+      <c r="F33">
+        <v>189.038</v>
+      </c>
+      <c r="G33">
+        <v>31.4</v>
+      </c>
+      <c r="H33">
+        <v>364.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>34.1</v>
+      </c>
+      <c r="K33">
+        <v>28.06</v>
+      </c>
+      <c r="L33">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M33">
+        <v>45.1422744</v>
+      </c>
+      <c r="N33">
+        <v>-39.1022744</v>
+      </c>
+      <c r="O33">
+        <v>-0</v>
+      </c>
+      <c r="P33">
+        <v>-39.1022744</v>
+      </c>
+      <c r="Q33">
+        <v>-11.0422744</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1366019826745162</v>
+      </c>
+      <c r="T33">
+        <v>1.445439650223934</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.2388</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.1337991955496155</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1702833680454162</v>
+      </c>
+      <c r="C34">
+        <v>172.4326592851747</v>
+      </c>
+      <c r="D34">
+        <v>336.1686592851747</v>
+      </c>
+      <c r="E34">
+        <v>-49.864</v>
+      </c>
+      <c r="F34">
+        <v>195.136</v>
+      </c>
+      <c r="G34">
+        <v>31.4</v>
+      </c>
+      <c r="H34">
+        <v>364.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>34.1</v>
+      </c>
+      <c r="K34">
+        <v>28.06</v>
+      </c>
+      <c r="L34">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M34">
+        <v>46.5984768</v>
+      </c>
+      <c r="N34">
+        <v>-40.5584768</v>
+      </c>
+      <c r="O34">
+        <v>-0</v>
+      </c>
+      <c r="P34">
+        <v>-40.5584768</v>
+      </c>
+      <c r="Q34">
+        <v>-12.4984768</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1380402471256121</v>
+      </c>
+      <c r="T34">
+        <v>1.466696115668404</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.2388</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.12961797068869</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1722833680454162</v>
+      </c>
+      <c r="C35">
+        <v>161.2977971770685</v>
+      </c>
+      <c r="D35">
+        <v>331.1317971770685</v>
+      </c>
+      <c r="E35">
+        <v>-43.76600000000002</v>
+      </c>
+      <c r="F35">
+        <v>201.234</v>
+      </c>
+      <c r="G35">
+        <v>31.4</v>
+      </c>
+      <c r="H35">
+        <v>364.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>34.1</v>
+      </c>
+      <c r="K35">
+        <v>28.06</v>
+      </c>
+      <c r="L35">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M35">
+        <v>48.0546792</v>
+      </c>
+      <c r="N35">
+        <v>-42.0146792</v>
+      </c>
+      <c r="O35">
+        <v>-0</v>
+      </c>
+      <c r="P35">
+        <v>-42.0146792</v>
+      </c>
+      <c r="Q35">
+        <v>-13.95467919999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1395214448439048</v>
+      </c>
+      <c r="T35">
+        <v>1.488587102469425</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.2388</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1256901533950933</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1742833680454162</v>
+      </c>
+      <c r="C36">
+        <v>150.3116429784503</v>
+      </c>
+      <c r="D36">
+        <v>326.2436429784503</v>
+      </c>
+      <c r="E36">
+        <v>-37.66800000000001</v>
+      </c>
+      <c r="F36">
+        <v>207.332</v>
+      </c>
+      <c r="G36">
+        <v>31.4</v>
+      </c>
+      <c r="H36">
+        <v>364.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>34.1</v>
+      </c>
+      <c r="K36">
+        <v>28.06</v>
+      </c>
+      <c r="L36">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M36">
+        <v>49.5108816</v>
+      </c>
+      <c r="N36">
+        <v>-43.4708816</v>
+      </c>
+      <c r="O36">
+        <v>-0</v>
+      </c>
+      <c r="P36">
+        <v>-43.4708816</v>
+      </c>
+      <c r="Q36">
+        <v>-15.4108816</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1410475273415397</v>
+      </c>
+      <c r="T36">
+        <v>1.51114145250684</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.2388</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.1219933841775905</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1762833680454162</v>
+      </c>
+      <c r="C37">
+        <v>139.467706831895</v>
+      </c>
+      <c r="D37">
+        <v>321.4977068318951</v>
+      </c>
+      <c r="E37">
+        <v>-31.56999999999999</v>
+      </c>
+      <c r="F37">
+        <v>213.43</v>
+      </c>
+      <c r="G37">
+        <v>31.4</v>
+      </c>
+      <c r="H37">
+        <v>364.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>34.1</v>
+      </c>
+      <c r="K37">
+        <v>28.06</v>
+      </c>
+      <c r="L37">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M37">
+        <v>50.96708400000001</v>
+      </c>
+      <c r="N37">
+        <v>-44.92708400000001</v>
+      </c>
+      <c r="O37">
+        <v>-0</v>
+      </c>
+      <c r="P37">
+        <v>-44.92708400000001</v>
+      </c>
+      <c r="Q37">
+        <v>-16.86708400000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1426205662237172</v>
+      </c>
+      <c r="T37">
+        <v>1.534389782545407</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.2388</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1185078589153736</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1782833680454162</v>
+      </c>
+      <c r="C38">
+        <v>128.7598711025597</v>
+      </c>
+      <c r="D38">
+        <v>316.8878711025597</v>
+      </c>
+      <c r="E38">
+        <v>-25.47200000000004</v>
+      </c>
+      <c r="F38">
+        <v>219.528</v>
+      </c>
+      <c r="G38">
+        <v>31.4</v>
+      </c>
+      <c r="H38">
+        <v>364.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>34.1</v>
+      </c>
+      <c r="K38">
+        <v>28.06</v>
+      </c>
+      <c r="L38">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M38">
+        <v>52.42328639999999</v>
+      </c>
+      <c r="N38">
+        <v>-46.3832864</v>
+      </c>
+      <c r="O38">
+        <v>-0</v>
+      </c>
+      <c r="P38">
+        <v>-46.3832864</v>
+      </c>
+      <c r="Q38">
+        <v>-18.32328639999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1442427625709628</v>
+      </c>
+      <c r="T38">
+        <v>1.558364622897679</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.2388</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1152159739455022</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1802833680454162</v>
+      </c>
+      <c r="C39">
+        <v>118.1823640696081</v>
+      </c>
+      <c r="D39">
+        <v>312.4083640696081</v>
+      </c>
+      <c r="E39">
+        <v>-19.37400000000002</v>
+      </c>
+      <c r="F39">
+        <v>225.626</v>
+      </c>
+      <c r="G39">
+        <v>31.4</v>
+      </c>
+      <c r="H39">
+        <v>364.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>34.1</v>
+      </c>
+      <c r="K39">
+        <v>28.06</v>
+      </c>
+      <c r="L39">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M39">
+        <v>53.8794888</v>
+      </c>
+      <c r="N39">
+        <v>-47.8394888</v>
+      </c>
+      <c r="O39">
+        <v>-0</v>
+      </c>
+      <c r="P39">
+        <v>-47.8394888</v>
+      </c>
+      <c r="Q39">
+        <v>-19.7794888</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1459164572149464</v>
+      </c>
+      <c r="T39">
+        <v>1.58310056929288</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.2388</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1121020287037319</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1822833680454162</v>
+      </c>
+      <c r="C40">
+        <v>107.729735817911</v>
+      </c>
+      <c r="D40">
+        <v>308.053735817911</v>
+      </c>
+      <c r="E40">
+        <v>-13.27600000000001</v>
+      </c>
+      <c r="F40">
+        <v>231.724</v>
+      </c>
+      <c r="G40">
+        <v>31.4</v>
+      </c>
+      <c r="H40">
+        <v>364.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>34.1</v>
+      </c>
+      <c r="K40">
+        <v>28.06</v>
+      </c>
+      <c r="L40">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M40">
+        <v>55.3356912</v>
+      </c>
+      <c r="N40">
+        <v>-49.2956912</v>
+      </c>
+      <c r="O40">
+        <v>-0</v>
+      </c>
+      <c r="P40">
+        <v>-49.2956912</v>
+      </c>
+      <c r="Q40">
+        <v>-21.2356912</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1476441420087358</v>
+      </c>
+      <c r="T40">
+        <v>1.608634449442765</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.2388</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1091519753167915</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1842833680454162</v>
+      </c>
+      <c r="C41">
+        <v>97.39683611828707</v>
+      </c>
+      <c r="D41">
+        <v>303.8188361182871</v>
+      </c>
+      <c r="E41">
+        <v>-7.177999999999997</v>
+      </c>
+      <c r="F41">
+        <v>237.822</v>
+      </c>
+      <c r="G41">
+        <v>31.4</v>
+      </c>
+      <c r="H41">
+        <v>364.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>34.1</v>
+      </c>
+      <c r="K41">
+        <v>28.06</v>
+      </c>
+      <c r="L41">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M41">
+        <v>56.7918936</v>
+      </c>
+      <c r="N41">
+        <v>-50.7518936</v>
+      </c>
+      <c r="O41">
+        <v>-0</v>
+      </c>
+      <c r="P41">
+        <v>-50.7518936</v>
+      </c>
+      <c r="Q41">
+        <v>-22.6918936</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1494284722056003</v>
+      </c>
+      <c r="T41">
+        <v>1.635005505991007</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.2388</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1063532067189251</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1862833680454162</v>
+      </c>
+      <c r="C42">
+        <v>87.17879410751974</v>
+      </c>
+      <c r="D42">
+        <v>299.6987941075197</v>
+      </c>
+      <c r="E42">
+        <v>-1.080000000000013</v>
+      </c>
+      <c r="F42">
+        <v>243.92</v>
+      </c>
+      <c r="G42">
+        <v>31.4</v>
+      </c>
+      <c r="H42">
+        <v>364.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>34.1</v>
+      </c>
+      <c r="K42">
+        <v>28.06</v>
+      </c>
+      <c r="L42">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M42">
+        <v>58.248096</v>
+      </c>
+      <c r="N42">
+        <v>-52.208096</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-52.208096</v>
+      </c>
+      <c r="Q42">
+        <v>-24.148096</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1512722800756937</v>
+      </c>
+      <c r="T42">
+        <v>1.662255597757524</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.2388</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1036943765509519</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1882833680454162</v>
+      </c>
+      <c r="C43">
+        <v>77.07099959959206</v>
+      </c>
+      <c r="D43">
+        <v>295.6889995995921</v>
+      </c>
+      <c r="E43">
+        <v>5.018000000000001</v>
+      </c>
+      <c r="F43">
+        <v>250.018</v>
+      </c>
+      <c r="G43">
+        <v>31.4</v>
+      </c>
+      <c r="H43">
+        <v>364.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>34.1</v>
+      </c>
+      <c r="K43">
+        <v>28.06</v>
+      </c>
+      <c r="L43">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M43">
+        <v>59.70429840000001</v>
+      </c>
+      <c r="N43">
+        <v>-53.66429840000001</v>
+      </c>
+      <c r="O43">
+        <v>-0</v>
+      </c>
+      <c r="P43">
+        <v>-53.66429840000001</v>
+      </c>
+      <c r="Q43">
+        <v>-25.6042984</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1531785899074851</v>
+      </c>
+      <c r="T43">
+        <v>1.690429421448329</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.2388</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1011652454155629</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1902833680454162</v>
+      </c>
+      <c r="C44">
+        <v>67.06908587738155</v>
+      </c>
+      <c r="D44">
+        <v>291.7850858773816</v>
+      </c>
+      <c r="E44">
+        <v>11.11599999999999</v>
+      </c>
+      <c r="F44">
+        <v>256.116</v>
+      </c>
+      <c r="G44">
+        <v>31.4</v>
+      </c>
+      <c r="H44">
+        <v>364.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>34.1</v>
+      </c>
+      <c r="K44">
+        <v>28.06</v>
+      </c>
+      <c r="L44">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M44">
+        <v>61.1605008</v>
+      </c>
+      <c r="N44">
+        <v>-55.1205008</v>
+      </c>
+      <c r="O44">
+        <v>-0</v>
+      </c>
+      <c r="P44">
+        <v>-55.1205008</v>
+      </c>
+      <c r="Q44">
+        <v>-27.0605008</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1551506345610624</v>
+      </c>
+      <c r="T44">
+        <v>1.719574756300887</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.2388</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.09875654909614473</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1922833680454162</v>
+      </c>
+      <c r="C45">
+        <v>57.16891382977514</v>
+      </c>
+      <c r="D45">
+        <v>287.9829138297752</v>
+      </c>
+      <c r="E45">
+        <v>17.214</v>
+      </c>
+      <c r="F45">
+        <v>262.214</v>
+      </c>
+      <c r="G45">
+        <v>31.4</v>
+      </c>
+      <c r="H45">
+        <v>364.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>34.1</v>
+      </c>
+      <c r="K45">
+        <v>28.06</v>
+      </c>
+      <c r="L45">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M45">
+        <v>62.6167032</v>
+      </c>
+      <c r="N45">
+        <v>-56.5767032</v>
+      </c>
+      <c r="O45">
+        <v>-0</v>
+      </c>
+      <c r="P45">
+        <v>-56.5767032</v>
+      </c>
+      <c r="Q45">
+        <v>-28.5167032</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.157191873763888</v>
+      </c>
+      <c r="T45">
+        <v>1.749742734481604</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.2388</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.09645988516367621</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1942833680454162</v>
+      </c>
+      <c r="C46">
+        <v>47.36655731306189</v>
+      </c>
+      <c r="D46">
+        <v>284.2785573130619</v>
+      </c>
+      <c r="E46">
+        <v>23.31199999999995</v>
+      </c>
+      <c r="F46">
+        <v>268.312</v>
+      </c>
+      <c r="G46">
+        <v>31.4</v>
+      </c>
+      <c r="H46">
+        <v>364.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>34.1</v>
+      </c>
+      <c r="K46">
+        <v>28.06</v>
+      </c>
+      <c r="L46">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M46">
+        <v>64.0729056</v>
+      </c>
+      <c r="N46">
+        <v>-58.0329056</v>
+      </c>
+      <c r="O46">
+        <v>-0</v>
+      </c>
+      <c r="P46">
+        <v>-58.0329056</v>
+      </c>
+      <c r="Q46">
+        <v>-29.9729056</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1593060143668146</v>
+      </c>
+      <c r="T46">
+        <v>1.78098814045449</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.2388</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.09426761504631997</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1962833680454162</v>
+      </c>
+      <c r="C47">
+        <v>37.65828962776476</v>
+      </c>
+      <c r="D47">
+        <v>280.6682896277648</v>
+      </c>
+      <c r="E47">
+        <v>29.40999999999997</v>
+      </c>
+      <c r="F47">
+        <v>274.41</v>
+      </c>
+      <c r="G47">
+        <v>31.4</v>
+      </c>
+      <c r="H47">
+        <v>364.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>34.1</v>
+      </c>
+      <c r="K47">
+        <v>28.06</v>
+      </c>
+      <c r="L47">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M47">
+        <v>65.52910799999999</v>
+      </c>
+      <c r="N47">
+        <v>-59.48910799999999</v>
+      </c>
+      <c r="O47">
+        <v>-0</v>
+      </c>
+      <c r="P47">
+        <v>-59.48910799999999</v>
+      </c>
+      <c r="Q47">
+        <v>-31.42910799999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1614970328098476</v>
+      </c>
+      <c r="T47">
+        <v>1.813369743008208</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.2388</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.09217277915640176</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1982833680454162</v>
+      </c>
+      <c r="C48">
+        <v>28.0405710129956</v>
+      </c>
+      <c r="D48">
+        <v>277.1485710129956</v>
+      </c>
+      <c r="E48">
+        <v>35.50799999999998</v>
+      </c>
+      <c r="F48">
+        <v>280.508</v>
+      </c>
+      <c r="G48">
+        <v>31.4</v>
+      </c>
+      <c r="H48">
+        <v>364.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>34.1</v>
+      </c>
+      <c r="K48">
+        <v>28.06</v>
+      </c>
+      <c r="L48">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M48">
+        <v>66.9853104</v>
+      </c>
+      <c r="N48">
+        <v>-60.9453104</v>
+      </c>
+      <c r="O48">
+        <v>-0</v>
+      </c>
+      <c r="P48">
+        <v>-60.9453104</v>
+      </c>
+      <c r="Q48">
+        <v>-32.8853104</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1637692000841041</v>
+      </c>
+      <c r="T48">
+        <v>1.846950664175027</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.2388</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.09016902308778429</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2002833680454162</v>
+      </c>
+      <c r="C49">
+        <v>18.51003707011859</v>
+      </c>
+      <c r="D49">
+        <v>273.7160370701186</v>
+      </c>
+      <c r="E49">
+        <v>41.60599999999999</v>
+      </c>
+      <c r="F49">
+        <v>286.606</v>
+      </c>
+      <c r="G49">
+        <v>31.4</v>
+      </c>
+      <c r="H49">
+        <v>364.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>34.1</v>
+      </c>
+      <c r="K49">
+        <v>28.06</v>
+      </c>
+      <c r="L49">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M49">
+        <v>68.4415128</v>
+      </c>
+      <c r="N49">
+        <v>-62.4015128</v>
+      </c>
+      <c r="O49">
+        <v>-0</v>
+      </c>
+      <c r="P49">
+        <v>-62.4015128</v>
+      </c>
+      <c r="Q49">
+        <v>-34.3415128</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1661271095196532</v>
+      </c>
+      <c r="T49">
+        <v>1.881798789914178</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.2388</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.08825053323485277</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2022833680454162</v>
+      </c>
+      <c r="C50">
+        <v>9.063488036138892</v>
+      </c>
+      <c r="D50">
+        <v>270.3674880361389</v>
+      </c>
+      <c r="E50">
+        <v>47.70399999999995</v>
+      </c>
+      <c r="F50">
+        <v>292.704</v>
+      </c>
+      <c r="G50">
+        <v>31.4</v>
+      </c>
+      <c r="H50">
+        <v>364.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>34.1</v>
+      </c>
+      <c r="K50">
+        <v>28.06</v>
+      </c>
+      <c r="L50">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M50">
+        <v>69.89771519999999</v>
+      </c>
+      <c r="N50">
+        <v>-63.85771519999999</v>
+      </c>
+      <c r="O50">
+        <v>-0</v>
+      </c>
+      <c r="P50">
+        <v>-63.85771519999999</v>
+      </c>
+      <c r="Q50">
+        <v>-35.79771519999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1685757077796465</v>
+      </c>
+      <c r="T50">
+        <v>1.917987228181758</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.2388</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.08641198045912668</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2042833680454162</v>
+      </c>
+      <c r="C51">
+        <v>-0.3021211650702753</v>
+      </c>
+      <c r="D51">
+        <v>267.0998788349297</v>
+      </c>
+      <c r="E51">
+        <v>53.80199999999996</v>
+      </c>
+      <c r="F51">
+        <v>298.802</v>
+      </c>
+      <c r="G51">
+        <v>31.4</v>
+      </c>
+      <c r="H51">
+        <v>364.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>34.1</v>
+      </c>
+      <c r="K51">
+        <v>28.06</v>
+      </c>
+      <c r="L51">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M51">
+        <v>71.35391759999999</v>
+      </c>
+      <c r="N51">
+        <v>-65.3139176</v>
+      </c>
+      <c r="O51">
+        <v>-0</v>
+      </c>
+      <c r="P51">
+        <v>-65.3139176</v>
+      </c>
+      <c r="Q51">
+        <v>-37.25391759999999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1711203295008161</v>
+      </c>
+      <c r="T51">
+        <v>1.955594820891205</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.2388</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.08464847065383829</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2062833680454162</v>
+      </c>
+      <c r="C52">
+        <v>-9.589690158720998</v>
+      </c>
+      <c r="D52">
+        <v>263.910309841279</v>
+      </c>
+      <c r="E52">
+        <v>59.89999999999998</v>
+      </c>
+      <c r="F52">
+        <v>304.9</v>
+      </c>
+      <c r="G52">
+        <v>31.4</v>
+      </c>
+      <c r="H52">
+        <v>364.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>34.1</v>
+      </c>
+      <c r="K52">
+        <v>28.06</v>
+      </c>
+      <c r="L52">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M52">
+        <v>72.81012</v>
+      </c>
+      <c r="N52">
+        <v>-66.77011999999999</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-66.77011999999999</v>
+      </c>
+      <c r="Q52">
+        <v>-38.71011999999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1737667360908324</v>
+      </c>
+      <c r="T52">
+        <v>1.994706717309029</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.2388</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.08295550124076168</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2082833680454162</v>
+      </c>
+      <c r="C53">
+        <v>-18.80198170112845</v>
+      </c>
+      <c r="D53">
+        <v>260.7960182988716</v>
+      </c>
+      <c r="E53">
+        <v>65.99799999999999</v>
+      </c>
+      <c r="F53">
+        <v>310.998</v>
+      </c>
+      <c r="G53">
+        <v>31.4</v>
+      </c>
+      <c r="H53">
+        <v>364.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>34.1</v>
+      </c>
+      <c r="K53">
+        <v>28.06</v>
+      </c>
+      <c r="L53">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M53">
+        <v>74.26632240000001</v>
+      </c>
+      <c r="N53">
+        <v>-68.22632240000002</v>
+      </c>
+      <c r="O53">
+        <v>-0</v>
+      </c>
+      <c r="P53">
+        <v>-68.22632240000002</v>
+      </c>
+      <c r="Q53">
+        <v>-40.16632240000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1765211592763596</v>
+      </c>
+      <c r="T53">
+        <v>2.035415017662274</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.2388</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.08132892278506021</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2102833680454162</v>
+      </c>
+      <c r="C54">
+        <v>-27.9416296611779</v>
+      </c>
+      <c r="D54">
+        <v>257.7543703388221</v>
+      </c>
+      <c r="E54">
+        <v>72.096</v>
+      </c>
+      <c r="F54">
+        <v>317.096</v>
+      </c>
+      <c r="G54">
+        <v>31.4</v>
+      </c>
+      <c r="H54">
+        <v>364.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>34.1</v>
+      </c>
+      <c r="K54">
+        <v>28.06</v>
+      </c>
+      <c r="L54">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M54">
+        <v>75.7225248</v>
+      </c>
+      <c r="N54">
+        <v>-69.68252480000001</v>
+      </c>
+      <c r="O54">
+        <v>-0</v>
+      </c>
+      <c r="P54">
+        <v>-69.68252480000001</v>
+      </c>
+      <c r="Q54">
+        <v>-41.62252480000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1793903500946171</v>
+      </c>
+      <c r="T54">
+        <v>2.077819497196905</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.2388</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.07976490503919376</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2122833680454162</v>
+      </c>
+      <c r="C55">
+        <v>-37.01114644970767</v>
+      </c>
+      <c r="D55">
+        <v>254.7828535502924</v>
+      </c>
+      <c r="E55">
+        <v>78.19400000000002</v>
+      </c>
+      <c r="F55">
+        <v>323.194</v>
+      </c>
+      <c r="G55">
+        <v>31.4</v>
+      </c>
+      <c r="H55">
+        <v>364.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>34.1</v>
+      </c>
+      <c r="K55">
+        <v>28.06</v>
+      </c>
+      <c r="L55">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M55">
+        <v>77.17872720000001</v>
+      </c>
+      <c r="N55">
+        <v>-71.13872720000001</v>
+      </c>
+      <c r="O55">
+        <v>-0</v>
+      </c>
+      <c r="P55">
+        <v>-71.13872720000001</v>
+      </c>
+      <c r="Q55">
+        <v>-43.0787272</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1823816341391834</v>
+      </c>
+      <c r="T55">
+        <v>2.122028422669179</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.2388</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.07825990683090722</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2142833680454162</v>
+      </c>
+      <c r="C56">
+        <v>-46.01292994085139</v>
+      </c>
+      <c r="D56">
+        <v>251.8790700591486</v>
+      </c>
+      <c r="E56">
+        <v>84.29199999999997</v>
+      </c>
+      <c r="F56">
+        <v>329.292</v>
+      </c>
+      <c r="G56">
+        <v>31.4</v>
+      </c>
+      <c r="H56">
+        <v>364.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>34.1</v>
+      </c>
+      <c r="K56">
+        <v>28.06</v>
+      </c>
+      <c r="L56">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M56">
+        <v>78.63492959999999</v>
+      </c>
+      <c r="N56">
+        <v>-72.5949296</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-72.5949296</v>
+      </c>
+      <c r="Q56">
+        <v>-44.5349296</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1855029740117743</v>
+      </c>
+      <c r="T56">
+        <v>2.168159475335901</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.2388</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.07681064929700132</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2162833680454162</v>
+      </c>
+      <c r="C57">
+        <v>-54.94926992541485</v>
+      </c>
+      <c r="D57">
+        <v>249.0407300745852</v>
+      </c>
+      <c r="E57">
+        <v>90.38999999999999</v>
+      </c>
+      <c r="F57">
+        <v>335.39</v>
+      </c>
+      <c r="G57">
+        <v>31.4</v>
+      </c>
+      <c r="H57">
+        <v>364.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>34.1</v>
+      </c>
+      <c r="K57">
+        <v>28.06</v>
+      </c>
+      <c r="L57">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M57">
+        <v>80.091132</v>
+      </c>
+      <c r="N57">
+        <v>-74.051132</v>
+      </c>
+      <c r="O57">
+        <v>-0</v>
+      </c>
+      <c r="P57">
+        <v>-74.051132</v>
+      </c>
+      <c r="Q57">
+        <v>-45.99113199999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1887630401009249</v>
+      </c>
+      <c r="T57">
+        <v>2.216340797010032</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.2388</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.07541409203705607</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2182833680454162</v>
+      </c>
+      <c r="C58">
+        <v>-63.82235413278909</v>
+      </c>
+      <c r="D58">
+        <v>246.2656458672109</v>
+      </c>
+      <c r="E58">
+        <v>96.488</v>
+      </c>
+      <c r="F58">
+        <v>341.488</v>
+      </c>
+      <c r="G58">
+        <v>31.4</v>
+      </c>
+      <c r="H58">
+        <v>364.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>34.1</v>
+      </c>
+      <c r="K58">
+        <v>28.06</v>
+      </c>
+      <c r="L58">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M58">
+        <v>81.54733440000001</v>
+      </c>
+      <c r="N58">
+        <v>-75.50733440000002</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-75.50733440000002</v>
+      </c>
+      <c r="Q58">
+        <v>-47.44733440000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1921712910123095</v>
+      </c>
+      <c r="T58">
+        <v>2.26671217876026</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.2388</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.07406741182210841</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2202833680454162</v>
+      </c>
+      <c r="C59">
+        <v>-72.63427385468435</v>
+      </c>
+      <c r="D59">
+        <v>243.5517261453157</v>
+      </c>
+      <c r="E59">
+        <v>102.586</v>
+      </c>
+      <c r="F59">
+        <v>347.586</v>
+      </c>
+      <c r="G59">
+        <v>31.4</v>
+      </c>
+      <c r="H59">
+        <v>364.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>34.1</v>
+      </c>
+      <c r="K59">
+        <v>28.06</v>
+      </c>
+      <c r="L59">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M59">
+        <v>83.00353680000001</v>
+      </c>
+      <c r="N59">
+        <v>-76.96353680000001</v>
+      </c>
+      <c r="O59">
+        <v>-0</v>
+      </c>
+      <c r="P59">
+        <v>-76.96353680000001</v>
+      </c>
+      <c r="Q59">
+        <v>-48.90353680000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1957380652218982</v>
+      </c>
+      <c r="T59">
+        <v>2.319426415475615</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.2388</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.07276798354452763</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2222833680454162</v>
+      </c>
+      <c r="C60">
+        <v>-81.38702920106562</v>
+      </c>
+      <c r="D60">
+        <v>240.8969707989343</v>
+      </c>
+      <c r="E60">
+        <v>108.684</v>
+      </c>
+      <c r="F60">
+        <v>353.684</v>
+      </c>
+      <c r="G60">
+        <v>31.4</v>
+      </c>
+      <c r="H60">
+        <v>364.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>34.1</v>
+      </c>
+      <c r="K60">
+        <v>28.06</v>
+      </c>
+      <c r="L60">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M60">
+        <v>84.4597392</v>
+      </c>
+      <c r="N60">
+        <v>-78.41973920000001</v>
+      </c>
+      <c r="O60">
+        <v>-0</v>
+      </c>
+      <c r="P60">
+        <v>-78.41973920000001</v>
+      </c>
+      <c r="Q60">
+        <v>-50.35973920000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1994746858224195</v>
+      </c>
+      <c r="T60">
+        <v>2.37465085393932</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.2388</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.07151336313858747</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2242833680454162</v>
+      </c>
+      <c r="C61">
+        <v>-90.08253401605208</v>
+      </c>
+      <c r="D61">
+        <v>238.2994659839479</v>
+      </c>
+      <c r="E61">
+        <v>114.782</v>
+      </c>
+      <c r="F61">
+        <v>359.782</v>
+      </c>
+      <c r="G61">
+        <v>31.4</v>
+      </c>
+      <c r="H61">
+        <v>364.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>34.1</v>
+      </c>
+      <c r="K61">
+        <v>28.06</v>
+      </c>
+      <c r="L61">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M61">
+        <v>85.9159416</v>
+      </c>
+      <c r="N61">
+        <v>-79.8759416</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-79.8759416</v>
+      </c>
+      <c r="Q61">
+        <v>-51.8159416</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2033935805985761</v>
+      </c>
+      <c r="T61">
+        <v>2.432569167450035</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.2388</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.07030127223793348</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2262833680454162</v>
+      </c>
+      <c r="C62">
+        <v>-98.72262047916934</v>
+      </c>
+      <c r="D62">
+        <v>235.7573795208306</v>
+      </c>
+      <c r="E62">
+        <v>120.8799999999999</v>
+      </c>
+      <c r="F62">
+        <v>365.8799999999999</v>
+      </c>
+      <c r="G62">
+        <v>31.4</v>
+      </c>
+      <c r="H62">
+        <v>364.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>34.1</v>
+      </c>
+      <c r="K62">
+        <v>28.06</v>
+      </c>
+      <c r="L62">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M62">
+        <v>87.37214399999999</v>
+      </c>
+      <c r="N62">
+        <v>-81.332144</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-81.332144</v>
+      </c>
+      <c r="Q62">
+        <v>-53.272144</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2075084201135405</v>
+      </c>
+      <c r="T62">
+        <v>2.493383396636286</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.2388</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.06912958436730121</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2282833680454162</v>
+      </c>
+      <c r="C63">
+        <v>-107.3090434152058</v>
+      </c>
+      <c r="D63">
+        <v>233.2689565847941</v>
+      </c>
+      <c r="E63">
+        <v>126.978</v>
+      </c>
+      <c r="F63">
+        <v>371.978</v>
+      </c>
+      <c r="G63">
+        <v>31.4</v>
+      </c>
+      <c r="H63">
+        <v>364.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>34.1</v>
+      </c>
+      <c r="K63">
+        <v>28.06</v>
+      </c>
+      <c r="L63">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M63">
+        <v>88.82834639999999</v>
+      </c>
+      <c r="N63">
+        <v>-82.78834639999999</v>
+      </c>
+      <c r="O63">
+        <v>-0</v>
+      </c>
+      <c r="P63">
+        <v>-82.78834639999999</v>
+      </c>
+      <c r="Q63">
+        <v>-54.72834639999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2118342770395287</v>
+      </c>
+      <c r="T63">
+        <v>2.557316304242344</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.2388</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.06799631249242744</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2302833680454162</v>
+      </c>
+      <c r="C64">
+        <v>-115.843484333975</v>
+      </c>
+      <c r="D64">
+        <v>230.8325156660249</v>
+      </c>
+      <c r="E64">
+        <v>133.076</v>
+      </c>
+      <c r="F64">
+        <v>378.076</v>
+      </c>
+      <c r="G64">
+        <v>31.4</v>
+      </c>
+      <c r="H64">
+        <v>364.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>34.1</v>
+      </c>
+      <c r="K64">
+        <v>28.06</v>
+      </c>
+      <c r="L64">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M64">
+        <v>90.2845488</v>
+      </c>
+      <c r="N64">
+        <v>-84.24454879999999</v>
+      </c>
+      <c r="O64">
+        <v>-0</v>
+      </c>
+      <c r="P64">
+        <v>-84.24454879999999</v>
+      </c>
+      <c r="Q64">
+        <v>-56.18454879999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2163878106458321</v>
+      </c>
+      <c r="T64">
+        <v>2.624614101722406</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.2388</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.06689959777480781</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2322833680454162</v>
+      </c>
+      <c r="C65">
+        <v>-124.3275552195288</v>
+      </c>
+      <c r="D65">
+        <v>228.4464447804712</v>
+      </c>
+      <c r="E65">
+        <v>139.174</v>
+      </c>
+      <c r="F65">
+        <v>384.174</v>
+      </c>
+      <c r="G65">
+        <v>31.4</v>
+      </c>
+      <c r="H65">
+        <v>364.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>34.1</v>
+      </c>
+      <c r="K65">
+        <v>28.06</v>
+      </c>
+      <c r="L65">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M65">
+        <v>91.74075120000001</v>
+      </c>
+      <c r="N65">
+        <v>-85.70075120000001</v>
+      </c>
+      <c r="O65">
+        <v>-0</v>
+      </c>
+      <c r="P65">
+        <v>-85.70075120000001</v>
+      </c>
+      <c r="Q65">
+        <v>-57.64075120000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2211874812038276</v>
+      </c>
+      <c r="T65">
+        <v>2.695549617985174</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.2388</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.06583769939742978</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2342833680454162</v>
+      </c>
+      <c r="C66">
+        <v>-132.7628020867651</v>
+      </c>
+      <c r="D66">
+        <v>226.1091979132349</v>
+      </c>
+      <c r="E66">
+        <v>145.272</v>
+      </c>
+      <c r="F66">
+        <v>390.272</v>
+      </c>
+      <c r="G66">
+        <v>31.4</v>
+      </c>
+      <c r="H66">
+        <v>364.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>34.1</v>
+      </c>
+      <c r="K66">
+        <v>28.06</v>
+      </c>
+      <c r="L66">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M66">
+        <v>93.1969536</v>
+      </c>
+      <c r="N66">
+        <v>-87.15695360000001</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-87.15695360000001</v>
+      </c>
+      <c r="Q66">
+        <v>-59.09695360000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2262538001261561</v>
+      </c>
+      <c r="T66">
+        <v>2.77042599626254</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.2388</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.06480898534434487</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2362833680454162</v>
+      </c>
+      <c r="C67">
+        <v>-141.1507083219194</v>
+      </c>
+      <c r="D67">
+        <v>223.8192916780806</v>
+      </c>
+      <c r="E67">
+        <v>151.37</v>
+      </c>
+      <c r="F67">
+        <v>396.37</v>
+      </c>
+      <c r="G67">
+        <v>31.4</v>
+      </c>
+      <c r="H67">
+        <v>364.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>34.1</v>
+      </c>
+      <c r="K67">
+        <v>28.06</v>
+      </c>
+      <c r="L67">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M67">
+        <v>94.65315600000001</v>
+      </c>
+      <c r="N67">
+        <v>-88.613156</v>
+      </c>
+      <c r="O67">
+        <v>-0</v>
+      </c>
+      <c r="P67">
+        <v>-88.613156</v>
+      </c>
+      <c r="Q67">
+        <v>-60.553156</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2316096229869035</v>
+      </c>
+      <c r="T67">
+        <v>2.849581024727184</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.2388</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.06381192403135516</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2382833680454162</v>
+      </c>
+      <c r="C68">
+        <v>-149.492697822108</v>
+      </c>
+      <c r="D68">
+        <v>221.575302177892</v>
+      </c>
+      <c r="E68">
+        <v>157.468</v>
+      </c>
+      <c r="F68">
+        <v>402.468</v>
+      </c>
+      <c r="G68">
+        <v>31.4</v>
+      </c>
+      <c r="H68">
+        <v>364.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>34.1</v>
+      </c>
+      <c r="K68">
+        <v>28.06</v>
+      </c>
+      <c r="L68">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M68">
+        <v>96.10935839999999</v>
+      </c>
+      <c r="N68">
+        <v>-90.0693584</v>
+      </c>
+      <c r="O68">
+        <v>-0</v>
+      </c>
+      <c r="P68">
+        <v>-90.0693584</v>
+      </c>
+      <c r="Q68">
+        <v>-62.0093584</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2372804942512241</v>
+      </c>
+      <c r="T68">
+        <v>2.933392231336807</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.2388</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.06284507669754658</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2402833680454162</v>
+      </c>
+      <c r="C69">
+        <v>-157.7901379478849</v>
+      </c>
+      <c r="D69">
+        <v>219.3758620521151</v>
+      </c>
+      <c r="E69">
+        <v>163.566</v>
+      </c>
+      <c r="F69">
+        <v>408.566</v>
+      </c>
+      <c r="G69">
+        <v>31.4</v>
+      </c>
+      <c r="H69">
+        <v>364.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>34.1</v>
+      </c>
+      <c r="K69">
+        <v>28.06</v>
+      </c>
+      <c r="L69">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M69">
+        <v>97.5655608</v>
+      </c>
+      <c r="N69">
+        <v>-91.52556079999999</v>
+      </c>
+      <c r="O69">
+        <v>-0</v>
+      </c>
+      <c r="P69">
+        <v>-91.52556079999999</v>
+      </c>
+      <c r="Q69">
+        <v>-63.46556079999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2432950546830794</v>
+      </c>
+      <c r="T69">
+        <v>3.02228290501368</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.2388</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.06190709047818033</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2422833680454162</v>
+      </c>
+      <c r="C70">
+        <v>-166.0443423016792</v>
+      </c>
+      <c r="D70">
+        <v>217.2196576983208</v>
+      </c>
+      <c r="E70">
+        <v>169.664</v>
+      </c>
+      <c r="F70">
+        <v>414.664</v>
+      </c>
+      <c r="G70">
+        <v>31.4</v>
+      </c>
+      <c r="H70">
+        <v>364.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>34.1</v>
+      </c>
+      <c r="K70">
+        <v>28.06</v>
+      </c>
+      <c r="L70">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M70">
+        <v>99.0217632</v>
+      </c>
+      <c r="N70">
+        <v>-92.98176319999999</v>
+      </c>
+      <c r="O70">
+        <v>-0</v>
+      </c>
+      <c r="P70">
+        <v>-92.98176319999999</v>
+      </c>
+      <c r="Q70">
+        <v>-64.92176319999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2496855251419256</v>
+      </c>
+      <c r="T70">
+        <v>3.116729245795358</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.2388</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.06099669208879532</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2442833680454162</v>
+      </c>
+      <c r="C71">
+        <v>-174.2565733439726</v>
+      </c>
+      <c r="D71">
+        <v>215.1054266560274</v>
+      </c>
+      <c r="E71">
+        <v>175.762</v>
+      </c>
+      <c r="F71">
+        <v>420.762</v>
+      </c>
+      <c r="G71">
+        <v>31.4</v>
+      </c>
+      <c r="H71">
+        <v>364.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>34.1</v>
+      </c>
+      <c r="K71">
+        <v>28.06</v>
+      </c>
+      <c r="L71">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M71">
+        <v>100.4779656</v>
+      </c>
+      <c r="N71">
+        <v>-94.43796560000001</v>
+      </c>
+      <c r="O71">
+        <v>-0</v>
+      </c>
+      <c r="P71">
+        <v>-94.43796560000001</v>
+      </c>
+      <c r="Q71">
+        <v>-66.37796560000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2564882840174716</v>
+      </c>
+      <c r="T71">
+        <v>3.217268898885531</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.2388</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.06011268205852283</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2462833680454162</v>
+      </c>
+      <c r="C72">
+        <v>-182.4280448581708</v>
+      </c>
+      <c r="D72">
+        <v>213.0319551418292</v>
+      </c>
+      <c r="E72">
+        <v>181.86</v>
+      </c>
+      <c r="F72">
+        <v>426.86</v>
+      </c>
+      <c r="G72">
+        <v>31.4</v>
+      </c>
+      <c r="H72">
+        <v>364.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>34.1</v>
+      </c>
+      <c r="K72">
+        <v>28.06</v>
+      </c>
+      <c r="L72">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M72">
+        <v>101.934168</v>
+      </c>
+      <c r="N72">
+        <v>-95.89416800000001</v>
+      </c>
+      <c r="O72">
+        <v>-0</v>
+      </c>
+      <c r="P72">
+        <v>-95.89416800000001</v>
+      </c>
+      <c r="Q72">
+        <v>-67.83416800000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2637445601513874</v>
+      </c>
+      <c r="T72">
+        <v>3.324511195515048</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.2388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.05925392945768693</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2482833680454162</v>
+      </c>
+      <c r="C73">
+        <v>-190.5599242742745</v>
+      </c>
+      <c r="D73">
+        <v>210.9980757257254</v>
+      </c>
+      <c r="E73">
+        <v>187.958</v>
+      </c>
+      <c r="F73">
+        <v>432.958</v>
+      </c>
+      <c r="G73">
+        <v>31.4</v>
+      </c>
+      <c r="H73">
+        <v>364.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>34.1</v>
+      </c>
+      <c r="K73">
+        <v>28.06</v>
+      </c>
+      <c r="L73">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M73">
+        <v>103.3903704</v>
+      </c>
+      <c r="N73">
+        <v>-97.3503704</v>
+      </c>
+      <c r="O73">
+        <v>-0</v>
+      </c>
+      <c r="P73">
+        <v>-97.3503704</v>
+      </c>
+      <c r="Q73">
+        <v>-69.2903704</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2715012691221248</v>
+      </c>
+      <c r="T73">
+        <v>3.439149512601773</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.2388</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.05841936707095874</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2502833680454162</v>
+      </c>
+      <c r="C74">
+        <v>-198.6533348607033</v>
+      </c>
+      <c r="D74">
+        <v>209.0026651392966</v>
+      </c>
+      <c r="E74">
+        <v>194.0559999999999</v>
+      </c>
+      <c r="F74">
+        <v>439.0559999999999</v>
+      </c>
+      <c r="G74">
+        <v>31.4</v>
+      </c>
+      <c r="H74">
+        <v>364.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>34.1</v>
+      </c>
+      <c r="K74">
+        <v>28.06</v>
+      </c>
+      <c r="L74">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M74">
+        <v>104.8465728</v>
+      </c>
+      <c r="N74">
+        <v>-98.8065728</v>
+      </c>
+      <c r="O74">
+        <v>-0</v>
+      </c>
+      <c r="P74">
+        <v>-98.8065728</v>
+      </c>
+      <c r="Q74">
+        <v>-70.7465728</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2798120287336293</v>
+      </c>
+      <c r="T74">
+        <v>3.56197628090898</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.2388</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.05760798697275105</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2522833680454162</v>
+      </c>
+      <c r="C75">
+        <v>-206.7093577929144</v>
+      </c>
+      <c r="D75">
+        <v>207.0446422070855</v>
+      </c>
+      <c r="E75">
+        <v>200.1539999999999</v>
+      </c>
+      <c r="F75">
+        <v>445.1539999999999</v>
+      </c>
+      <c r="G75">
+        <v>31.4</v>
+      </c>
+      <c r="H75">
+        <v>364.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>34.1</v>
+      </c>
+      <c r="K75">
+        <v>28.06</v>
+      </c>
+      <c r="L75">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M75">
+        <v>106.3027752</v>
+      </c>
+      <c r="N75">
+        <v>-100.2627752</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
+        <v>-100.2627752</v>
+      </c>
+      <c r="Q75">
+        <v>-72.20277519999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2887384001682081</v>
+      </c>
+      <c r="T75">
+        <v>3.693901328350053</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.2388</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.05681883646627495</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2542833680454162</v>
+      </c>
+      <c r="C76">
+        <v>-214.7290341068232</v>
+      </c>
+      <c r="D76">
+        <v>205.1229658931767</v>
+      </c>
+      <c r="E76">
+        <v>206.252</v>
+      </c>
+      <c r="F76">
+        <v>451.252</v>
+      </c>
+      <c r="G76">
+        <v>31.4</v>
+      </c>
+      <c r="H76">
+        <v>364.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>34.1</v>
+      </c>
+      <c r="K76">
+        <v>28.06</v>
+      </c>
+      <c r="L76">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M76">
+        <v>107.7589776</v>
+      </c>
+      <c r="N76">
+        <v>-101.7189776</v>
+      </c>
+      <c r="O76">
+        <v>-0</v>
+      </c>
+      <c r="P76">
+        <v>-101.7189776</v>
+      </c>
+      <c r="Q76">
+        <v>-73.65897759999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2983514155592931</v>
+      </c>
+      <c r="T76">
+        <v>3.835974456363517</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.2388</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.05605101435186599</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2562833680454162</v>
+      </c>
+      <c r="C77">
+        <v>-222.7133665444407</v>
+      </c>
+      <c r="D77">
+        <v>203.2366334555593</v>
+      </c>
+      <c r="E77">
+        <v>212.35</v>
+      </c>
+      <c r="F77">
+        <v>457.35</v>
+      </c>
+      <c r="G77">
+        <v>31.4</v>
+      </c>
+      <c r="H77">
+        <v>364.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>34.1</v>
+      </c>
+      <c r="K77">
+        <v>28.06</v>
+      </c>
+      <c r="L77">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M77">
+        <v>109.21518</v>
+      </c>
+      <c r="N77">
+        <v>-103.17518</v>
+      </c>
+      <c r="O77">
+        <v>-0</v>
+      </c>
+      <c r="P77">
+        <v>-103.17518</v>
+      </c>
+      <c r="Q77">
+        <v>-75.11518000000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3087334721816648</v>
+      </c>
+      <c r="T77">
+        <v>3.989413434618057</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.2388</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.05530366749384097</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2582833680454162</v>
+      </c>
+      <c r="C78">
+        <v>-230.6633212986023</v>
+      </c>
+      <c r="D78">
+        <v>201.3846787013977</v>
+      </c>
+      <c r="E78">
+        <v>218.448</v>
+      </c>
+      <c r="F78">
+        <v>463.448</v>
+      </c>
+      <c r="G78">
+        <v>31.4</v>
+      </c>
+      <c r="H78">
+        <v>364.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>34.1</v>
+      </c>
+      <c r="K78">
+        <v>28.06</v>
+      </c>
+      <c r="L78">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M78">
+        <v>110.6713824</v>
+      </c>
+      <c r="N78">
+        <v>-104.6313824</v>
+      </c>
+      <c r="O78">
+        <v>-0</v>
+      </c>
+      <c r="P78">
+        <v>-104.6313824</v>
+      </c>
+      <c r="Q78">
+        <v>-76.5713824</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3199807001892341</v>
+      </c>
+      <c r="T78">
+        <v>4.15563899439381</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.2388</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.05457598765839566</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2602833680454162</v>
+      </c>
+      <c r="C79">
+        <v>-238.5798296631681</v>
+      </c>
+      <c r="D79">
+        <v>199.5661703368319</v>
+      </c>
+      <c r="E79">
+        <v>224.546</v>
+      </c>
+      <c r="F79">
+        <v>469.546</v>
+      </c>
+      <c r="G79">
+        <v>31.4</v>
+      </c>
+      <c r="H79">
+        <v>364.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>34.1</v>
+      </c>
+      <c r="K79">
+        <v>28.06</v>
+      </c>
+      <c r="L79">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M79">
+        <v>112.1275848</v>
+      </c>
+      <c r="N79">
+        <v>-106.0875848</v>
+      </c>
+      <c r="O79">
+        <v>-0</v>
+      </c>
+      <c r="P79">
+        <v>-106.0875848</v>
+      </c>
+      <c r="Q79">
+        <v>-78.0275848</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3322059480235486</v>
+      </c>
+      <c r="T79">
+        <v>4.336318950671801</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.2388</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.05386720859789718</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2622833680454162</v>
+      </c>
+      <c r="C80">
+        <v>-246.463789594614</v>
+      </c>
+      <c r="D80">
+        <v>197.780210405386</v>
+      </c>
+      <c r="E80">
+        <v>230.644</v>
+      </c>
+      <c r="F80">
+        <v>475.644</v>
+      </c>
+      <c r="G80">
+        <v>31.4</v>
+      </c>
+      <c r="H80">
+        <v>364.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>34.1</v>
+      </c>
+      <c r="K80">
+        <v>28.06</v>
+      </c>
+      <c r="L80">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M80">
+        <v>113.5837872</v>
+      </c>
+      <c r="N80">
+        <v>-107.5437872</v>
+      </c>
+      <c r="O80">
+        <v>-0</v>
+      </c>
+      <c r="P80">
+        <v>-107.5437872</v>
+      </c>
+      <c r="Q80">
+        <v>-79.48378719999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3455425820246191</v>
+      </c>
+      <c r="T80">
+        <v>4.53342435752052</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.2388</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.05317660335946262</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2642833680454162</v>
+      </c>
+      <c r="C81">
+        <v>-254.3160671905166</v>
+      </c>
+      <c r="D81">
+        <v>196.0259328094833</v>
+      </c>
+      <c r="E81">
+        <v>236.742</v>
+      </c>
+      <c r="F81">
+        <v>481.742</v>
+      </c>
+      <c r="G81">
+        <v>31.4</v>
+      </c>
+      <c r="H81">
+        <v>364.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>34.1</v>
+      </c>
+      <c r="K81">
+        <v>28.06</v>
+      </c>
+      <c r="L81">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M81">
+        <v>115.0399896</v>
+      </c>
+      <c r="N81">
+        <v>-108.9999896</v>
+      </c>
+      <c r="O81">
+        <v>-0</v>
+      </c>
+      <c r="P81">
+        <v>-108.9999896</v>
+      </c>
+      <c r="Q81">
+        <v>-80.93998959999999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3601493716448391</v>
+      </c>
+      <c r="T81">
+        <v>4.749301707878641</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.2388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.05250348179795039</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2662833680454162</v>
+      </c>
+      <c r="C82">
+        <v>-262.1374980900482</v>
+      </c>
+      <c r="D82">
+        <v>194.3025019099518</v>
+      </c>
+      <c r="E82">
+        <v>242.84</v>
+      </c>
+      <c r="F82">
+        <v>487.84</v>
+      </c>
+      <c r="G82">
+        <v>31.4</v>
+      </c>
+      <c r="H82">
+        <v>364.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>34.1</v>
+      </c>
+      <c r="K82">
+        <v>28.06</v>
+      </c>
+      <c r="L82">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M82">
+        <v>116.496192</v>
+      </c>
+      <c r="N82">
+        <v>-110.456192</v>
+      </c>
+      <c r="O82">
+        <v>-0</v>
+      </c>
+      <c r="P82">
+        <v>-110.456192</v>
+      </c>
+      <c r="Q82">
+        <v>-82.39619199999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.376216840227081</v>
+      </c>
+      <c r="T82">
+        <v>4.986766793272572</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.2388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.05184718827547607</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2682833680454162</v>
+      </c>
+      <c r="C83">
+        <v>-269.9288888012347</v>
+      </c>
+      <c r="D83">
+        <v>192.6091111987653</v>
+      </c>
+      <c r="E83">
+        <v>248.938</v>
+      </c>
+      <c r="F83">
+        <v>493.938</v>
+      </c>
+      <c r="G83">
+        <v>31.4</v>
+      </c>
+      <c r="H83">
+        <v>364.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>34.1</v>
+      </c>
+      <c r="K83">
+        <v>28.06</v>
+      </c>
+      <c r="L83">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M83">
+        <v>117.9523944</v>
+      </c>
+      <c r="N83">
+        <v>-111.9123944</v>
+      </c>
+      <c r="O83">
+        <v>-0</v>
+      </c>
+      <c r="P83">
+        <v>-111.9123944</v>
+      </c>
+      <c r="Q83">
+        <v>-83.85239440000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3939756212916642</v>
+      </c>
+      <c r="T83">
+        <v>5.249228203444813</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.2388</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.05120709953133429</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2702833680454162</v>
+      </c>
+      <c r="C84">
+        <v>-277.6910179594123</v>
+      </c>
+      <c r="D84">
+        <v>190.9449820405877</v>
+      </c>
+      <c r="E84">
+        <v>255.036</v>
+      </c>
+      <c r="F84">
+        <v>500.036</v>
+      </c>
+      <c r="G84">
+        <v>31.4</v>
+      </c>
+      <c r="H84">
+        <v>364.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>34.1</v>
+      </c>
+      <c r="K84">
+        <v>28.06</v>
+      </c>
+      <c r="L84">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M84">
+        <v>119.4085968</v>
+      </c>
+      <c r="N84">
+        <v>-113.3685968</v>
+      </c>
+      <c r="O84">
+        <v>-0</v>
+      </c>
+      <c r="P84">
+        <v>-113.3685968</v>
+      </c>
+      <c r="Q84">
+        <v>-85.3085968</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4137076002523123</v>
+      </c>
+      <c r="T84">
+        <v>5.540851992525082</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.2388</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.05058262270778147</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2722833680454162</v>
+      </c>
+      <c r="C85">
+        <v>-285.4246375210031</v>
+      </c>
+      <c r="D85">
+        <v>189.3093624789969</v>
+      </c>
+      <c r="E85">
+        <v>261.134</v>
+      </c>
+      <c r="F85">
+        <v>506.134</v>
+      </c>
+      <c r="G85">
+        <v>31.4</v>
+      </c>
+      <c r="H85">
+        <v>364.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>34.1</v>
+      </c>
+      <c r="K85">
+        <v>28.06</v>
+      </c>
+      <c r="L85">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M85">
+        <v>120.8647992</v>
+      </c>
+      <c r="N85">
+        <v>-114.8247992</v>
+      </c>
+      <c r="O85">
+        <v>-0</v>
+      </c>
+      <c r="P85">
+        <v>-114.8247992</v>
+      </c>
+      <c r="Q85">
+        <v>-86.7647992</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4357609885024484</v>
+      </c>
+      <c r="T85">
+        <v>5.866784462673616</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.2388</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.04997319351853113</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2742833680454162</v>
+      </c>
+      <c r="C86">
+        <v>-293.1304738964577</v>
+      </c>
+      <c r="D86">
+        <v>187.7015261035423</v>
+      </c>
+      <c r="E86">
+        <v>267.232</v>
+      </c>
+      <c r="F86">
+        <v>512.232</v>
+      </c>
+      <c r="G86">
+        <v>31.4</v>
+      </c>
+      <c r="H86">
+        <v>364.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>34.1</v>
+      </c>
+      <c r="K86">
+        <v>28.06</v>
+      </c>
+      <c r="L86">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M86">
+        <v>122.3210016</v>
+      </c>
+      <c r="N86">
+        <v>-116.2810016</v>
+      </c>
+      <c r="O86">
+        <v>-0</v>
+      </c>
+      <c r="P86">
+        <v>-116.2810016</v>
+      </c>
+      <c r="Q86">
+        <v>-88.22100159999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4605710502838511</v>
+      </c>
+      <c r="T86">
+        <v>6.233458491590714</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.2388</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.04937827454807242</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2762833680454162</v>
+      </c>
+      <c r="C87">
+        <v>-300.8092290259507</v>
+      </c>
+      <c r="D87">
+        <v>186.1207709740492</v>
+      </c>
+      <c r="E87">
+        <v>273.3299999999999</v>
+      </c>
+      <c r="F87">
+        <v>518.3299999999999</v>
+      </c>
+      <c r="G87">
+        <v>31.4</v>
+      </c>
+      <c r="H87">
+        <v>364.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>34.1</v>
+      </c>
+      <c r="K87">
+        <v>28.06</v>
+      </c>
+      <c r="L87">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M87">
+        <v>123.777204</v>
+      </c>
+      <c r="N87">
+        <v>-117.737204</v>
+      </c>
+      <c r="O87">
+        <v>-0</v>
+      </c>
+      <c r="P87">
+        <v>-117.737204</v>
+      </c>
+      <c r="Q87">
+        <v>-89.67720399999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4886891203027746</v>
+      </c>
+      <c r="T87">
+        <v>6.649022391030095</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.2388</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.04879735367103621</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2782833680454162</v>
+      </c>
+      <c r="C88">
+        <v>-308.4615814011751</v>
+      </c>
+      <c r="D88">
+        <v>184.5664185988249</v>
+      </c>
+      <c r="E88">
+        <v>279.428</v>
+      </c>
+      <c r="F88">
+        <v>524.428</v>
+      </c>
+      <c r="G88">
+        <v>31.4</v>
+      </c>
+      <c r="H88">
+        <v>364.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>34.1</v>
+      </c>
+      <c r="K88">
+        <v>28.06</v>
+      </c>
+      <c r="L88">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M88">
+        <v>125.2334064</v>
+      </c>
+      <c r="N88">
+        <v>-119.1934064</v>
+      </c>
+      <c r="O88">
+        <v>-0</v>
+      </c>
+      <c r="P88">
+        <v>-119.1934064</v>
+      </c>
+      <c r="Q88">
+        <v>-91.13340640000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5208240574672585</v>
+      </c>
+      <c r="T88">
+        <v>7.123952561817959</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.2388</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.0482299425818381</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2802833680454162</v>
+      </c>
+      <c r="C89">
+        <v>-316.0881870363599</v>
+      </c>
+      <c r="D89">
+        <v>183.0378129636401</v>
+      </c>
+      <c r="E89">
+        <v>285.526</v>
+      </c>
+      <c r="F89">
+        <v>530.526</v>
+      </c>
+      <c r="G89">
+        <v>31.4</v>
+      </c>
+      <c r="H89">
+        <v>364.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>34.1</v>
+      </c>
+      <c r="K89">
+        <v>28.06</v>
+      </c>
+      <c r="L89">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M89">
+        <v>126.6896088</v>
+      </c>
+      <c r="N89">
+        <v>-120.6496088</v>
+      </c>
+      <c r="O89">
+        <v>-0</v>
+      </c>
+      <c r="P89">
+        <v>-120.6496088</v>
+      </c>
+      <c r="Q89">
+        <v>-92.58960880000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5579028311185861</v>
+      </c>
+      <c r="T89">
+        <v>7.671948912727033</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.2388</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.04767557542572498</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2822833680454162</v>
+      </c>
+      <c r="C90">
+        <v>-323.6896803914337</v>
+      </c>
+      <c r="D90">
+        <v>181.5343196085662</v>
+      </c>
+      <c r="E90">
+        <v>291.6239999999999</v>
+      </c>
+      <c r="F90">
+        <v>536.6239999999999</v>
+      </c>
+      <c r="G90">
+        <v>31.4</v>
+      </c>
+      <c r="H90">
+        <v>364.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>34.1</v>
+      </c>
+      <c r="K90">
+        <v>28.06</v>
+      </c>
+      <c r="L90">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M90">
+        <v>128.1458112</v>
+      </c>
+      <c r="N90">
+        <v>-122.1058112</v>
+      </c>
+      <c r="O90">
+        <v>-0</v>
+      </c>
+      <c r="P90">
+        <v>-122.1058112</v>
+      </c>
+      <c r="Q90">
+        <v>-94.0458112</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6011614003784682</v>
+      </c>
+      <c r="T90">
+        <v>8.311277988787619</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.2388</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.04713380752315988</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2842833680454162</v>
+      </c>
+      <c r="C91">
+        <v>-331.2666752500588</v>
+      </c>
+      <c r="D91">
+        <v>180.0553247499412</v>
+      </c>
+      <c r="E91">
+        <v>297.722</v>
+      </c>
+      <c r="F91">
+        <v>542.722</v>
+      </c>
+      <c r="G91">
+        <v>31.4</v>
+      </c>
+      <c r="H91">
+        <v>364.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>34.1</v>
+      </c>
+      <c r="K91">
+        <v>28.06</v>
+      </c>
+      <c r="L91">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M91">
+        <v>129.6020136</v>
+      </c>
+      <c r="N91">
+        <v>-123.5620136</v>
+      </c>
+      <c r="O91">
+        <v>-0</v>
+      </c>
+      <c r="P91">
+        <v>-123.5620136</v>
+      </c>
+      <c r="Q91">
+        <v>-95.5020136</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6522851640492382</v>
+      </c>
+      <c r="T91">
+        <v>9.06684871504104</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.2388</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.04660421418020311</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2862833680454162</v>
+      </c>
+      <c r="C92">
+        <v>-338.8197655550921</v>
+      </c>
+      <c r="D92">
+        <v>178.6002344449078</v>
+      </c>
+      <c r="E92">
+        <v>303.8199999999999</v>
+      </c>
+      <c r="F92">
+        <v>548.8199999999999</v>
+      </c>
+      <c r="G92">
+        <v>31.4</v>
+      </c>
+      <c r="H92">
+        <v>364.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>34.1</v>
+      </c>
+      <c r="K92">
+        <v>28.06</v>
+      </c>
+      <c r="L92">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M92">
+        <v>131.058216</v>
+      </c>
+      <c r="N92">
+        <v>-125.018216</v>
+      </c>
+      <c r="O92">
+        <v>-0</v>
+      </c>
+      <c r="P92">
+        <v>-125.018216</v>
+      </c>
+      <c r="Q92">
+        <v>-96.95821599999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7136336804541621</v>
+      </c>
+      <c r="T92">
+        <v>9.973533586545145</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.2388</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.04608638957820077</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2882833680454162</v>
+      </c>
+      <c r="C93">
+        <v>-346.3495262038613</v>
+      </c>
+      <c r="D93">
+        <v>177.1684737961387</v>
+      </c>
+      <c r="E93">
+        <v>309.918</v>
+      </c>
+      <c r="F93">
+        <v>554.918</v>
+      </c>
+      <c r="G93">
+        <v>31.4</v>
+      </c>
+      <c r="H93">
+        <v>364.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>34.1</v>
+      </c>
+      <c r="K93">
+        <v>28.06</v>
+      </c>
+      <c r="L93">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M93">
+        <v>132.5144184</v>
+      </c>
+      <c r="N93">
+        <v>-126.4744184</v>
+      </c>
+      <c r="O93">
+        <v>-0</v>
+      </c>
+      <c r="P93">
+        <v>-126.4744184</v>
+      </c>
+      <c r="Q93">
+        <v>-98.41441840000002</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7886152005046247</v>
+      </c>
+      <c r="T93">
+        <v>11.08170398505016</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.2388</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.04557994573668211</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2902833680454162</v>
+      </c>
+      <c r="C94">
+        <v>-353.8565138054918</v>
+      </c>
+      <c r="D94">
+        <v>175.7594861945082</v>
+      </c>
+      <c r="E94">
+        <v>316.016</v>
+      </c>
+      <c r="F94">
+        <v>561.016</v>
+      </c>
+      <c r="G94">
+        <v>31.4</v>
+      </c>
+      <c r="H94">
+        <v>364.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>34.1</v>
+      </c>
+      <c r="K94">
+        <v>28.06</v>
+      </c>
+      <c r="L94">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M94">
+        <v>133.9706208</v>
+      </c>
+      <c r="N94">
+        <v>-127.9306208</v>
+      </c>
+      <c r="O94">
+        <v>-0</v>
+      </c>
+      <c r="P94">
+        <v>-127.9306208</v>
+      </c>
+      <c r="Q94">
+        <v>-99.87062080000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.882342100567703</v>
+      </c>
+      <c r="T94">
+        <v>12.46691698318144</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.2388</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.04508451154389215</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2922833680454162</v>
+      </c>
+      <c r="C95">
+        <v>-361.3412674023828</v>
+      </c>
+      <c r="D95">
+        <v>174.3727325976172</v>
+      </c>
+      <c r="E95">
+        <v>322.114</v>
+      </c>
+      <c r="F95">
+        <v>567.114</v>
+      </c>
+      <c r="G95">
+        <v>31.4</v>
+      </c>
+      <c r="H95">
+        <v>364.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>34.1</v>
+      </c>
+      <c r="K95">
+        <v>28.06</v>
+      </c>
+      <c r="L95">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M95">
+        <v>135.4268232</v>
+      </c>
+      <c r="N95">
+        <v>-129.3868232</v>
+      </c>
+      <c r="O95">
+        <v>-0</v>
+      </c>
+      <c r="P95">
+        <v>-129.3868232</v>
+      </c>
+      <c r="Q95">
+        <v>-101.3268232</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.002848114934518</v>
+      </c>
+      <c r="T95">
+        <v>14.24790512363593</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.2388</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.04459973184987176</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2942833680454162</v>
+      </c>
+      <c r="C96">
+        <v>-368.8043091577946</v>
+      </c>
+      <c r="D96">
+        <v>173.0076908422054</v>
+      </c>
+      <c r="E96">
+        <v>328.212</v>
+      </c>
+      <c r="F96">
+        <v>573.212</v>
+      </c>
+      <c r="G96">
+        <v>31.4</v>
+      </c>
+      <c r="H96">
+        <v>364.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>34.1</v>
+      </c>
+      <c r="K96">
+        <v>28.06</v>
+      </c>
+      <c r="L96">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M96">
+        <v>136.8830256</v>
+      </c>
+      <c r="N96">
+        <v>-130.8430256</v>
+      </c>
+      <c r="O96">
+        <v>-0</v>
+      </c>
+      <c r="P96">
+        <v>-130.8430256</v>
+      </c>
+      <c r="Q96">
+        <v>-102.7830256</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.163522800756938</v>
+      </c>
+      <c r="T96">
+        <v>16.62255597757525</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.2388</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.04412526661742633</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2962833680454162</v>
+      </c>
+      <c r="C97">
+        <v>-376.2461450113918</v>
+      </c>
+      <c r="D97">
+        <v>171.6638549886081</v>
+      </c>
+      <c r="E97">
+        <v>334.3099999999999</v>
+      </c>
+      <c r="F97">
+        <v>579.3099999999999</v>
+      </c>
+      <c r="G97">
+        <v>31.4</v>
+      </c>
+      <c r="H97">
+        <v>364.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>34.1</v>
+      </c>
+      <c r="K97">
+        <v>28.06</v>
+      </c>
+      <c r="L97">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M97">
+        <v>138.339228</v>
+      </c>
+      <c r="N97">
+        <v>-132.299228</v>
+      </c>
+      <c r="O97">
+        <v>-0</v>
+      </c>
+      <c r="P97">
+        <v>-132.299228</v>
+      </c>
+      <c r="Q97">
+        <v>-104.239228</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.388467360908326</v>
+      </c>
+      <c r="T97">
+        <v>19.94706717309031</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.2388</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.04366079012671653</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2982833680454162</v>
+      </c>
+      <c r="C98">
+        <v>-383.6672653044701</v>
+      </c>
+      <c r="D98">
+        <v>170.3407346955298</v>
+      </c>
+      <c r="E98">
+        <v>340.4079999999999</v>
+      </c>
+      <c r="F98">
+        <v>585.4079999999999</v>
+      </c>
+      <c r="G98">
+        <v>31.4</v>
+      </c>
+      <c r="H98">
+        <v>364.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>34.1</v>
+      </c>
+      <c r="K98">
+        <v>28.06</v>
+      </c>
+      <c r="L98">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M98">
+        <v>139.7954304</v>
+      </c>
+      <c r="N98">
+        <v>-133.7554304</v>
+      </c>
+      <c r="O98">
+        <v>-0</v>
+      </c>
+      <c r="P98">
+        <v>-133.7554304</v>
+      </c>
+      <c r="Q98">
+        <v>-105.6954304</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.725884201135403</v>
+      </c>
+      <c r="T98">
+        <v>24.93383396636284</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.2388</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.04320599022956328</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3002833680454162</v>
+      </c>
+      <c r="C99">
+        <v>-391.0681453764903</v>
+      </c>
+      <c r="D99">
+        <v>169.0378546235097</v>
+      </c>
+      <c r="E99">
+        <v>346.506</v>
+      </c>
+      <c r="F99">
+        <v>591.506</v>
+      </c>
+      <c r="G99">
+        <v>31.4</v>
+      </c>
+      <c r="H99">
+        <v>364.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>34.1</v>
+      </c>
+      <c r="K99">
+        <v>28.06</v>
+      </c>
+      <c r="L99">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M99">
+        <v>141.2516328</v>
+      </c>
+      <c r="N99">
+        <v>-135.2116328</v>
+      </c>
+      <c r="O99">
+        <v>-0</v>
+      </c>
+      <c r="P99">
+        <v>-135.2116328</v>
+      </c>
+      <c r="Q99">
+        <v>-107.1516328</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.288245601513871</v>
+      </c>
+      <c r="T99">
+        <v>33.24511195515045</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.2388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.04276056764987701</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3022833680454162</v>
+      </c>
+      <c r="C100">
+        <v>-398.449246134443</v>
+      </c>
+      <c r="D100">
+        <v>167.7547538655569</v>
+      </c>
+      <c r="E100">
+        <v>352.6039999999999</v>
+      </c>
+      <c r="F100">
+        <v>597.6039999999999</v>
+      </c>
+      <c r="G100">
+        <v>31.4</v>
+      </c>
+      <c r="H100">
+        <v>364.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>34.1</v>
+      </c>
+      <c r="K100">
+        <v>28.06</v>
+      </c>
+      <c r="L100">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M100">
+        <v>142.7078352</v>
+      </c>
+      <c r="N100">
+        <v>-136.6678352</v>
+      </c>
+      <c r="O100">
+        <v>-0</v>
+      </c>
+      <c r="P100">
+        <v>-136.6678352</v>
+      </c>
+      <c r="Q100">
+        <v>-108.6078352</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.412968402270807</v>
+      </c>
+      <c r="T100">
+        <v>49.86766793272567</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.2388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.04232423532691909</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3042833680454162</v>
+      </c>
+      <c r="C101">
+        <v>-405.8110145964799</v>
+      </c>
+      <c r="D101">
+        <v>166.4909854035201</v>
+      </c>
+      <c r="E101">
+        <v>358.702</v>
+      </c>
+      <c r="F101">
+        <v>603.702</v>
+      </c>
+      <c r="G101">
+        <v>31.4</v>
+      </c>
+      <c r="H101">
+        <v>364.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>34.1</v>
+      </c>
+      <c r="K101">
+        <v>28.06</v>
+      </c>
+      <c r="L101">
+        <v>6.039999999999999</v>
+      </c>
+      <c r="M101">
+        <v>144.1640376</v>
+      </c>
+      <c r="N101">
+        <v>-138.1240376</v>
+      </c>
+      <c r="O101">
+        <v>-0</v>
+      </c>
+      <c r="P101">
+        <v>-138.1240376</v>
+      </c>
+      <c r="Q101">
+        <v>-110.0640376</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.787136804541614</v>
+      </c>
+      <c r="T101">
+        <v>99.73533586545135</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.2388</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.04189671779836435</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_drugs_pharmaceutical.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08990992359842957</v>
+        <v>0.0897188987894335</v>
       </c>
       <c r="C2">
-        <v>640.6192505197266</v>
+        <v>636.1911060262482</v>
       </c>
       <c r="D2">
-        <v>594.5192505197266</v>
+        <v>597.1051060262482</v>
       </c>
       <c r="E2">
-        <v>-292.5</v>
+        <v>-285.486</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.014</v>
       </c>
       <c r="G2">
         <v>46.1</v>
@@ -1439,28 +1439,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3528042</v>
       </c>
       <c r="N2">
-        <v>34.66666666666667</v>
+        <v>34.31386246666667</v>
       </c>
       <c r="O2">
-        <v>8.666666666666668</v>
+        <v>8.578465616666668</v>
       </c>
       <c r="P2">
-        <v>26</v>
+        <v>25.73539685</v>
       </c>
       <c r="Q2">
-        <v>52.50000000000001</v>
+        <v>52.23539685</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08990992359842957</v>
+        <v>0.09024408968629646</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286288</v>
+        <v>0.8908222216697548</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>98.26035706679986</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0897188987894335</v>
+        <v>0.08952787398043743</v>
       </c>
       <c r="C3">
-        <v>636.1911060262482</v>
+        <v>631.7855541040183</v>
       </c>
       <c r="D3">
-        <v>597.1051060262482</v>
+        <v>599.7135541040183</v>
       </c>
       <c r="E3">
-        <v>-285.486</v>
+        <v>-278.472</v>
       </c>
       <c r="F3">
-        <v>7.014</v>
+        <v>14.028</v>
       </c>
       <c r="G3">
         <v>46.1</v>
@@ -1521,28 +1521,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M3">
-        <v>0.3528042</v>
+        <v>0.7056084</v>
       </c>
       <c r="N3">
-        <v>34.31386246666667</v>
+        <v>33.96105826666667</v>
       </c>
       <c r="O3">
-        <v>8.578465616666668</v>
+        <v>8.490264566666667</v>
       </c>
       <c r="P3">
-        <v>25.73539685</v>
+        <v>25.4707937</v>
       </c>
       <c r="Q3">
-        <v>52.23539685</v>
+        <v>51.9707937</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09024408968629646</v>
+        <v>0.09058507549024228</v>
       </c>
       <c r="T3">
-        <v>0.8908222216697548</v>
+        <v>0.8976568251811079</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>98.26035706679986</v>
+        <v>49.13017853339993</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08952787398043743</v>
+        <v>0.08933684917144134</v>
       </c>
       <c r="C4">
-        <v>631.7855541040183</v>
+        <v>627.4028921384719</v>
       </c>
       <c r="D4">
-        <v>599.7135541040183</v>
+        <v>602.3448921384719</v>
       </c>
       <c r="E4">
-        <v>-278.472</v>
+        <v>-271.458</v>
       </c>
       <c r="F4">
-        <v>14.028</v>
+        <v>21.042</v>
       </c>
       <c r="G4">
         <v>46.1</v>
@@ -1603,28 +1603,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M4">
-        <v>0.7056084</v>
+        <v>1.0584126</v>
       </c>
       <c r="N4">
-        <v>33.96105826666667</v>
+        <v>33.60825406666667</v>
       </c>
       <c r="O4">
-        <v>8.490264566666667</v>
+        <v>8.402063516666669</v>
       </c>
       <c r="P4">
-        <v>25.4707937</v>
+        <v>25.20619055000001</v>
       </c>
       <c r="Q4">
-        <v>51.9707937</v>
+        <v>51.70619055000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09058507549024228</v>
+        <v>0.09093309192932097</v>
       </c>
       <c r="T4">
-        <v>0.8976568251811079</v>
+        <v>0.9046323483524887</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>49.13017853339993</v>
+        <v>32.75345235559996</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08933684917144134</v>
+        <v>0.08914582436244528</v>
       </c>
       <c r="C5">
-        <v>627.4028921384719</v>
+        <v>623.0434227573472</v>
       </c>
       <c r="D5">
-        <v>602.3448921384719</v>
+        <v>604.9994227573472</v>
       </c>
       <c r="E5">
-        <v>-271.458</v>
+        <v>-264.444</v>
       </c>
       <c r="F5">
-        <v>21.042</v>
+        <v>28.056</v>
       </c>
       <c r="G5">
         <v>46.1</v>
@@ -1685,28 +1685,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M5">
-        <v>1.0584126</v>
+        <v>1.4112168</v>
       </c>
       <c r="N5">
-        <v>33.60825406666667</v>
+        <v>33.25544986666667</v>
       </c>
       <c r="O5">
-        <v>8.402063516666669</v>
+        <v>8.313862466666668</v>
       </c>
       <c r="P5">
-        <v>25.20619055000001</v>
+        <v>24.9415874</v>
       </c>
       <c r="Q5">
-        <v>51.70619055000001</v>
+        <v>51.4415874</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09093309192932097</v>
+        <v>0.09128835871088051</v>
       </c>
       <c r="T5">
-        <v>0.9046323483524887</v>
+        <v>0.9117531949232734</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.75345235559996</v>
+        <v>24.56508926669996</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08914582436244528</v>
+        <v>0.0889547995534492</v>
       </c>
       <c r="C6">
-        <v>623.0434227573472</v>
+        <v>618.7074539467128</v>
       </c>
       <c r="D6">
-        <v>604.9994227573472</v>
+        <v>607.6774539467128</v>
       </c>
       <c r="E6">
-        <v>-264.444</v>
+        <v>-257.43</v>
       </c>
       <c r="F6">
-        <v>28.056</v>
+        <v>35.07</v>
       </c>
       <c r="G6">
         <v>46.1</v>
@@ -1767,28 +1767,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M6">
-        <v>1.4112168</v>
+        <v>1.764021</v>
       </c>
       <c r="N6">
-        <v>33.25544986666667</v>
+        <v>32.90264566666667</v>
       </c>
       <c r="O6">
-        <v>8.313862466666668</v>
+        <v>8.225661416666668</v>
       </c>
       <c r="P6">
-        <v>24.9415874</v>
+        <v>24.67698425</v>
       </c>
       <c r="Q6">
-        <v>51.4415874</v>
+        <v>51.17698425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09128835871088051</v>
+        <v>0.09165110479310443</v>
       </c>
       <c r="T6">
-        <v>0.9117531949232734</v>
+        <v>0.9190239540534431</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.56508926669996</v>
+        <v>19.65207141335997</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0889547995534492</v>
+        <v>0.08876377474445313</v>
       </c>
       <c r="C7">
-        <v>618.7074539467128</v>
+        <v>614.3952991700862</v>
       </c>
       <c r="D7">
-        <v>607.6774539467128</v>
+        <v>610.3792991700863</v>
       </c>
       <c r="E7">
-        <v>-257.43</v>
+        <v>-250.416</v>
       </c>
       <c r="F7">
-        <v>35.07</v>
+        <v>42.084</v>
       </c>
       <c r="G7">
         <v>46.1</v>
@@ -1849,28 +1849,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M7">
-        <v>1.764021</v>
+        <v>2.1168252</v>
       </c>
       <c r="N7">
-        <v>32.90264566666667</v>
+        <v>32.54984146666667</v>
       </c>
       <c r="O7">
-        <v>8.225661416666668</v>
+        <v>8.137460366666668</v>
       </c>
       <c r="P7">
-        <v>24.67698425</v>
+        <v>24.4123811</v>
       </c>
       <c r="Q7">
-        <v>51.17698425</v>
+        <v>50.9123811</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09165110479310443</v>
+        <v>0.0920215688770778</v>
       </c>
       <c r="T7">
-        <v>0.9190239540534431</v>
+        <v>0.9264494101863823</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.65207141335997</v>
+        <v>16.37672617779997</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08876377474445313</v>
+        <v>0.08857274993545705</v>
       </c>
       <c r="C8">
-        <v>614.3952991700863</v>
+        <v>610.1072774907477</v>
       </c>
       <c r="D8">
-        <v>610.3792991700863</v>
+        <v>613.1052774907477</v>
       </c>
       <c r="E8">
-        <v>-250.416</v>
+        <v>-243.402</v>
       </c>
       <c r="F8">
-        <v>42.084</v>
+        <v>49.09799999999999</v>
       </c>
       <c r="G8">
         <v>46.1</v>
@@ -1931,28 +1931,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M8">
-        <v>2.1168252</v>
+        <v>2.4696294</v>
       </c>
       <c r="N8">
-        <v>32.54984146666667</v>
+        <v>32.19703726666667</v>
       </c>
       <c r="O8">
-        <v>8.137460366666668</v>
+        <v>8.049259316666667</v>
       </c>
       <c r="P8">
-        <v>24.4123811</v>
+        <v>24.14777795</v>
       </c>
       <c r="Q8">
-        <v>50.9123811</v>
+        <v>50.64777795000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0920215688770778</v>
+        <v>0.09239999993059898</v>
       </c>
       <c r="T8">
-        <v>0.9264494101863823</v>
+        <v>0.9340345535479868</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.37672617779998</v>
+        <v>14.0371938666857</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08857274993545705</v>
+        <v>0.088471725126461</v>
       </c>
       <c r="C9">
-        <v>610.1072774907477</v>
+        <v>604.5447970477709</v>
       </c>
       <c r="D9">
-        <v>613.1052774907477</v>
+        <v>614.5567970477708</v>
       </c>
       <c r="E9">
-        <v>-243.402</v>
+        <v>-236.388</v>
       </c>
       <c r="F9">
-        <v>49.09800000000001</v>
+        <v>56.112</v>
       </c>
       <c r="G9">
         <v>46.1</v>
@@ -2013,45 +2013,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M9">
-        <v>2.4696294</v>
+        <v>2.9066016</v>
       </c>
       <c r="N9">
-        <v>32.19703726666667</v>
+        <v>31.76006506666667</v>
       </c>
       <c r="O9">
-        <v>8.049259316666667</v>
+        <v>7.940016266666667</v>
       </c>
       <c r="P9">
-        <v>24.14777795</v>
+        <v>23.8200488</v>
       </c>
       <c r="Q9">
-        <v>50.64777795000001</v>
+        <v>50.32004880000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09239999993059898</v>
+        <v>0.09278665774615324</v>
       </c>
       <c r="T9">
-        <v>0.9340345535479868</v>
+        <v>0.941784591330496</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.03719386668569</v>
+        <v>11.92687249145761</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.088471725126461</v>
+        <v>0.08829195031746491</v>
       </c>
       <c r="C10">
-        <v>604.5447970477709</v>
+        <v>600.1308620008051</v>
       </c>
       <c r="D10">
-        <v>614.5567970477708</v>
+        <v>617.1568620008051</v>
       </c>
       <c r="E10">
-        <v>-236.388</v>
+        <v>-229.374</v>
       </c>
       <c r="F10">
-        <v>56.112</v>
+        <v>63.126</v>
       </c>
       <c r="G10">
         <v>46.1</v>
@@ -2095,28 +2095,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M10">
-        <v>2.9066016</v>
+        <v>3.2699268</v>
       </c>
       <c r="N10">
-        <v>31.76006506666667</v>
+        <v>31.39673986666667</v>
       </c>
       <c r="O10">
-        <v>7.940016266666667</v>
+        <v>7.849184966666668</v>
       </c>
       <c r="P10">
-        <v>23.8200488</v>
+        <v>23.5475549</v>
       </c>
       <c r="Q10">
-        <v>50.32004880000001</v>
+        <v>50.04755490000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09278665774615324</v>
+        <v>0.09318181353567573</v>
       </c>
       <c r="T10">
-        <v>0.941784591330496</v>
+        <v>0.9497049596137194</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.92687249145761</v>
+        <v>10.60166443685121</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08829195031746491</v>
+        <v>0.08823967550846884</v>
       </c>
       <c r="C11">
-        <v>600.1308620008051</v>
+        <v>593.8770411655884</v>
       </c>
       <c r="D11">
-        <v>617.1568620008051</v>
+        <v>617.9170411655883</v>
       </c>
       <c r="E11">
-        <v>-229.374</v>
+        <v>-222.36</v>
       </c>
       <c r="F11">
-        <v>63.126</v>
+        <v>70.13999999999999</v>
       </c>
       <c r="G11">
         <v>46.1</v>
@@ -2177,45 +2177,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M11">
-        <v>3.2699268</v>
+        <v>3.752489999999999</v>
       </c>
       <c r="N11">
-        <v>31.39673986666667</v>
+        <v>30.91417666666667</v>
       </c>
       <c r="O11">
-        <v>7.849184966666668</v>
+        <v>7.728544166666668</v>
       </c>
       <c r="P11">
-        <v>23.5475549</v>
+        <v>23.1856325</v>
       </c>
       <c r="Q11">
-        <v>50.04755490000001</v>
+        <v>49.68563250000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09318181353567573</v>
+        <v>0.09358575056496538</v>
       </c>
       <c r="T11">
-        <v>0.9497049596137194</v>
+        <v>0.9578013360810145</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.60166443685121</v>
+        <v>9.238310206467354</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08823967550846884</v>
+        <v>0.08807265069947276</v>
       </c>
       <c r="C12">
-        <v>593.8770411655884</v>
+        <v>589.3045127569924</v>
       </c>
       <c r="D12">
-        <v>617.9170411655883</v>
+        <v>620.3585127569924</v>
       </c>
       <c r="E12">
-        <v>-222.36</v>
+        <v>-215.346</v>
       </c>
       <c r="F12">
-        <v>70.14</v>
+        <v>77.154</v>
       </c>
       <c r="G12">
         <v>46.1</v>
@@ -2259,28 +2259,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M12">
-        <v>3.75249</v>
+        <v>4.127739</v>
       </c>
       <c r="N12">
-        <v>30.91417666666667</v>
+        <v>30.53892766666667</v>
       </c>
       <c r="O12">
-        <v>7.728544166666667</v>
+        <v>7.634731916666668</v>
       </c>
       <c r="P12">
-        <v>23.1856325</v>
+        <v>22.90419575000001</v>
       </c>
       <c r="Q12">
-        <v>49.68563250000001</v>
+        <v>49.40419575000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09358575056496538</v>
+        <v>0.09399876483086828</v>
       </c>
       <c r="T12">
-        <v>0.9578013360810145</v>
+        <v>0.9660796535925186</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.238310206467352</v>
+        <v>8.398463824061228</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08807265069947276</v>
+        <v>0.08790562589047668</v>
       </c>
       <c r="C13">
-        <v>589.3045127569924</v>
+        <v>584.7513540320241</v>
       </c>
       <c r="D13">
-        <v>620.3585127569924</v>
+        <v>622.8193540320241</v>
       </c>
       <c r="E13">
-        <v>-215.346</v>
+        <v>-208.332</v>
       </c>
       <c r="F13">
-        <v>77.154</v>
+        <v>84.16799999999999</v>
       </c>
       <c r="G13">
         <v>46.1</v>
@@ -2341,28 +2341,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M13">
-        <v>4.127739</v>
+        <v>4.502987999999999</v>
       </c>
       <c r="N13">
-        <v>30.53892766666667</v>
+        <v>30.16367866666667</v>
       </c>
       <c r="O13">
-        <v>7.634731916666668</v>
+        <v>7.540919666666668</v>
       </c>
       <c r="P13">
-        <v>22.90419575000001</v>
+        <v>22.62275900000001</v>
       </c>
       <c r="Q13">
-        <v>49.40419575000001</v>
+        <v>49.12275900000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09399876483086828</v>
+        <v>0.0944211657846326</v>
       </c>
       <c r="T13">
-        <v>0.9660796535925186</v>
+        <v>0.9745461146838295</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.398463824061228</v>
+        <v>7.698591838722794</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08790562589047668</v>
+        <v>0.08781660108148061</v>
       </c>
       <c r="C14">
-        <v>584.7513540320241</v>
+        <v>579.0569841925941</v>
       </c>
       <c r="D14">
-        <v>622.8193540320241</v>
+        <v>624.1389841925941</v>
       </c>
       <c r="E14">
-        <v>-208.332</v>
+        <v>-201.318</v>
       </c>
       <c r="F14">
-        <v>84.16799999999999</v>
+        <v>91.182</v>
       </c>
       <c r="G14">
         <v>46.1</v>
@@ -2423,45 +2423,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M14">
-        <v>4.502987999999999</v>
+        <v>4.9511826</v>
       </c>
       <c r="N14">
-        <v>30.16367866666667</v>
+        <v>29.71548406666667</v>
       </c>
       <c r="O14">
-        <v>7.540919666666668</v>
+        <v>7.428871016666668</v>
       </c>
       <c r="P14">
-        <v>22.62275900000001</v>
+        <v>22.28661305</v>
       </c>
       <c r="Q14">
-        <v>49.12275900000001</v>
+        <v>48.78661305000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0944211657846326</v>
+        <v>0.09485327710515012</v>
       </c>
       <c r="T14">
-        <v>0.9745461146838295</v>
+        <v>0.9832072070645957</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.698591838722794</v>
+        <v>7.001694234962506</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08781660108148061</v>
+        <v>0.08765557627248453</v>
       </c>
       <c r="C15">
-        <v>579.0569841925941</v>
+        <v>574.4441424053573</v>
       </c>
       <c r="D15">
-        <v>624.1389841925941</v>
+        <v>626.5401424053573</v>
       </c>
       <c r="E15">
-        <v>-201.318</v>
+        <v>-194.304</v>
       </c>
       <c r="F15">
-        <v>91.182</v>
+        <v>98.19600000000001</v>
       </c>
       <c r="G15">
         <v>46.1</v>
@@ -2505,28 +2505,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M15">
-        <v>4.9511826</v>
+        <v>5.332042800000001</v>
       </c>
       <c r="N15">
-        <v>29.71548406666667</v>
+        <v>29.33462386666667</v>
       </c>
       <c r="O15">
-        <v>7.428871016666668</v>
+        <v>7.333655966666668</v>
       </c>
       <c r="P15">
-        <v>22.28661305</v>
+        <v>22.0009679</v>
       </c>
       <c r="Q15">
-        <v>48.78661305000001</v>
+        <v>48.50096790000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09485327710515012</v>
+        <v>0.09529543752614481</v>
       </c>
       <c r="T15">
-        <v>0.9832072070645957</v>
+        <v>0.9920697201984032</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.001694234962506</v>
+        <v>6.501573218179469</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08765557627248453</v>
+        <v>0.08760705146348846</v>
       </c>
       <c r="C16">
-        <v>574.4441424053573</v>
+        <v>568.1573580226831</v>
       </c>
       <c r="D16">
-        <v>626.5401424053573</v>
+        <v>627.2673580226831</v>
       </c>
       <c r="E16">
-        <v>-194.304</v>
+        <v>-187.29</v>
       </c>
       <c r="F16">
-        <v>98.19600000000001</v>
+        <v>105.21</v>
       </c>
       <c r="G16">
         <v>46.1</v>
@@ -2587,45 +2587,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M16">
-        <v>5.332042800000001</v>
+        <v>5.818113</v>
       </c>
       <c r="N16">
-        <v>29.33462386666667</v>
+        <v>28.84855366666667</v>
       </c>
       <c r="O16">
-        <v>7.333655966666668</v>
+        <v>7.212138416666668</v>
       </c>
       <c r="P16">
-        <v>22.0009679</v>
+        <v>21.63641525</v>
       </c>
       <c r="Q16">
-        <v>48.50096790000001</v>
+        <v>48.13641525000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09529543752614481</v>
+        <v>0.09574800172175113</v>
       </c>
       <c r="T16">
-        <v>0.9920697201984032</v>
+        <v>1.001140763053006</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.501573218179469</v>
+        <v>5.9584038100784</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08760705146348846</v>
+        <v>0.08745352665449239</v>
       </c>
       <c r="C17">
-        <v>568.1573580226831</v>
+        <v>563.4553135535724</v>
       </c>
       <c r="D17">
-        <v>627.2673580226831</v>
+        <v>629.5793135535724</v>
       </c>
       <c r="E17">
-        <v>-187.29</v>
+        <v>-180.276</v>
       </c>
       <c r="F17">
-        <v>105.21</v>
+        <v>112.224</v>
       </c>
       <c r="G17">
         <v>46.1</v>
@@ -2669,28 +2669,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M17">
-        <v>5.818112999999999</v>
+        <v>6.2059872</v>
       </c>
       <c r="N17">
-        <v>28.84855366666667</v>
+        <v>28.46067946666667</v>
       </c>
       <c r="O17">
-        <v>7.212138416666668</v>
+        <v>7.115169866666668</v>
       </c>
       <c r="P17">
-        <v>21.63641525</v>
+        <v>21.3455096</v>
       </c>
       <c r="Q17">
-        <v>48.13641525000001</v>
+        <v>47.84550960000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09574800172175113</v>
+        <v>0.09621134125534808</v>
       </c>
       <c r="T17">
-        <v>1.001140763053006</v>
+        <v>1.010427783118433</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.9584038100784</v>
+        <v>5.5860035719485</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08745352665449239</v>
+        <v>0.08730000184549631</v>
       </c>
       <c r="C18">
-        <v>563.4553135535724</v>
+        <v>558.7703747478597</v>
       </c>
       <c r="D18">
-        <v>629.5793135535724</v>
+        <v>631.9083747478597</v>
       </c>
       <c r="E18">
-        <v>-180.276</v>
+        <v>-173.262</v>
       </c>
       <c r="F18">
-        <v>112.224</v>
+        <v>119.238</v>
       </c>
       <c r="G18">
         <v>46.1</v>
@@ -2751,28 +2751,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M18">
-        <v>6.2059872</v>
+        <v>6.5938614</v>
       </c>
       <c r="N18">
-        <v>28.46067946666667</v>
+        <v>28.07280526666667</v>
       </c>
       <c r="O18">
-        <v>7.115169866666668</v>
+        <v>7.018201316666667</v>
       </c>
       <c r="P18">
-        <v>21.3455096</v>
+        <v>21.05460395</v>
       </c>
       <c r="Q18">
-        <v>47.84550960000001</v>
+        <v>47.55460395</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09621134125534808</v>
+        <v>0.09668584559698352</v>
       </c>
       <c r="T18">
-        <v>1.010427783118433</v>
+        <v>1.019938586799894</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.5860035719485</v>
+        <v>5.257415126539764</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08730000184549631</v>
+        <v>0.08714647703650023</v>
       </c>
       <c r="C19">
-        <v>558.7703747478597</v>
+        <v>554.1027321521567</v>
       </c>
       <c r="D19">
-        <v>631.9083747478597</v>
+        <v>634.2547321521567</v>
       </c>
       <c r="E19">
-        <v>-173.262</v>
+        <v>-166.248</v>
       </c>
       <c r="F19">
-        <v>119.238</v>
+        <v>126.252</v>
       </c>
       <c r="G19">
         <v>46.1</v>
@@ -2833,28 +2833,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M19">
-        <v>6.5938614</v>
+        <v>6.9817356</v>
       </c>
       <c r="N19">
-        <v>28.07280526666667</v>
+        <v>27.68493106666667</v>
       </c>
       <c r="O19">
-        <v>7.018201316666667</v>
+        <v>6.921232766666668</v>
       </c>
       <c r="P19">
-        <v>21.05460395</v>
+        <v>20.7636983</v>
       </c>
       <c r="Q19">
-        <v>47.55460395</v>
+        <v>47.2636983</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09668584559698352</v>
+        <v>0.09717192321524419</v>
       </c>
       <c r="T19">
-        <v>1.019938586799894</v>
+        <v>1.029681361302854</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.257415126539764</v>
+        <v>4.965336508398666</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08714647703650025</v>
+        <v>0.08699295222750418</v>
       </c>
       <c r="C20">
-        <v>554.1027321521566</v>
+        <v>549.4525791537195</v>
       </c>
       <c r="D20">
-        <v>634.2547321521565</v>
+        <v>636.6185791537195</v>
       </c>
       <c r="E20">
-        <v>-166.248</v>
+        <v>-159.234</v>
       </c>
       <c r="F20">
-        <v>126.252</v>
+        <v>133.266</v>
       </c>
       <c r="G20">
         <v>46.1</v>
@@ -2915,28 +2915,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M20">
-        <v>6.9817356</v>
+        <v>7.3696098</v>
       </c>
       <c r="N20">
-        <v>27.68493106666667</v>
+        <v>27.29705686666667</v>
       </c>
       <c r="O20">
-        <v>6.921232766666668</v>
+        <v>6.824264216666668</v>
       </c>
       <c r="P20">
-        <v>20.7636983</v>
+        <v>20.47279265</v>
       </c>
       <c r="Q20">
-        <v>47.2636983</v>
+        <v>46.97279265</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09717192321524419</v>
+        <v>0.09767000275000515</v>
       </c>
       <c r="T20">
-        <v>1.029681361302854</v>
+        <v>1.039664698139221</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.965336508398666</v>
+        <v>4.704003007956632</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08699295222750418</v>
+        <v>0.08721442741850809</v>
       </c>
       <c r="C21">
-        <v>549.4525791537195</v>
+        <v>539.0340839040352</v>
       </c>
       <c r="D21">
-        <v>636.6185791537195</v>
+        <v>633.2140839040352</v>
       </c>
       <c r="E21">
-        <v>-159.234</v>
+        <v>-152.22</v>
       </c>
       <c r="F21">
-        <v>133.266</v>
+        <v>140.28</v>
       </c>
       <c r="G21">
         <v>46.1</v>
@@ -2997,45 +2997,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M21">
-        <v>7.3696098</v>
+        <v>8.108184000000001</v>
       </c>
       <c r="N21">
-        <v>27.29705686666667</v>
+        <v>26.55848266666667</v>
       </c>
       <c r="O21">
-        <v>6.824264216666668</v>
+        <v>6.639620666666668</v>
       </c>
       <c r="P21">
-        <v>20.47279265</v>
+        <v>19.918862</v>
       </c>
       <c r="Q21">
-        <v>46.97279265</v>
+        <v>46.418862</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09767000275000515</v>
+        <v>0.09818053427313511</v>
       </c>
       <c r="T21">
-        <v>1.039664698139221</v>
+        <v>1.049897618396497</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.704003007956632</v>
+        <v>4.275515536730131</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08721442741850809</v>
+        <v>0.08707965260951202</v>
       </c>
       <c r="C22">
-        <v>539.0340839040352</v>
+        <v>534.0874779303144</v>
       </c>
       <c r="D22">
-        <v>633.2140839040352</v>
+        <v>635.2814779303144</v>
       </c>
       <c r="E22">
-        <v>-152.22</v>
+        <v>-145.206</v>
       </c>
       <c r="F22">
-        <v>140.28</v>
+        <v>147.294</v>
       </c>
       <c r="G22">
         <v>46.1</v>
@@ -3079,28 +3079,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M22">
-        <v>8.108184000000001</v>
+        <v>8.513593200000001</v>
       </c>
       <c r="N22">
-        <v>26.55848266666667</v>
+        <v>26.15307346666667</v>
       </c>
       <c r="O22">
-        <v>6.639620666666668</v>
+        <v>6.538268366666667</v>
       </c>
       <c r="P22">
-        <v>19.918862</v>
+        <v>19.6148051</v>
       </c>
       <c r="Q22">
-        <v>46.418862</v>
+        <v>46.11480510000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09818053427313511</v>
+        <v>0.09870399064495192</v>
       </c>
       <c r="T22">
-        <v>1.049897618396497</v>
+        <v>1.060389599926109</v>
       </c>
       <c r="U22">
         <v>0.0578</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.275515536730131</v>
+        <v>4.071919558790602</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08707965260951202</v>
+        <v>0.08752237780051594</v>
       </c>
       <c r="C23">
-        <v>534.0874779303144</v>
+        <v>520.3323685188926</v>
       </c>
       <c r="D23">
-        <v>635.2814779303144</v>
+        <v>628.5403685188926</v>
       </c>
       <c r="E23">
-        <v>-145.206</v>
+        <v>-138.192</v>
       </c>
       <c r="F23">
-        <v>147.294</v>
+        <v>154.308</v>
       </c>
       <c r="G23">
         <v>46.1</v>
@@ -3161,45 +3161,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M23">
-        <v>8.513593199999999</v>
+        <v>9.459080399999999</v>
       </c>
       <c r="N23">
-        <v>26.15307346666667</v>
+        <v>25.20758626666667</v>
       </c>
       <c r="O23">
-        <v>6.538268366666668</v>
+        <v>6.301896566666668</v>
       </c>
       <c r="P23">
-        <v>19.61480510000001</v>
+        <v>18.9056897</v>
       </c>
       <c r="Q23">
-        <v>46.11480510000001</v>
+        <v>45.40568970000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09870399064495192</v>
+        <v>0.09924086897502044</v>
       </c>
       <c r="T23">
-        <v>1.060389599926109</v>
+        <v>1.071150606623146</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.071919558790603</v>
+        <v>3.664908764985936</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08752237780051594</v>
+        <v>0.08741385299151988</v>
       </c>
       <c r="C24">
-        <v>520.3323685188926</v>
+        <v>514.957539576995</v>
       </c>
       <c r="D24">
-        <v>628.5403685188926</v>
+        <v>630.179539576995</v>
       </c>
       <c r="E24">
-        <v>-138.192</v>
+        <v>-131.178</v>
       </c>
       <c r="F24">
-        <v>154.308</v>
+        <v>161.322</v>
       </c>
       <c r="G24">
         <v>46.1</v>
@@ -3243,28 +3243,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M24">
-        <v>9.459080399999999</v>
+        <v>9.889038600000001</v>
       </c>
       <c r="N24">
-        <v>25.20758626666667</v>
+        <v>24.77762806666667</v>
       </c>
       <c r="O24">
-        <v>6.301896566666668</v>
+        <v>6.194407016666668</v>
       </c>
       <c r="P24">
-        <v>18.9056897</v>
+        <v>18.58322105000001</v>
       </c>
       <c r="Q24">
-        <v>45.40568970000001</v>
+        <v>45.08322105000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09924086897502044</v>
+        <v>0.09979169219677905</v>
       </c>
       <c r="T24">
-        <v>1.071150606623146</v>
+        <v>1.08219111998764</v>
       </c>
       <c r="U24">
         <v>0.0613</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.664908764985936</v>
+        <v>3.505564905638721</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08741385299151988</v>
+        <v>0.08780932818252381</v>
       </c>
       <c r="C25">
-        <v>514.957539576995</v>
+        <v>502.0110387596014</v>
       </c>
       <c r="D25">
-        <v>630.179539576995</v>
+        <v>624.2470387596014</v>
       </c>
       <c r="E25">
-        <v>-131.178</v>
+        <v>-124.164</v>
       </c>
       <c r="F25">
-        <v>161.322</v>
+        <v>168.336</v>
       </c>
       <c r="G25">
         <v>46.1</v>
@@ -3325,45 +3325,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M25">
-        <v>9.889038600000001</v>
+        <v>10.7903376</v>
       </c>
       <c r="N25">
-        <v>24.77762806666667</v>
+        <v>23.87632906666667</v>
       </c>
       <c r="O25">
-        <v>6.194407016666668</v>
+        <v>5.969082266666668</v>
       </c>
       <c r="P25">
-        <v>18.58322105000001</v>
+        <v>17.9072468</v>
       </c>
       <c r="Q25">
-        <v>45.08322105000001</v>
+        <v>44.40724680000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09979169219677905</v>
+        <v>0.1003570107664787</v>
       </c>
       <c r="T25">
-        <v>1.08219111998764</v>
+        <v>1.093522173177515</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.505564905638721</v>
+        <v>3.212750884334394</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08780932818252381</v>
+        <v>0.08772180337352772</v>
       </c>
       <c r="C26">
-        <v>502.0110387596014</v>
+        <v>496.3003486946961</v>
       </c>
       <c r="D26">
-        <v>624.2470387596014</v>
+        <v>625.5503486946961</v>
       </c>
       <c r="E26">
-        <v>-124.164</v>
+        <v>-117.15</v>
       </c>
       <c r="F26">
-        <v>168.336</v>
+        <v>175.35</v>
       </c>
       <c r="G26">
         <v>46.1</v>
@@ -3407,28 +3407,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M26">
-        <v>10.7903376</v>
+        <v>11.239935</v>
       </c>
       <c r="N26">
-        <v>23.87632906666667</v>
+        <v>23.42673166666667</v>
       </c>
       <c r="O26">
-        <v>5.969082266666668</v>
+        <v>5.856682916666667</v>
       </c>
       <c r="P26">
-        <v>17.9072468</v>
+        <v>17.57004875</v>
       </c>
       <c r="Q26">
-        <v>44.40724680000001</v>
+        <v>44.07004875000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1003570107664787</v>
+        <v>0.100937404498037</v>
       </c>
       <c r="T26">
-        <v>1.093522173177515</v>
+        <v>1.105155387785786</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.212750884334395</v>
+        <v>3.084240848961019</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08772180337352772</v>
+        <v>0.08915527856453165</v>
       </c>
       <c r="C27">
-        <v>496.3003486946961</v>
+        <v>468.6034944894578</v>
       </c>
       <c r="D27">
-        <v>625.5503486946961</v>
+        <v>604.8674944894578</v>
       </c>
       <c r="E27">
-        <v>-117.15</v>
+        <v>-110.136</v>
       </c>
       <c r="F27">
-        <v>175.35</v>
+        <v>182.364</v>
       </c>
       <c r="G27">
         <v>46.1</v>
@@ -3489,45 +3489,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M27">
-        <v>11.239935</v>
+        <v>13.1119716</v>
       </c>
       <c r="N27">
-        <v>23.42673166666667</v>
+        <v>21.55469506666667</v>
       </c>
       <c r="O27">
-        <v>5.856682916666667</v>
+        <v>5.388673766666667</v>
       </c>
       <c r="P27">
-        <v>17.57004875</v>
+        <v>16.1660213</v>
       </c>
       <c r="Q27">
-        <v>44.07004875000001</v>
+        <v>42.6660213</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.100937404498037</v>
+        <v>0.1015334845466644</v>
       </c>
       <c r="T27">
-        <v>1.105155387785786</v>
+        <v>1.117103013599686</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.084240848961019</v>
+        <v>2.643894276484451</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08915527856453165</v>
+        <v>0.08912625375553558</v>
       </c>
       <c r="C28">
-        <v>468.6034944894578</v>
+        <v>461.9947029248453</v>
       </c>
       <c r="D28">
-        <v>604.8674944894578</v>
+        <v>605.2727029248454</v>
       </c>
       <c r="E28">
-        <v>-110.136</v>
+        <v>-103.122</v>
       </c>
       <c r="F28">
-        <v>182.364</v>
+        <v>189.378</v>
       </c>
       <c r="G28">
         <v>46.1</v>
@@ -3571,28 +3571,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M28">
-        <v>13.1119716</v>
+        <v>13.6162782</v>
       </c>
       <c r="N28">
-        <v>21.55469506666667</v>
+        <v>21.05038846666667</v>
       </c>
       <c r="O28">
-        <v>5.388673766666667</v>
+        <v>5.262597116666667</v>
       </c>
       <c r="P28">
-        <v>16.1660213</v>
+        <v>15.78779135</v>
       </c>
       <c r="Q28">
-        <v>42.6660213</v>
+        <v>42.28779135000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1015334845466644</v>
+        <v>0.1021458955555282</v>
       </c>
       <c r="T28">
-        <v>1.117103013599686</v>
+        <v>1.129377971627666</v>
       </c>
       <c r="U28">
         <v>0.07190000000000001</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.643894276484451</v>
+        <v>2.545972266244286</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08912625375553558</v>
+        <v>0.08991622894653951</v>
       </c>
       <c r="C29">
-        <v>461.9947029248453</v>
+        <v>444.1422783695201</v>
       </c>
       <c r="D29">
-        <v>605.2727029248454</v>
+        <v>594.4342783695201</v>
       </c>
       <c r="E29">
-        <v>-103.122</v>
+        <v>-96.10799999999998</v>
       </c>
       <c r="F29">
-        <v>189.378</v>
+        <v>196.392</v>
       </c>
       <c r="G29">
         <v>46.1</v>
@@ -3653,45 +3653,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M29">
-        <v>13.6162782</v>
+        <v>14.8865136</v>
       </c>
       <c r="N29">
-        <v>21.05038846666667</v>
+        <v>19.78015306666667</v>
       </c>
       <c r="O29">
-        <v>5.262597116666667</v>
+        <v>4.945038266666668</v>
       </c>
       <c r="P29">
-        <v>15.78779135</v>
+        <v>14.8351148</v>
       </c>
       <c r="Q29">
-        <v>42.28779135000001</v>
+        <v>41.33511480000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1021458955555282</v>
+        <v>0.1027753179813049</v>
       </c>
       <c r="T29">
-        <v>1.129377971627666</v>
+        <v>1.141993900711979</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.545972266244286</v>
+        <v>2.328729721287237</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08991622894653951</v>
+        <v>0.08991645413754341</v>
       </c>
       <c r="C30">
-        <v>444.1422783695201</v>
+        <v>437.1252440990986</v>
       </c>
       <c r="D30">
-        <v>594.4342783695201</v>
+        <v>594.4312440990985</v>
       </c>
       <c r="E30">
-        <v>-96.10799999999998</v>
+        <v>-89.09399999999999</v>
       </c>
       <c r="F30">
-        <v>196.392</v>
+        <v>203.406</v>
       </c>
       <c r="G30">
         <v>46.1</v>
@@ -3735,28 +3735,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M30">
-        <v>14.8865136</v>
+        <v>15.4181748</v>
       </c>
       <c r="N30">
-        <v>19.78015306666667</v>
+        <v>19.24849186666667</v>
       </c>
       <c r="O30">
-        <v>4.945038266666668</v>
+        <v>4.812122966666667</v>
       </c>
       <c r="P30">
-        <v>14.8351148</v>
+        <v>14.4363689</v>
       </c>
       <c r="Q30">
-        <v>41.33511480000001</v>
+        <v>40.93636890000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1027753179813049</v>
+        <v>0.1034224706162583</v>
       </c>
       <c r="T30">
-        <v>1.141993900711979</v>
+        <v>1.154965208080357</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.328729721287237</v>
+        <v>2.248428696415264</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08991645413754341</v>
+        <v>0.08991667932854734</v>
       </c>
       <c r="C31">
-        <v>437.1252440990986</v>
+        <v>430.108209859653</v>
       </c>
       <c r="D31">
-        <v>594.4312440990985</v>
+        <v>594.428209859653</v>
       </c>
       <c r="E31">
-        <v>-89.09400000000002</v>
+        <v>-82.08000000000001</v>
       </c>
       <c r="F31">
-        <v>203.406</v>
+        <v>210.42</v>
       </c>
       <c r="G31">
         <v>46.1</v>
@@ -3817,28 +3817,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M31">
-        <v>15.4181748</v>
+        <v>15.949836</v>
       </c>
       <c r="N31">
-        <v>19.24849186666667</v>
+        <v>18.71683066666667</v>
       </c>
       <c r="O31">
-        <v>4.812122966666668</v>
+        <v>4.679207666666668</v>
       </c>
       <c r="P31">
-        <v>14.43636890000001</v>
+        <v>14.037623</v>
       </c>
       <c r="Q31">
-        <v>40.93636890000001</v>
+        <v>40.53762300000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1034224706162583</v>
+        <v>0.1040881133264962</v>
       </c>
       <c r="T31">
-        <v>1.154965208080357</v>
+        <v>1.168307124230688</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.248428696415264</v>
+        <v>2.173481073201422</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08991667932854734</v>
+        <v>0.08991690451955127</v>
       </c>
       <c r="C32">
-        <v>430.108209859653</v>
+        <v>423.0911756511836</v>
       </c>
       <c r="D32">
-        <v>594.428209859653</v>
+        <v>594.4251756511835</v>
       </c>
       <c r="E32">
-        <v>-82.08000000000001</v>
+        <v>-75.066</v>
       </c>
       <c r="F32">
-        <v>210.42</v>
+        <v>217.434</v>
       </c>
       <c r="G32">
         <v>46.1</v>
@@ -3899,28 +3899,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M32">
-        <v>15.949836</v>
+        <v>16.4814972</v>
       </c>
       <c r="N32">
-        <v>18.71683066666667</v>
+        <v>18.18516946666667</v>
       </c>
       <c r="O32">
-        <v>4.679207666666668</v>
+        <v>4.546292366666668</v>
       </c>
       <c r="P32">
-        <v>14.037623</v>
+        <v>13.6388771</v>
       </c>
       <c r="Q32">
-        <v>40.53762300000001</v>
+        <v>40.13887710000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1040881133264962</v>
+        <v>0.1047730500283352</v>
       </c>
       <c r="T32">
-        <v>1.168307124230688</v>
+        <v>1.182035762588275</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.173481073201422</v>
+        <v>2.103368780517505</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08991690451955127</v>
+        <v>0.08991712971055521</v>
       </c>
       <c r="C33">
-        <v>423.0911756511836</v>
+        <v>416.0741414736895</v>
       </c>
       <c r="D33">
-        <v>594.4251756511835</v>
+        <v>594.4221414736894</v>
       </c>
       <c r="E33">
-        <v>-75.066</v>
+        <v>-68.05199999999999</v>
       </c>
       <c r="F33">
-        <v>217.434</v>
+        <v>224.448</v>
       </c>
       <c r="G33">
         <v>46.1</v>
@@ -3981,28 +3981,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M33">
-        <v>16.4814972</v>
+        <v>17.0131584</v>
       </c>
       <c r="N33">
-        <v>18.18516946666667</v>
+        <v>17.65350826666667</v>
       </c>
       <c r="O33">
-        <v>4.546292366666668</v>
+        <v>4.413377066666667</v>
       </c>
       <c r="P33">
-        <v>13.6388771</v>
+        <v>13.2401312</v>
       </c>
       <c r="Q33">
-        <v>40.13887710000001</v>
+        <v>39.74013120000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1047730500283352</v>
+        <v>0.1054781319272871</v>
       </c>
       <c r="T33">
-        <v>1.182035762588275</v>
+        <v>1.196168184426968</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.103368780517505</v>
+        <v>2.037638506126333</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08991712971055521</v>
+        <v>0.09343185490155913</v>
       </c>
       <c r="C34">
-        <v>416.0741414736895</v>
+        <v>365.1980983295397</v>
       </c>
       <c r="D34">
-        <v>594.4221414736894</v>
+        <v>550.5600983295396</v>
       </c>
       <c r="E34">
-        <v>-68.05199999999999</v>
+        <v>-61.03799999999998</v>
       </c>
       <c r="F34">
-        <v>224.448</v>
+        <v>231.462</v>
       </c>
       <c r="G34">
         <v>46.1</v>
@@ -4063,45 +4063,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M34">
-        <v>17.0131584</v>
+        <v>20.83158</v>
       </c>
       <c r="N34">
-        <v>17.65350826666667</v>
+        <v>13.83508666666667</v>
       </c>
       <c r="O34">
-        <v>4.413377066666667</v>
+        <v>3.458771666666667</v>
       </c>
       <c r="P34">
-        <v>13.2401312</v>
+        <v>10.376315</v>
       </c>
       <c r="Q34">
-        <v>39.74013120000001</v>
+        <v>36.87631500000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1054781319272871</v>
+        <v>0.1062042610471032</v>
       </c>
       <c r="T34">
-        <v>1.196168184426968</v>
+        <v>1.21072246960413</v>
       </c>
       <c r="U34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.037638506126333</v>
+        <v>1.664140054026947</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09343185490155913</v>
+        <v>0.09353858009256305</v>
       </c>
       <c r="C35">
-        <v>365.1980983295397</v>
+        <v>356.9532567012501</v>
       </c>
       <c r="D35">
-        <v>550.5600983295396</v>
+        <v>549.3292567012501</v>
       </c>
       <c r="E35">
-        <v>-61.03799999999998</v>
+        <v>-54.024</v>
       </c>
       <c r="F35">
-        <v>231.462</v>
+        <v>238.476</v>
       </c>
       <c r="G35">
         <v>46.1</v>
@@ -4145,28 +4145,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M35">
-        <v>20.83158</v>
+        <v>21.46284</v>
       </c>
       <c r="N35">
-        <v>13.83508666666667</v>
+        <v>13.20382666666667</v>
       </c>
       <c r="O35">
-        <v>3.458771666666667</v>
+        <v>3.300956666666668</v>
       </c>
       <c r="P35">
-        <v>10.376315</v>
+        <v>9.902870000000004</v>
       </c>
       <c r="Q35">
-        <v>36.87631500000001</v>
+        <v>36.40287000000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1062042610471032</v>
+        <v>0.106952394079641</v>
       </c>
       <c r="T35">
-        <v>1.21072246960413</v>
+        <v>1.225717793726054</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.664140054026947</v>
+        <v>1.615194758320272</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09353858009256305</v>
+        <v>0.09364530528356699</v>
       </c>
       <c r="C36">
-        <v>356.9532567012501</v>
+        <v>348.7139061783927</v>
       </c>
       <c r="D36">
-        <v>549.3292567012501</v>
+        <v>548.1039061783927</v>
       </c>
       <c r="E36">
-        <v>-54.024</v>
+        <v>-47.00999999999999</v>
       </c>
       <c r="F36">
-        <v>238.476</v>
+        <v>245.49</v>
       </c>
       <c r="G36">
         <v>46.1</v>
@@ -4227,28 +4227,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M36">
-        <v>21.46284</v>
+        <v>22.0941</v>
       </c>
       <c r="N36">
-        <v>13.20382666666667</v>
+        <v>12.57256666666667</v>
       </c>
       <c r="O36">
-        <v>3.300956666666668</v>
+        <v>3.143141666666668</v>
       </c>
       <c r="P36">
-        <v>9.902870000000004</v>
+        <v>9.429425000000002</v>
       </c>
       <c r="Q36">
-        <v>36.40287000000001</v>
+        <v>35.92942500000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.106952394079641</v>
+        <v>0.1077235465901031</v>
       </c>
       <c r="T36">
-        <v>1.225717793726054</v>
+        <v>1.241174512436344</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.615194758320272</v>
+        <v>1.569046336653979</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09364530528356699</v>
+        <v>0.09375203047457091</v>
       </c>
       <c r="C37">
-        <v>348.7139061783927</v>
+        <v>340.4800100968721</v>
       </c>
       <c r="D37">
-        <v>548.1039061783927</v>
+        <v>546.8840100968721</v>
       </c>
       <c r="E37">
-        <v>-47.00999999999999</v>
+        <v>-39.99599999999998</v>
       </c>
       <c r="F37">
-        <v>245.49</v>
+        <v>252.504</v>
       </c>
       <c r="G37">
         <v>46.1</v>
@@ -4309,28 +4309,28 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M37">
-        <v>22.0941</v>
+        <v>22.72536</v>
       </c>
       <c r="N37">
-        <v>12.57256666666667</v>
+        <v>11.94130666666667</v>
       </c>
       <c r="O37">
-        <v>3.143141666666668</v>
+        <v>2.985326666666667</v>
       </c>
       <c r="P37">
-        <v>9.429425000000002</v>
+        <v>8.955980000000002</v>
       </c>
       <c r="Q37">
-        <v>35.92942500000001</v>
+        <v>35.45598</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1077235465901031</v>
+        <v>0.1085187976165171</v>
       </c>
       <c r="T37">
-        <v>1.241174512436344</v>
+        <v>1.257114253606332</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.569046336653979</v>
+        <v>1.525461716191368</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09375203047457092</v>
+        <v>0.111210926217691</v>
       </c>
       <c r="C38">
-        <v>340.4800100968719</v>
+        <v>187.4966519489001</v>
       </c>
       <c r="D38">
-        <v>546.8840100968719</v>
+        <v>400.9146519489</v>
       </c>
       <c r="E38">
-        <v>-39.99600000000001</v>
+        <v>-32.98200000000003</v>
       </c>
       <c r="F38">
-        <v>252.504</v>
+        <v>259.518</v>
       </c>
       <c r="G38">
         <v>46.1</v>
@@ -4391,45 +4391,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M38">
-        <v>22.72536</v>
+        <v>38.0972424</v>
       </c>
       <c r="N38">
-        <v>11.94130666666667</v>
+        <v>-3.430575733333328</v>
       </c>
       <c r="O38">
-        <v>2.985326666666668</v>
+        <v>-0.8576439333333319</v>
       </c>
       <c r="P38">
-        <v>8.955980000000004</v>
+        <v>-2.572931799999996</v>
       </c>
       <c r="Q38">
-        <v>35.45598000000001</v>
+        <v>23.92706820000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1085187976165171</v>
+        <v>0.1099224859029223</v>
       </c>
       <c r="T38">
-        <v>1.257114253606332</v>
+        <v>1.285249304333062</v>
       </c>
       <c r="U38">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.25</v>
+        <v>0.227488031172216</v>
       </c>
       <c r="W38">
-        <v>0.0675</v>
+        <v>0.1134047570239187</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.525461716191368</v>
+        <v>0.9099521246888639</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.111210926217691</v>
+        <v>0.1122209262176909</v>
       </c>
       <c r="C39">
-        <v>187.4966519489001</v>
+        <v>174.3863232536141</v>
       </c>
       <c r="D39">
-        <v>400.9146519489</v>
+        <v>394.818323253614</v>
       </c>
       <c r="E39">
-        <v>-32.98200000000003</v>
+        <v>-25.96800000000002</v>
       </c>
       <c r="F39">
-        <v>259.518</v>
+        <v>266.532</v>
       </c>
       <c r="G39">
         <v>46.1</v>
@@ -4473,37 +4473,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M39">
-        <v>38.0972424</v>
+        <v>39.1268976</v>
       </c>
       <c r="N39">
-        <v>-3.430575733333328</v>
+        <v>-4.460230933333328</v>
       </c>
       <c r="O39">
-        <v>-0.8576439333333319</v>
+        <v>-1.115057733333332</v>
       </c>
       <c r="P39">
-        <v>-2.572931799999996</v>
+        <v>-3.345173199999996</v>
       </c>
       <c r="Q39">
-        <v>23.92706820000001</v>
+        <v>23.15482680000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1099224859029223</v>
+        <v>0.1109567195465178</v>
       </c>
       <c r="T39">
-        <v>1.285249304333062</v>
+        <v>1.305979131822305</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.227488031172216</v>
+        <v>0.221501504036105</v>
       </c>
       <c r="W39">
-        <v>0.1134047570239187</v>
+        <v>0.1142835792074998</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.9099521246888639</v>
+        <v>0.8860060161444201</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1122209262176909</v>
+        <v>0.113230926217691</v>
       </c>
       <c r="C40">
-        <v>174.3863232536141</v>
+        <v>161.4586197224065</v>
       </c>
       <c r="D40">
-        <v>394.818323253614</v>
+        <v>388.9046197224064</v>
       </c>
       <c r="E40">
-        <v>-25.96800000000002</v>
+        <v>-18.95400000000001</v>
       </c>
       <c r="F40">
-        <v>266.532</v>
+        <v>273.546</v>
       </c>
       <c r="G40">
         <v>46.1</v>
@@ -4555,37 +4555,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M40">
-        <v>39.1268976</v>
+        <v>40.1565528</v>
       </c>
       <c r="N40">
-        <v>-4.460230933333328</v>
+        <v>-5.489886133333329</v>
       </c>
       <c r="O40">
-        <v>-1.115057733333332</v>
+        <v>-1.372471533333332</v>
       </c>
       <c r="P40">
-        <v>-3.345173199999996</v>
+        <v>-4.117414599999996</v>
       </c>
       <c r="Q40">
-        <v>23.15482680000001</v>
+        <v>22.38258540000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1109567195465178</v>
+        <v>0.1120248624899033</v>
       </c>
       <c r="T40">
-        <v>1.305979131822305</v>
+        <v>1.327388625786605</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.221501504036105</v>
+        <v>0.2158219782915895</v>
       </c>
       <c r="W40">
-        <v>0.1142835792074998</v>
+        <v>0.1151173335867947</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8860060161444201</v>
+        <v>0.863287913166358</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.113230926217691</v>
+        <v>0.114240926217691</v>
       </c>
       <c r="C41">
-        <v>161.4586197224065</v>
+        <v>148.7054562185364</v>
       </c>
       <c r="D41">
-        <v>388.9046197224064</v>
+        <v>383.1654562185364</v>
       </c>
       <c r="E41">
-        <v>-18.95400000000001</v>
+        <v>-11.94</v>
       </c>
       <c r="F41">
-        <v>273.546</v>
+        <v>280.56</v>
       </c>
       <c r="G41">
         <v>46.1</v>
@@ -4637,37 +4637,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M41">
-        <v>40.1565528</v>
+        <v>41.18620800000001</v>
       </c>
       <c r="N41">
-        <v>-5.489886133333329</v>
+        <v>-6.519541333333336</v>
       </c>
       <c r="O41">
-        <v>-1.372471533333332</v>
+        <v>-1.629885333333334</v>
       </c>
       <c r="P41">
-        <v>-4.117414599999996</v>
+        <v>-4.889656000000002</v>
       </c>
       <c r="Q41">
-        <v>22.38258540000001</v>
+        <v>21.610344</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1120248624899033</v>
+        <v>0.1131286101980684</v>
       </c>
       <c r="T41">
-        <v>1.327388625786605</v>
+        <v>1.349511769549716</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2158219782915895</v>
+        <v>0.2104264288342997</v>
       </c>
       <c r="W41">
-        <v>0.1151173335867947</v>
+        <v>0.1159094002471248</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.863287913166358</v>
+        <v>0.841705715337199</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.114240926217691</v>
+        <v>0.115250926217691</v>
       </c>
       <c r="C42">
-        <v>148.7054562185364</v>
+        <v>136.1192179222798</v>
       </c>
       <c r="D42">
-        <v>383.1654562185364</v>
+        <v>377.5932179222798</v>
       </c>
       <c r="E42">
-        <v>-11.94</v>
+        <v>-4.925999999999988</v>
       </c>
       <c r="F42">
-        <v>280.56</v>
+        <v>287.574</v>
       </c>
       <c r="G42">
         <v>46.1</v>
@@ -4719,37 +4719,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M42">
-        <v>41.18620800000001</v>
+        <v>42.21586320000001</v>
       </c>
       <c r="N42">
-        <v>-6.519541333333336</v>
+        <v>-7.549196533333337</v>
       </c>
       <c r="O42">
-        <v>-1.629885333333334</v>
+        <v>-1.887299133333334</v>
       </c>
       <c r="P42">
-        <v>-4.889656000000002</v>
+        <v>-5.661897400000003</v>
       </c>
       <c r="Q42">
-        <v>21.610344</v>
+        <v>20.8381026</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1131286101980684</v>
+        <v>0.1142697730827814</v>
       </c>
       <c r="T42">
-        <v>1.349511769549716</v>
+        <v>1.372384850389541</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2104264288342997</v>
+        <v>0.2052940769115119</v>
       </c>
       <c r="W42">
-        <v>0.1159094002471248</v>
+        <v>0.1166628295093901</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.841705715337199</v>
+        <v>0.8211763076460477</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.115250926217691</v>
+        <v>0.116260926217691</v>
       </c>
       <c r="C43">
-        <v>136.1192179222798</v>
+        <v>123.6927266228714</v>
       </c>
       <c r="D43">
-        <v>377.5932179222798</v>
+        <v>372.1807266228714</v>
       </c>
       <c r="E43">
-        <v>-4.925999999999988</v>
+        <v>2.088000000000022</v>
       </c>
       <c r="F43">
-        <v>287.574</v>
+        <v>294.588</v>
       </c>
       <c r="G43">
         <v>46.1</v>
@@ -4801,37 +4801,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M43">
-        <v>42.21586320000001</v>
+        <v>43.24551840000001</v>
       </c>
       <c r="N43">
-        <v>-7.549196533333337</v>
+        <v>-8.578851733333337</v>
       </c>
       <c r="O43">
-        <v>-1.887299133333334</v>
+        <v>-2.144712933333334</v>
       </c>
       <c r="P43">
-        <v>-5.661897400000003</v>
+        <v>-6.434138800000003</v>
       </c>
       <c r="Q43">
-        <v>20.8381026</v>
+        <v>20.0658612</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1142697730827814</v>
+        <v>0.1154502864117949</v>
       </c>
       <c r="T43">
-        <v>1.372384850389541</v>
+        <v>1.396046658154878</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2052940769115119</v>
+        <v>0.2004061226993331</v>
       </c>
       <c r="W43">
-        <v>0.1166628295093901</v>
+        <v>0.1173803811877379</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8211763076460477</v>
+        <v>0.8016244907973323</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.116260926217691</v>
+        <v>0.1414893769343134</v>
       </c>
       <c r="C44">
-        <v>123.6927266228714</v>
+        <v>18.55348618236417</v>
       </c>
       <c r="D44">
-        <v>372.1807266228714</v>
+        <v>274.0554861823641</v>
       </c>
       <c r="E44">
-        <v>2.087999999999965</v>
+        <v>9.101999999999975</v>
       </c>
       <c r="F44">
-        <v>294.588</v>
+        <v>301.602</v>
       </c>
       <c r="G44">
         <v>46.1</v>
@@ -4883,45 +4883,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M44">
-        <v>43.2455184</v>
+        <v>60.5616816</v>
       </c>
       <c r="N44">
-        <v>-8.57885173333333</v>
+        <v>-25.89501493333333</v>
       </c>
       <c r="O44">
-        <v>-2.144712933333333</v>
+        <v>-6.473753733333332</v>
       </c>
       <c r="P44">
-        <v>-6.434138799999998</v>
+        <v>-19.4212612</v>
       </c>
       <c r="Q44">
-        <v>20.06586120000001</v>
+        <v>7.078738800000007</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1154502864117949</v>
+        <v>0.1184238891850236</v>
       </c>
       <c r="T44">
-        <v>1.396046658154878</v>
+        <v>1.45564854104883</v>
       </c>
       <c r="U44">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.2004061226993331</v>
+        <v>0.1431047889969203</v>
       </c>
       <c r="W44">
-        <v>0.1173803811877379</v>
+        <v>0.1720645583694184</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.8016244907973324</v>
+        <v>0.572419155987681</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1414893769343134</v>
+        <v>0.1430393769343134</v>
       </c>
       <c r="C45">
-        <v>18.55348618236417</v>
+        <v>7.171029524423943</v>
       </c>
       <c r="D45">
-        <v>274.0554861823641</v>
+        <v>269.6870295244239</v>
       </c>
       <c r="E45">
-        <v>9.101999999999975</v>
+        <v>16.11599999999999</v>
       </c>
       <c r="F45">
-        <v>301.602</v>
+        <v>308.616</v>
       </c>
       <c r="G45">
         <v>46.1</v>
@@ -4965,37 +4965,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M45">
-        <v>60.5616816</v>
+        <v>61.9700928</v>
       </c>
       <c r="N45">
-        <v>-25.89501493333333</v>
+        <v>-27.30342613333332</v>
       </c>
       <c r="O45">
-        <v>-6.473753733333332</v>
+        <v>-6.825856533333331</v>
       </c>
       <c r="P45">
-        <v>-19.4212612</v>
+        <v>-20.4775696</v>
       </c>
       <c r="Q45">
-        <v>7.078738800000007</v>
+        <v>6.022430400000008</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1184238891850236</v>
+        <v>0.1197207443490419</v>
       </c>
       <c r="T45">
-        <v>1.45564854104883</v>
+        <v>1.48164226499613</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1431047889969203</v>
+        <v>0.1398524074288084</v>
       </c>
       <c r="W45">
-        <v>0.1720645583694184</v>
+        <v>0.1727176365882953</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.572419155987681</v>
+        <v>0.5594096297152338</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1430393769343134</v>
+        <v>0.1445893769343134</v>
       </c>
       <c r="C46">
-        <v>7.171029524423943</v>
+        <v>-4.074345434452596</v>
       </c>
       <c r="D46">
-        <v>269.6870295244239</v>
+        <v>265.4556545655474</v>
       </c>
       <c r="E46">
-        <v>16.11599999999999</v>
+        <v>23.13</v>
       </c>
       <c r="F46">
-        <v>308.616</v>
+        <v>315.63</v>
       </c>
       <c r="G46">
         <v>46.1</v>
@@ -5047,37 +5047,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M46">
-        <v>61.9700928</v>
+        <v>63.378504</v>
       </c>
       <c r="N46">
-        <v>-27.30342613333332</v>
+        <v>-28.71183733333333</v>
       </c>
       <c r="O46">
-        <v>-6.825856533333331</v>
+        <v>-7.177959333333332</v>
       </c>
       <c r="P46">
-        <v>-20.4775696</v>
+        <v>-21.53387799999999</v>
       </c>
       <c r="Q46">
-        <v>6.022430400000008</v>
+        <v>4.966122000000009</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1197207443490419</v>
+        <v>0.1210647578826608</v>
       </c>
       <c r="T46">
-        <v>1.48164226499613</v>
+        <v>1.508581215268787</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1398524074288084</v>
+        <v>0.1367445761526127</v>
       </c>
       <c r="W46">
-        <v>0.1727176365882953</v>
+        <v>0.1733416891085554</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5594096297152338</v>
+        <v>0.5469783046104508</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1445893769343134</v>
+        <v>0.1461393769343134</v>
       </c>
       <c r="C47">
-        <v>-4.074345434452596</v>
+        <v>-15.18899143353974</v>
       </c>
       <c r="D47">
-        <v>265.4556545655474</v>
+        <v>261.3550085664602</v>
       </c>
       <c r="E47">
-        <v>23.13</v>
+        <v>30.14400000000001</v>
       </c>
       <c r="F47">
-        <v>315.63</v>
+        <v>322.644</v>
       </c>
       <c r="G47">
         <v>46.1</v>
@@ -5129,37 +5129,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M47">
-        <v>63.378504</v>
+        <v>64.78691520000001</v>
       </c>
       <c r="N47">
-        <v>-28.71183733333333</v>
+        <v>-30.12024853333334</v>
       </c>
       <c r="O47">
-        <v>-7.177959333333332</v>
+        <v>-7.530062133333335</v>
       </c>
       <c r="P47">
-        <v>-21.53387799999999</v>
+        <v>-22.5901864</v>
       </c>
       <c r="Q47">
-        <v>4.966122000000009</v>
+        <v>3.9098136</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1210647578826608</v>
+        <v>0.1224585496953027</v>
       </c>
       <c r="T47">
-        <v>1.508581215268787</v>
+        <v>1.536517904440432</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1367445761526127</v>
+        <v>0.133771867975382</v>
       </c>
       <c r="W47">
-        <v>0.1733416891085554</v>
+        <v>0.1739386089105433</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5469783046104508</v>
+        <v>0.5350874719015278</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1461393769343134</v>
+        <v>0.1476893769343134</v>
       </c>
       <c r="C48">
-        <v>-15.18899143353974</v>
+        <v>-26.17887464596902</v>
       </c>
       <c r="D48">
-        <v>261.3550085664602</v>
+        <v>257.379125354031</v>
       </c>
       <c r="E48">
-        <v>30.14400000000001</v>
+        <v>37.15800000000002</v>
       </c>
       <c r="F48">
-        <v>322.644</v>
+        <v>329.658</v>
       </c>
       <c r="G48">
         <v>46.1</v>
@@ -5211,37 +5211,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M48">
-        <v>64.78691520000001</v>
+        <v>66.1953264</v>
       </c>
       <c r="N48">
-        <v>-30.12024853333334</v>
+        <v>-31.52865973333333</v>
       </c>
       <c r="O48">
-        <v>-7.530062133333335</v>
+        <v>-7.882164933333332</v>
       </c>
       <c r="P48">
-        <v>-22.5901864</v>
+        <v>-23.6464948</v>
       </c>
       <c r="Q48">
-        <v>3.9098136</v>
+        <v>2.853505200000008</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1224585496953027</v>
+        <v>0.1239049374254027</v>
       </c>
       <c r="T48">
-        <v>1.536517904440432</v>
+        <v>1.565508808297798</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.133771867975382</v>
+        <v>0.130925658018459</v>
       </c>
       <c r="W48">
-        <v>0.1739386089105433</v>
+        <v>0.1745101278698934</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5350874719015278</v>
+        <v>0.5237026320738358</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1476893769343134</v>
+        <v>0.1492393769343134</v>
       </c>
       <c r="C49">
-        <v>-26.17887464596902</v>
+        <v>-37.04960364146643</v>
       </c>
       <c r="D49">
-        <v>257.379125354031</v>
+        <v>253.5223963585336</v>
       </c>
       <c r="E49">
-        <v>37.15800000000002</v>
+        <v>44.17200000000003</v>
       </c>
       <c r="F49">
-        <v>329.658</v>
+        <v>336.672</v>
       </c>
       <c r="G49">
         <v>46.1</v>
@@ -5293,37 +5293,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M49">
-        <v>66.1953264</v>
+        <v>67.6037376</v>
       </c>
       <c r="N49">
-        <v>-31.52865973333333</v>
+        <v>-32.93707093333333</v>
       </c>
       <c r="O49">
-        <v>-7.882164933333332</v>
+        <v>-8.234267733333333</v>
       </c>
       <c r="P49">
-        <v>-23.6464948</v>
+        <v>-24.7028032</v>
       </c>
       <c r="Q49">
-        <v>2.853505200000008</v>
+        <v>1.797196800000005</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1239049374254027</v>
+        <v>0.1254069554528143</v>
       </c>
       <c r="T49">
-        <v>1.565508808297798</v>
+        <v>1.59561474691891</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.130925658018459</v>
+        <v>0.1281980401430744</v>
       </c>
       <c r="W49">
-        <v>0.1745101278698934</v>
+        <v>0.1750578335392707</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5237026320738358</v>
+        <v>0.5127921605722976</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1492393769343134</v>
+        <v>0.1507893769343134</v>
       </c>
       <c r="C50">
-        <v>-37.04960364146632</v>
+        <v>-47.80645578356058</v>
       </c>
       <c r="D50">
-        <v>253.5223963585337</v>
+        <v>249.7795442164394</v>
       </c>
       <c r="E50">
-        <v>44.17199999999997</v>
+        <v>51.18599999999998</v>
       </c>
       <c r="F50">
-        <v>336.672</v>
+        <v>343.686</v>
       </c>
       <c r="G50">
         <v>46.1</v>
@@ -5375,37 +5375,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M50">
-        <v>67.6037376</v>
+        <v>69.01214879999999</v>
       </c>
       <c r="N50">
-        <v>-32.93707093333333</v>
+        <v>-34.34548213333332</v>
       </c>
       <c r="O50">
-        <v>-8.234267733333333</v>
+        <v>-8.58637053333333</v>
       </c>
       <c r="P50">
-        <v>-24.7028032</v>
+        <v>-25.75911159999999</v>
       </c>
       <c r="Q50">
-        <v>1.797196800000005</v>
+        <v>0.7408884000000135</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1254069554528143</v>
+        <v>0.1269678761479676</v>
       </c>
       <c r="T50">
-        <v>1.59561474691891</v>
+        <v>1.626901310583986</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1281980401430744</v>
+        <v>0.1255817536095423</v>
       </c>
       <c r="W50">
-        <v>0.1750578335392707</v>
+        <v>0.1755831838752039</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5127921605722976</v>
+        <v>0.5023270144381691</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1507893769343134</v>
+        <v>0.1702422638584178</v>
       </c>
       <c r="C51">
-        <v>-47.80645578356058</v>
+        <v>-93.86613913053748</v>
       </c>
       <c r="D51">
-        <v>249.7795442164394</v>
+        <v>210.7338608694625</v>
       </c>
       <c r="E51">
-        <v>51.18599999999998</v>
+        <v>58.19999999999999</v>
       </c>
       <c r="F51">
-        <v>343.686</v>
+        <v>350.7</v>
       </c>
       <c r="G51">
         <v>46.1</v>
@@ -5457,45 +5457,45 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M51">
-        <v>69.01214879999999</v>
+        <v>82.69506</v>
       </c>
       <c r="N51">
-        <v>-34.34548213333332</v>
+        <v>-48.02839333333333</v>
       </c>
       <c r="O51">
-        <v>-8.58637053333333</v>
+        <v>-12.00709833333333</v>
       </c>
       <c r="P51">
-        <v>-25.75911159999999</v>
+        <v>-36.02129499999999</v>
       </c>
       <c r="Q51">
-        <v>0.7408884000000135</v>
+        <v>-9.521294999999991</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1269678761479676</v>
+        <v>0.1293970075191357</v>
       </c>
       <c r="T51">
-        <v>1.626901310583986</v>
+        <v>1.675589993827709</v>
       </c>
       <c r="U51">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1255817536095423</v>
+        <v>0.1048027133261245</v>
       </c>
       <c r="W51">
-        <v>0.1755831838752039</v>
+        <v>0.2110875201976998</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.5023270144381691</v>
+        <v>0.4192108533044981</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1702422638584178</v>
+        <v>0.1721422638584177</v>
       </c>
       <c r="C52">
-        <v>-93.86613913053748</v>
+        <v>-104.0492634079105</v>
       </c>
       <c r="D52">
-        <v>210.7338608694625</v>
+        <v>207.5647365920895</v>
       </c>
       <c r="E52">
-        <v>58.19999999999999</v>
+        <v>65.214</v>
       </c>
       <c r="F52">
-        <v>350.7</v>
+        <v>357.714</v>
       </c>
       <c r="G52">
         <v>46.1</v>
@@ -5539,37 +5539,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M52">
-        <v>82.69506</v>
+        <v>84.34896120000001</v>
       </c>
       <c r="N52">
-        <v>-48.02839333333333</v>
+        <v>-49.68229453333333</v>
       </c>
       <c r="O52">
-        <v>-12.00709833333333</v>
+        <v>-12.42057363333333</v>
       </c>
       <c r="P52">
-        <v>-36.02129499999999</v>
+        <v>-37.2617209</v>
       </c>
       <c r="Q52">
-        <v>-9.521294999999991</v>
+        <v>-10.7617209</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1293970075191357</v>
+        <v>0.1311030688970772</v>
       </c>
       <c r="T52">
-        <v>1.675589993827709</v>
+        <v>1.709785707987458</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1048027133261245</v>
+        <v>0.1027477581628672</v>
       </c>
       <c r="W52">
-        <v>0.2110875201976998</v>
+        <v>0.2115720786251959</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4192108533044981</v>
+        <v>0.4109910326514687</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1721422638584177</v>
+        <v>0.1740422638584178</v>
       </c>
       <c r="C53">
-        <v>-104.0492634079105</v>
+        <v>-114.138482042232</v>
       </c>
       <c r="D53">
-        <v>207.5647365920895</v>
+        <v>204.489517957768</v>
       </c>
       <c r="E53">
-        <v>65.214</v>
+        <v>72.22800000000001</v>
       </c>
       <c r="F53">
-        <v>357.714</v>
+        <v>364.728</v>
       </c>
       <c r="G53">
         <v>46.1</v>
@@ -5621,37 +5621,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M53">
-        <v>84.34896120000001</v>
+        <v>86.00286240000001</v>
       </c>
       <c r="N53">
-        <v>-49.68229453333333</v>
+        <v>-51.33619573333334</v>
       </c>
       <c r="O53">
-        <v>-12.42057363333333</v>
+        <v>-12.83404893333334</v>
       </c>
       <c r="P53">
-        <v>-37.2617209</v>
+        <v>-38.50214680000001</v>
       </c>
       <c r="Q53">
-        <v>-10.7617209</v>
+        <v>-12.0021468</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1311030688970772</v>
+        <v>0.1328802161657663</v>
       </c>
       <c r="T53">
-        <v>1.709785707987458</v>
+        <v>1.74540624357053</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1027477581628672</v>
+        <v>0.1007718397366582</v>
       </c>
       <c r="W53">
-        <v>0.2115720786251959</v>
+        <v>0.212038000190096</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4109910326514687</v>
+        <v>0.4030873589466327</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1740422638584178</v>
+        <v>0.1759422638584178</v>
       </c>
       <c r="C54">
-        <v>-114.138482042232</v>
+        <v>-124.1379079338735</v>
       </c>
       <c r="D54">
-        <v>204.489517957768</v>
+        <v>201.5040920661266</v>
       </c>
       <c r="E54">
-        <v>72.22800000000001</v>
+        <v>79.24200000000002</v>
       </c>
       <c r="F54">
-        <v>364.728</v>
+        <v>371.742</v>
       </c>
       <c r="G54">
         <v>46.1</v>
@@ -5703,37 +5703,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M54">
-        <v>86.00286240000001</v>
+        <v>87.6567636</v>
       </c>
       <c r="N54">
-        <v>-51.33619573333334</v>
+        <v>-52.99009693333333</v>
       </c>
       <c r="O54">
-        <v>-12.83404893333334</v>
+        <v>-13.24752423333333</v>
       </c>
       <c r="P54">
-        <v>-38.50214680000001</v>
+        <v>-39.7425727</v>
       </c>
       <c r="Q54">
-        <v>-12.0021468</v>
+        <v>-13.24257269999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1328802161657663</v>
+        <v>0.1347329867224848</v>
       </c>
       <c r="T54">
-        <v>1.74540624357053</v>
+        <v>1.782542546625222</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1007718397366582</v>
+        <v>0.0988704842699288</v>
       </c>
       <c r="W54">
-        <v>0.212038000190096</v>
+        <v>0.2124863398091508</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4030873589466327</v>
+        <v>0.3954819370797152</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1759422638584178</v>
+        <v>0.1778422638584178</v>
       </c>
       <c r="C55">
-        <v>-124.1379079338735</v>
+        <v>-134.0514172556476</v>
       </c>
       <c r="D55">
-        <v>201.5040920661266</v>
+        <v>198.6045827443525</v>
       </c>
       <c r="E55">
-        <v>79.24200000000002</v>
+        <v>86.25600000000003</v>
       </c>
       <c r="F55">
-        <v>371.742</v>
+        <v>378.756</v>
       </c>
       <c r="G55">
         <v>46.1</v>
@@ -5785,37 +5785,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M55">
-        <v>87.6567636</v>
+        <v>89.31066480000001</v>
       </c>
       <c r="N55">
-        <v>-52.99009693333333</v>
+        <v>-54.64399813333334</v>
       </c>
       <c r="O55">
-        <v>-13.24752423333333</v>
+        <v>-13.66099953333334</v>
       </c>
       <c r="P55">
-        <v>-39.7425727</v>
+        <v>-40.9829986</v>
       </c>
       <c r="Q55">
-        <v>-13.24257269999999</v>
+        <v>-14.4829986</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1347329867224848</v>
+        <v>0.1366663125207996</v>
       </c>
       <c r="T55">
-        <v>1.782542546625222</v>
+        <v>1.821293471551858</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0988704842699288</v>
+        <v>0.09703954937604121</v>
       </c>
       <c r="W55">
-        <v>0.2124863398091508</v>
+        <v>0.2129180742571295</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3954819370797152</v>
+        <v>0.3881581975041649</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1778422638584178</v>
+        <v>0.1797422638584178</v>
       </c>
       <c r="C56">
-        <v>-134.0514172556476</v>
+        <v>-143.8826662429661</v>
       </c>
       <c r="D56">
-        <v>198.6045827443525</v>
+        <v>195.787333757034</v>
       </c>
       <c r="E56">
-        <v>86.25600000000003</v>
+        <v>93.27000000000004</v>
       </c>
       <c r="F56">
-        <v>378.756</v>
+        <v>385.77</v>
       </c>
       <c r="G56">
         <v>46.1</v>
@@ -5867,37 +5867,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M56">
-        <v>89.31066480000001</v>
+        <v>90.96456600000002</v>
       </c>
       <c r="N56">
-        <v>-54.64399813333334</v>
+        <v>-56.29789933333335</v>
       </c>
       <c r="O56">
-        <v>-13.66099953333334</v>
+        <v>-14.07447483333334</v>
       </c>
       <c r="P56">
-        <v>-40.9829986</v>
+        <v>-42.22342450000001</v>
       </c>
       <c r="Q56">
-        <v>-14.4829986</v>
+        <v>-15.7234245</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1366663125207996</v>
+        <v>0.1386855639101508</v>
       </c>
       <c r="T56">
-        <v>1.821293471551858</v>
+        <v>1.861766659808566</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.09703954937604121</v>
+        <v>0.09527519393284047</v>
       </c>
       <c r="W56">
-        <v>0.2129180742571295</v>
+        <v>0.2133341092706362</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3881581975041649</v>
+        <v>0.3811007757313618</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1797422638584178</v>
+        <v>0.1816422638584178</v>
       </c>
       <c r="C57">
-        <v>-143.8826662429661</v>
+        <v>-153.6351065749535</v>
       </c>
       <c r="D57">
-        <v>195.787333757034</v>
+        <v>193.0488934250466</v>
       </c>
       <c r="E57">
-        <v>93.27000000000004</v>
+        <v>100.284</v>
       </c>
       <c r="F57">
-        <v>385.77</v>
+        <v>392.784</v>
       </c>
       <c r="G57">
         <v>46.1</v>
@@ -5949,37 +5949,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M57">
-        <v>90.96456600000002</v>
+        <v>92.61846720000001</v>
       </c>
       <c r="N57">
-        <v>-56.29789933333335</v>
+        <v>-57.95180053333334</v>
       </c>
       <c r="O57">
-        <v>-14.07447483333334</v>
+        <v>-14.48795013333334</v>
       </c>
       <c r="P57">
-        <v>-42.22342450000001</v>
+        <v>-43.46385040000001</v>
       </c>
       <c r="Q57">
-        <v>-15.7234245</v>
+        <v>-16.9638504</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1386855639101508</v>
+        <v>0.1407965994535633</v>
       </c>
       <c r="T57">
-        <v>1.861766659808566</v>
+        <v>1.904079538440579</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.09527519393284047</v>
+        <v>0.09357385118403976</v>
       </c>
       <c r="W57">
-        <v>0.2133341092706362</v>
+        <v>0.2137352858908035</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3811007757313618</v>
+        <v>0.374295404736159</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1816422638584178</v>
+        <v>0.1835422638584178</v>
       </c>
       <c r="C58">
-        <v>-153.6351065749535</v>
+        <v>-163.3119994825697</v>
       </c>
       <c r="D58">
-        <v>193.0488934250466</v>
+        <v>190.3860005174304</v>
       </c>
       <c r="E58">
-        <v>100.284</v>
+        <v>107.2980000000001</v>
       </c>
       <c r="F58">
-        <v>392.784</v>
+        <v>399.7980000000001</v>
       </c>
       <c r="G58">
         <v>46.1</v>
@@ -6031,37 +6031,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M58">
-        <v>92.61846720000001</v>
+        <v>94.27236840000002</v>
       </c>
       <c r="N58">
-        <v>-57.95180053333334</v>
+        <v>-59.60570173333335</v>
       </c>
       <c r="O58">
-        <v>-14.48795013333334</v>
+        <v>-14.90142543333334</v>
       </c>
       <c r="P58">
-        <v>-43.46385040000001</v>
+        <v>-44.70427630000001</v>
       </c>
       <c r="Q58">
-        <v>-16.9638504</v>
+        <v>-18.20427630000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1407965994535633</v>
+        <v>0.1430058226966694</v>
       </c>
       <c r="T58">
-        <v>1.904079538440579</v>
+        <v>1.948360457939197</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09357385118403976</v>
+        <v>0.09193220467203904</v>
       </c>
       <c r="W58">
-        <v>0.2137352858908035</v>
+        <v>0.2141223861383332</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.374295404736159</v>
+        <v>0.3677288186881562</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1835422638584178</v>
+        <v>0.1854422638584178</v>
       </c>
       <c r="C59">
-        <v>-163.3119994825697</v>
+        <v>-172.9164287049853</v>
       </c>
       <c r="D59">
-        <v>190.3860005174304</v>
+        <v>187.7955712950147</v>
       </c>
       <c r="E59">
-        <v>107.2980000000001</v>
+        <v>114.312</v>
       </c>
       <c r="F59">
-        <v>399.7980000000001</v>
+        <v>406.812</v>
       </c>
       <c r="G59">
         <v>46.1</v>
@@ -6113,37 +6113,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M59">
-        <v>94.27236840000002</v>
+        <v>95.92626960000001</v>
       </c>
       <c r="N59">
-        <v>-59.60570173333335</v>
+        <v>-61.25960293333334</v>
       </c>
       <c r="O59">
-        <v>-14.90142543333334</v>
+        <v>-15.31490073333334</v>
       </c>
       <c r="P59">
-        <v>-44.70427630000001</v>
+        <v>-45.94470220000001</v>
       </c>
       <c r="Q59">
-        <v>-18.20427630000001</v>
+        <v>-19.44470220000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1430058226966694</v>
+        <v>0.1453202470465901</v>
       </c>
       <c r="T59">
-        <v>1.948360457939197</v>
+        <v>1.994749992652035</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09193220467203904</v>
+        <v>0.09034716666045217</v>
       </c>
       <c r="W59">
-        <v>0.2141223861383332</v>
+        <v>0.2144961381014654</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3677288186881562</v>
+        <v>0.3613886666418087</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1854422638584177</v>
+        <v>0.1873422638584177</v>
       </c>
       <c r="C60">
-        <v>-172.9164287049852</v>
+        <v>-182.451312402433</v>
       </c>
       <c r="D60">
-        <v>187.7955712950147</v>
+        <v>185.274687597567</v>
       </c>
       <c r="E60">
-        <v>114.312</v>
+        <v>121.326</v>
       </c>
       <c r="F60">
-        <v>406.812</v>
+        <v>413.826</v>
       </c>
       <c r="G60">
         <v>46.1</v>
@@ -6195,37 +6195,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M60">
-        <v>95.9262696</v>
+        <v>97.58017079999999</v>
       </c>
       <c r="N60">
-        <v>-61.25960293333333</v>
+        <v>-62.91350413333332</v>
       </c>
       <c r="O60">
-        <v>-15.31490073333333</v>
+        <v>-15.72837603333333</v>
       </c>
       <c r="P60">
-        <v>-45.94470219999999</v>
+        <v>-47.18512809999999</v>
       </c>
       <c r="Q60">
-        <v>-19.44470219999999</v>
+        <v>-20.68512809999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1453202470465901</v>
+        <v>0.1477475701452874</v>
       </c>
       <c r="T60">
-        <v>1.994749992652034</v>
+        <v>2.043402431497205</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09034716666045219</v>
+        <v>0.08881585875095301</v>
       </c>
       <c r="W60">
-        <v>0.2144961381014654</v>
+        <v>0.2148572205065253</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3613886666418088</v>
+        <v>0.355263435003812</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1873422638584177</v>
+        <v>0.1892422638584178</v>
       </c>
       <c r="C61">
-        <v>-182.451312402433</v>
+        <v>-191.9194141222918</v>
       </c>
       <c r="D61">
-        <v>185.274687597567</v>
+        <v>182.8205858777082</v>
       </c>
       <c r="E61">
-        <v>121.326</v>
+        <v>128.34</v>
       </c>
       <c r="F61">
-        <v>413.826</v>
+        <v>420.84</v>
       </c>
       <c r="G61">
         <v>46.1</v>
@@ -6277,37 +6277,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M61">
-        <v>97.58017079999999</v>
+        <v>99.234072</v>
       </c>
       <c r="N61">
-        <v>-62.91350413333332</v>
+        <v>-64.56740533333333</v>
       </c>
       <c r="O61">
-        <v>-15.72837603333333</v>
+        <v>-16.14185133333333</v>
       </c>
       <c r="P61">
-        <v>-47.18512809999999</v>
+        <v>-48.42555399999999</v>
       </c>
       <c r="Q61">
-        <v>-20.68512809999998</v>
+        <v>-21.92555399999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1477475701452874</v>
+        <v>0.1502962593989196</v>
       </c>
       <c r="T61">
-        <v>2.043402431497205</v>
+        <v>2.094487492284636</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08881585875095301</v>
+        <v>0.08733559443843711</v>
       </c>
       <c r="W61">
-        <v>0.2148572205065253</v>
+        <v>0.2152062668314166</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.355263435003812</v>
+        <v>0.3493423777537484</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1892422638584178</v>
+        <v>0.1911422638584178</v>
       </c>
       <c r="C62">
-        <v>-191.9194141222918</v>
+        <v>-201.3233529050399</v>
       </c>
       <c r="D62">
-        <v>182.8205858777082</v>
+        <v>180.4306470949601</v>
       </c>
       <c r="E62">
-        <v>128.34</v>
+        <v>135.354</v>
       </c>
       <c r="F62">
-        <v>420.84</v>
+        <v>427.854</v>
       </c>
       <c r="G62">
         <v>46.1</v>
@@ -6359,37 +6359,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M62">
-        <v>99.234072</v>
+        <v>100.8879732</v>
       </c>
       <c r="N62">
-        <v>-64.56740533333333</v>
+        <v>-66.22130653333333</v>
       </c>
       <c r="O62">
-        <v>-16.14185133333333</v>
+        <v>-16.55532663333333</v>
       </c>
       <c r="P62">
-        <v>-48.42555399999999</v>
+        <v>-49.6659799</v>
       </c>
       <c r="Q62">
-        <v>-21.92555399999999</v>
+        <v>-23.16597989999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1502962593989196</v>
+        <v>0.1529756506655586</v>
       </c>
       <c r="T62">
-        <v>2.094487492284636</v>
+        <v>2.148192299779114</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08733559443843711</v>
+        <v>0.08590386338206929</v>
       </c>
       <c r="W62">
-        <v>0.2152062668314166</v>
+        <v>0.2155438690145081</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3493423777537484</v>
+        <v>0.3436154535282772</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1911422638584178</v>
+        <v>0.1930422638584178</v>
       </c>
       <c r="C63">
-        <v>-201.3233529050399</v>
+        <v>-210.6656126077708</v>
       </c>
       <c r="D63">
-        <v>180.4306470949601</v>
+        <v>178.1023873922292</v>
       </c>
       <c r="E63">
-        <v>135.354</v>
+        <v>142.368</v>
       </c>
       <c r="F63">
-        <v>427.854</v>
+        <v>434.868</v>
       </c>
       <c r="G63">
         <v>46.1</v>
@@ -6441,37 +6441,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M63">
-        <v>100.8879732</v>
+        <v>102.5418744</v>
       </c>
       <c r="N63">
-        <v>-66.22130653333333</v>
+        <v>-67.87520773333333</v>
       </c>
       <c r="O63">
-        <v>-16.55532663333333</v>
+        <v>-16.96880193333333</v>
       </c>
       <c r="P63">
-        <v>-49.6659799</v>
+        <v>-50.90640579999999</v>
       </c>
       <c r="Q63">
-        <v>-23.16597989999999</v>
+        <v>-24.40640579999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1529756506655586</v>
+        <v>0.1557960625251785</v>
       </c>
       <c r="T63">
-        <v>2.148192299779114</v>
+        <v>2.204723676089091</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08590386338206929</v>
+        <v>0.08451831719848753</v>
       </c>
       <c r="W63">
-        <v>0.2155438690145081</v>
+        <v>0.2158705808045966</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3436154535282772</v>
+        <v>0.3380732687939502</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1930422638584178</v>
+        <v>0.1949422638584178</v>
       </c>
       <c r="C64">
-        <v>-210.6656126077708</v>
+        <v>-219.9485505150462</v>
       </c>
       <c r="D64">
-        <v>178.1023873922292</v>
+        <v>175.8334494849538</v>
       </c>
       <c r="E64">
-        <v>142.368</v>
+        <v>149.382</v>
       </c>
       <c r="F64">
-        <v>434.868</v>
+        <v>441.882</v>
       </c>
       <c r="G64">
         <v>46.1</v>
@@ -6523,37 +6523,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M64">
-        <v>102.5418744</v>
+        <v>104.1957756</v>
       </c>
       <c r="N64">
-        <v>-67.87520773333333</v>
+        <v>-69.52910893333333</v>
       </c>
       <c r="O64">
-        <v>-16.96880193333333</v>
+        <v>-17.38227723333333</v>
       </c>
       <c r="P64">
-        <v>-50.90640579999999</v>
+        <v>-52.1468317</v>
       </c>
       <c r="Q64">
-        <v>-24.40640579999999</v>
+        <v>-25.6468317</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1557960625251785</v>
+        <v>0.1587689290799131</v>
       </c>
       <c r="T64">
-        <v>2.204723676089091</v>
+        <v>2.264310802469877</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08451831719848753</v>
+        <v>0.08317675660803533</v>
       </c>
       <c r="W64">
-        <v>0.2158705808045966</v>
+        <v>0.2161869207918253</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3380732687939502</v>
+        <v>0.3327070264321413</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1949422638584178</v>
+        <v>0.1968422638584178</v>
       </c>
       <c r="C65">
-        <v>-219.9485505150462</v>
+        <v>-229.1744052998406</v>
       </c>
       <c r="D65">
-        <v>175.8334494849538</v>
+        <v>173.6215947001594</v>
       </c>
       <c r="E65">
-        <v>149.382</v>
+        <v>156.396</v>
       </c>
       <c r="F65">
-        <v>441.882</v>
+        <v>448.896</v>
       </c>
       <c r="G65">
         <v>46.1</v>
@@ -6605,37 +6605,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M65">
-        <v>104.1957756</v>
+        <v>105.8496768</v>
       </c>
       <c r="N65">
-        <v>-69.52910893333333</v>
+        <v>-71.18301013333334</v>
       </c>
       <c r="O65">
-        <v>-17.38227723333333</v>
+        <v>-17.79575253333334</v>
       </c>
       <c r="P65">
-        <v>-52.1468317</v>
+        <v>-53.38725760000001</v>
       </c>
       <c r="Q65">
-        <v>-25.6468317</v>
+        <v>-26.8872576</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1587689290799131</v>
+        <v>0.1619069548876885</v>
       </c>
       <c r="T65">
-        <v>2.264310802469877</v>
+        <v>2.327208324760707</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08317675660803533</v>
+        <v>0.08187711978603478</v>
       </c>
       <c r="W65">
-        <v>0.2161869207918253</v>
+        <v>0.216493375154453</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3327070264321413</v>
+        <v>0.3275084791441392</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1968422638584178</v>
+        <v>0.1987422638584178</v>
       </c>
       <c r="C66">
-        <v>-229.1744052998406</v>
+        <v>-238.345304391093</v>
       </c>
       <c r="D66">
-        <v>173.6215947001594</v>
+        <v>171.464695608907</v>
       </c>
       <c r="E66">
-        <v>156.396</v>
+        <v>163.41</v>
       </c>
       <c r="F66">
-        <v>448.896</v>
+        <v>455.91</v>
       </c>
       <c r="G66">
         <v>46.1</v>
@@ -6687,37 +6687,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M66">
-        <v>105.8496768</v>
+        <v>107.503578</v>
       </c>
       <c r="N66">
-        <v>-71.18301013333334</v>
+        <v>-72.83691133333333</v>
       </c>
       <c r="O66">
-        <v>-17.79575253333334</v>
+        <v>-18.20922783333333</v>
       </c>
       <c r="P66">
-        <v>-53.38725760000001</v>
+        <v>-54.6276835</v>
       </c>
       <c r="Q66">
-        <v>-26.8872576</v>
+        <v>-28.1276835</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1619069548876885</v>
+        <v>0.1652242964559081</v>
       </c>
       <c r="T66">
-        <v>2.327208324760707</v>
+        <v>2.393699991182442</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08187711978603478</v>
+        <v>0.08061747178932656</v>
       </c>
       <c r="W66">
-        <v>0.216493375154453</v>
+        <v>0.2167904001520768</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3275084791441392</v>
+        <v>0.3224698871573063</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1987422638584178</v>
+        <v>0.2006422638584178</v>
       </c>
       <c r="C67">
-        <v>-238.345304391093</v>
+        <v>-247.4632707988355</v>
       </c>
       <c r="D67">
-        <v>171.464695608907</v>
+        <v>169.3607292011645</v>
       </c>
       <c r="E67">
-        <v>163.41</v>
+        <v>170.424</v>
       </c>
       <c r="F67">
-        <v>455.91</v>
+        <v>462.924</v>
       </c>
       <c r="G67">
         <v>46.1</v>
@@ -6769,37 +6769,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M67">
-        <v>107.503578</v>
+        <v>109.1574792</v>
       </c>
       <c r="N67">
-        <v>-72.83691133333333</v>
+        <v>-74.49081253333334</v>
       </c>
       <c r="O67">
-        <v>-18.20922783333333</v>
+        <v>-18.62270313333334</v>
       </c>
       <c r="P67">
-        <v>-54.6276835</v>
+        <v>-55.86810940000001</v>
       </c>
       <c r="Q67">
-        <v>-28.1276835</v>
+        <v>-29.36810940000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1652242964559081</v>
+        <v>0.1687367757634348</v>
       </c>
       <c r="T67">
-        <v>2.393699991182442</v>
+        <v>2.464102932099572</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08061747178932656</v>
+        <v>0.07939599494403372</v>
       </c>
       <c r="W67">
-        <v>0.2167904001520768</v>
+        <v>0.2170784243921969</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3224698871573063</v>
+        <v>0.317583979776135</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2006422638584178</v>
+        <v>0.2025422638584178</v>
       </c>
       <c r="C68">
-        <v>-247.4632707988355</v>
+        <v>-256.5302294429245</v>
       </c>
       <c r="D68">
-        <v>169.3607292011645</v>
+        <v>167.3077705570755</v>
       </c>
       <c r="E68">
-        <v>170.424</v>
+        <v>177.438</v>
       </c>
       <c r="F68">
-        <v>462.924</v>
+        <v>469.938</v>
       </c>
       <c r="G68">
         <v>46.1</v>
@@ -6851,37 +6851,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M68">
-        <v>109.1574792</v>
+        <v>110.8113804</v>
       </c>
       <c r="N68">
-        <v>-74.49081253333334</v>
+        <v>-76.14471373333333</v>
       </c>
       <c r="O68">
-        <v>-18.62270313333334</v>
+        <v>-19.03617843333333</v>
       </c>
       <c r="P68">
-        <v>-55.86810940000001</v>
+        <v>-57.1085353</v>
       </c>
       <c r="Q68">
-        <v>-29.36810940000001</v>
+        <v>-30.6085353</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1687367757634348</v>
+        <v>0.172462132604751</v>
       </c>
       <c r="T68">
-        <v>2.464102932099572</v>
+        <v>2.538772717920772</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07939599494403372</v>
+        <v>0.07821098009412278</v>
       </c>
       <c r="W68">
-        <v>0.2170784243921969</v>
+        <v>0.2173578508938059</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.317583979776135</v>
+        <v>0.3128439203764911</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2025422638584178</v>
+        <v>0.2044422638584178</v>
       </c>
       <c r="C69">
-        <v>-256.5302294429245</v>
+        <v>-265.5480130269897</v>
       </c>
       <c r="D69">
-        <v>167.3077705570755</v>
+        <v>165.3039869730103</v>
       </c>
       <c r="E69">
-        <v>177.438</v>
+        <v>184.452</v>
       </c>
       <c r="F69">
-        <v>469.938</v>
+        <v>476.952</v>
       </c>
       <c r="G69">
         <v>46.1</v>
@@ -6933,37 +6933,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M69">
-        <v>110.8113804</v>
+        <v>112.4652816</v>
       </c>
       <c r="N69">
-        <v>-76.14471373333333</v>
+        <v>-77.79861493333333</v>
       </c>
       <c r="O69">
-        <v>-19.03617843333333</v>
+        <v>-19.44965373333333</v>
       </c>
       <c r="P69">
-        <v>-57.1085353</v>
+        <v>-58.34896119999999</v>
       </c>
       <c r="Q69">
-        <v>-30.6085353</v>
+        <v>-31.84896119999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.172462132604751</v>
+        <v>0.1764203242486495</v>
       </c>
       <c r="T69">
-        <v>2.538772717920772</v>
+        <v>2.618109365355796</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07821098009412278</v>
+        <v>0.07706081862215039</v>
       </c>
       <c r="W69">
-        <v>0.2173578508938059</v>
+        <v>0.2176290589688969</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3128439203764911</v>
+        <v>0.3082432744886016</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2044422638584178</v>
+        <v>0.2063422638584178</v>
       </c>
       <c r="C70">
-        <v>-265.5480130269897</v>
+        <v>-274.5183674952792</v>
       </c>
       <c r="D70">
-        <v>165.3039869730103</v>
+        <v>163.3476325047208</v>
       </c>
       <c r="E70">
-        <v>184.452</v>
+        <v>191.466</v>
       </c>
       <c r="F70">
-        <v>476.952</v>
+        <v>483.966</v>
       </c>
       <c r="G70">
         <v>46.1</v>
@@ -7015,37 +7015,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M70">
-        <v>112.4652816</v>
+        <v>114.1191828</v>
       </c>
       <c r="N70">
-        <v>-77.79861493333333</v>
+        <v>-79.45251613333333</v>
       </c>
       <c r="O70">
-        <v>-19.44965373333333</v>
+        <v>-19.86312903333333</v>
       </c>
       <c r="P70">
-        <v>-58.34896119999999</v>
+        <v>-59.5893871</v>
       </c>
       <c r="Q70">
-        <v>-31.84896119999999</v>
+        <v>-33.0893871</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1764203242486495</v>
+        <v>0.1806338830953802</v>
       </c>
       <c r="T70">
-        <v>2.618109365355796</v>
+        <v>2.702564506173725</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07706081862215039</v>
+        <v>0.07594399516385836</v>
       </c>
       <c r="W70">
-        <v>0.2176290589688969</v>
+        <v>0.2178924059403622</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3082432744886016</v>
+        <v>0.3037759806554334</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2063422638584178</v>
+        <v>0.2082422638584178</v>
       </c>
       <c r="C71">
-        <v>-274.5183674952792</v>
+        <v>-283.4429571065486</v>
       </c>
       <c r="D71">
-        <v>163.3476325047208</v>
+        <v>161.4370428934514</v>
       </c>
       <c r="E71">
-        <v>191.466</v>
+        <v>198.48</v>
       </c>
       <c r="F71">
-        <v>483.966</v>
+        <v>490.98</v>
       </c>
       <c r="G71">
         <v>46.1</v>
@@ -7097,37 +7097,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M71">
-        <v>114.1191828</v>
+        <v>115.773084</v>
       </c>
       <c r="N71">
-        <v>-79.45251613333333</v>
+        <v>-81.10641733333334</v>
       </c>
       <c r="O71">
-        <v>-19.86312903333333</v>
+        <v>-20.27660433333334</v>
       </c>
       <c r="P71">
-        <v>-59.5893871</v>
+        <v>-60.829813</v>
       </c>
       <c r="Q71">
-        <v>-33.0893871</v>
+        <v>-34.329813</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1806338830953802</v>
+        <v>0.1851283458652262</v>
       </c>
       <c r="T71">
-        <v>2.702564506173725</v>
+        <v>2.792649989712849</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07594399516385836</v>
+        <v>0.0748590809472318</v>
       </c>
       <c r="W71">
-        <v>0.2178924059403622</v>
+        <v>0.2181482287126427</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3037759806554334</v>
+        <v>0.2994363237889273</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2082422638584178</v>
+        <v>0.2101422638584178</v>
       </c>
       <c r="C72">
-        <v>-283.4429571065486</v>
+        <v>-292.3233691559883</v>
       </c>
       <c r="D72">
-        <v>161.4370428934514</v>
+        <v>159.5706308440117</v>
       </c>
       <c r="E72">
-        <v>198.48</v>
+        <v>205.494</v>
       </c>
       <c r="F72">
-        <v>490.98</v>
+        <v>497.994</v>
       </c>
       <c r="G72">
         <v>46.1</v>
@@ -7179,37 +7179,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M72">
-        <v>115.773084</v>
+        <v>117.4269852</v>
       </c>
       <c r="N72">
-        <v>-81.10641733333334</v>
+        <v>-82.76031853333335</v>
       </c>
       <c r="O72">
-        <v>-20.27660433333334</v>
+        <v>-20.69007963333334</v>
       </c>
       <c r="P72">
-        <v>-60.829813</v>
+        <v>-62.07023890000001</v>
       </c>
       <c r="Q72">
-        <v>-34.329813</v>
+        <v>-35.57023890000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1851283458652262</v>
+        <v>0.1899327715847167</v>
       </c>
       <c r="T72">
-        <v>2.792649989712849</v>
+        <v>2.888948265220189</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0748590809472318</v>
+        <v>0.07380472769445388</v>
       </c>
       <c r="W72">
-        <v>0.2181482287126427</v>
+        <v>0.2183968452096478</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2994363237889273</v>
+        <v>0.2952189107778156</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2101422638584178</v>
+        <v>0.2120422638584178</v>
       </c>
       <c r="C73">
-        <v>-292.3233691559882</v>
+        <v>-301.1611183733464</v>
       </c>
       <c r="D73">
-        <v>159.5706308440117</v>
+        <v>157.7468816266536</v>
       </c>
       <c r="E73">
-        <v>205.494</v>
+        <v>212.508</v>
       </c>
       <c r="F73">
-        <v>497.994</v>
+        <v>505.008</v>
       </c>
       <c r="G73">
         <v>46.1</v>
@@ -7261,37 +7261,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M73">
-        <v>117.4269852</v>
+        <v>119.0808864</v>
       </c>
       <c r="N73">
-        <v>-82.76031853333333</v>
+        <v>-84.41421973333333</v>
       </c>
       <c r="O73">
-        <v>-20.69007963333333</v>
+        <v>-21.10355493333333</v>
       </c>
       <c r="P73">
-        <v>-62.0702389</v>
+        <v>-63.3106648</v>
       </c>
       <c r="Q73">
-        <v>-35.57023889999999</v>
+        <v>-36.8106648</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1899327715847167</v>
+        <v>0.1950803705698851</v>
       </c>
       <c r="T73">
-        <v>2.888948265220188</v>
+        <v>2.992124988978051</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0738047276944539</v>
+        <v>0.07277966203203093</v>
       </c>
       <c r="W73">
-        <v>0.2183968452096478</v>
+        <v>0.2186385556928471</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2952189107778156</v>
+        <v>0.2911186481281237</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2120422638584178</v>
+        <v>0.2139422638584177</v>
       </c>
       <c r="C74">
-        <v>-301.1611183733464</v>
+        <v>-309.9576510228591</v>
       </c>
       <c r="D74">
-        <v>157.7468816266536</v>
+        <v>155.9643489771408</v>
       </c>
       <c r="E74">
-        <v>212.508</v>
+        <v>219.5219999999999</v>
       </c>
       <c r="F74">
-        <v>505.008</v>
+        <v>512.0219999999999</v>
       </c>
       <c r="G74">
         <v>46.1</v>
@@ -7343,37 +7343,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M74">
-        <v>119.0808864</v>
+        <v>120.7347876</v>
       </c>
       <c r="N74">
-        <v>-84.41421973333333</v>
+        <v>-86.06812093333332</v>
       </c>
       <c r="O74">
-        <v>-21.10355493333333</v>
+        <v>-21.51703023333333</v>
       </c>
       <c r="P74">
-        <v>-63.3106648</v>
+        <v>-64.55109069999999</v>
       </c>
       <c r="Q74">
-        <v>-36.8106648</v>
+        <v>-38.05109069999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1950803705698851</v>
+        <v>0.2006092731835846</v>
       </c>
       <c r="T74">
-        <v>2.992124988978051</v>
+        <v>3.102944433014275</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07277966203203093</v>
+        <v>0.07178268036035927</v>
       </c>
       <c r="W74">
-        <v>0.2186385556928471</v>
+        <v>0.2188736439710273</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2911186481281237</v>
+        <v>0.2871307214414371</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2139422638584177</v>
+        <v>0.2158422638584178</v>
       </c>
       <c r="C75">
-        <v>-309.9576510228591</v>
+        <v>-318.7143487283149</v>
       </c>
       <c r="D75">
-        <v>155.9643489771408</v>
+        <v>154.2216512716851</v>
       </c>
       <c r="E75">
-        <v>219.5219999999999</v>
+        <v>226.5359999999999</v>
       </c>
       <c r="F75">
-        <v>512.0219999999999</v>
+        <v>519.0359999999999</v>
       </c>
       <c r="G75">
         <v>46.1</v>
@@ -7425,37 +7425,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M75">
-        <v>120.7347876</v>
+        <v>122.3886888</v>
       </c>
       <c r="N75">
-        <v>-86.06812093333332</v>
+        <v>-87.72202213333333</v>
       </c>
       <c r="O75">
-        <v>-21.51703023333333</v>
+        <v>-21.93050553333333</v>
       </c>
       <c r="P75">
-        <v>-64.55109069999999</v>
+        <v>-65.79151659999999</v>
       </c>
       <c r="Q75">
-        <v>-38.05109069999999</v>
+        <v>-39.29151659999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2006092731835846</v>
+        <v>0.2065634759983378</v>
       </c>
       <c r="T75">
-        <v>3.102944433014275</v>
+        <v>3.222288449668671</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07178268036035927</v>
+        <v>0.07081264413927334</v>
       </c>
       <c r="W75">
-        <v>0.2188736439710273</v>
+        <v>0.2191023785119594</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2871307214414371</v>
+        <v>0.2832505765570933</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2158422638584178</v>
+        <v>0.2177422638584178</v>
       </c>
       <c r="C76">
-        <v>-318.7143487283149</v>
+        <v>-327.4325320445092</v>
       </c>
       <c r="D76">
-        <v>154.2216512716851</v>
+        <v>152.5174679554907</v>
       </c>
       <c r="E76">
-        <v>226.5359999999999</v>
+        <v>233.55</v>
       </c>
       <c r="F76">
-        <v>519.0359999999999</v>
+        <v>526.05</v>
       </c>
       <c r="G76">
         <v>46.1</v>
@@ -7507,37 +7507,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M76">
-        <v>122.3886888</v>
+        <v>124.04259</v>
       </c>
       <c r="N76">
-        <v>-87.72202213333333</v>
+        <v>-89.37592333333332</v>
       </c>
       <c r="O76">
-        <v>-21.93050553333333</v>
+        <v>-22.34398083333333</v>
       </c>
       <c r="P76">
-        <v>-65.79151659999999</v>
+        <v>-67.03194249999999</v>
       </c>
       <c r="Q76">
-        <v>-39.29151659999999</v>
+        <v>-40.53194249999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2065634759983378</v>
+        <v>0.2129940150382714</v>
       </c>
       <c r="T76">
-        <v>3.222288449668671</v>
+        <v>3.351179987655418</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07081264413927334</v>
+        <v>0.0698684755507497</v>
       </c>
       <c r="W76">
-        <v>0.2191023785119594</v>
+        <v>0.2193250134651332</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2832505765570933</v>
+        <v>0.2794739022029987</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2177422638584178</v>
+        <v>0.2196422638584178</v>
       </c>
       <c r="C77">
-        <v>-327.4325320445092</v>
+        <v>-336.1134637944976</v>
       </c>
       <c r="D77">
-        <v>152.5174679554907</v>
+        <v>150.8505362055024</v>
       </c>
       <c r="E77">
-        <v>233.55</v>
+        <v>240.564</v>
       </c>
       <c r="F77">
-        <v>526.05</v>
+        <v>533.064</v>
       </c>
       <c r="G77">
         <v>46.1</v>
@@ -7589,37 +7589,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M77">
-        <v>124.04259</v>
+        <v>125.6964912</v>
       </c>
       <c r="N77">
-        <v>-89.37592333333332</v>
+        <v>-91.02982453333333</v>
       </c>
       <c r="O77">
-        <v>-22.34398083333333</v>
+        <v>-22.75745613333333</v>
       </c>
       <c r="P77">
-        <v>-67.03194249999999</v>
+        <v>-68.27236839999999</v>
       </c>
       <c r="Q77">
-        <v>-40.53194249999999</v>
+        <v>-41.77236839999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2129940150382714</v>
+        <v>0.2199604323315327</v>
       </c>
       <c r="T77">
-        <v>3.351179987655418</v>
+        <v>3.49081248714106</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0698684755507497</v>
+        <v>0.0689491535040293</v>
       </c>
       <c r="W77">
-        <v>0.2193250134651332</v>
+        <v>0.2195417896037499</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2794739022029987</v>
+        <v>0.2757966140161172</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2196422638584178</v>
+        <v>0.2215422638584178</v>
       </c>
       <c r="C78">
-        <v>-336.1134637944976</v>
+        <v>-344.7583521903667</v>
       </c>
       <c r="D78">
-        <v>150.8505362055024</v>
+        <v>149.2196478096333</v>
       </c>
       <c r="E78">
-        <v>240.564</v>
+        <v>247.578</v>
       </c>
       <c r="F78">
-        <v>533.064</v>
+        <v>540.078</v>
       </c>
       <c r="G78">
         <v>46.1</v>
@@ -7671,37 +7671,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M78">
-        <v>125.6964912</v>
+        <v>127.3503924</v>
       </c>
       <c r="N78">
-        <v>-91.02982453333333</v>
+        <v>-92.68372573333333</v>
       </c>
       <c r="O78">
-        <v>-22.75745613333333</v>
+        <v>-23.17093143333333</v>
       </c>
       <c r="P78">
-        <v>-68.27236839999999</v>
+        <v>-69.5127943</v>
       </c>
       <c r="Q78">
-        <v>-41.77236839999999</v>
+        <v>-43.0127943</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2199604323315327</v>
+        <v>0.2275326250415993</v>
       </c>
       <c r="T78">
-        <v>3.49081248714106</v>
+        <v>3.642586943103715</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0689491535040293</v>
+        <v>0.06805370995202892</v>
       </c>
       <c r="W78">
-        <v>0.2195417896037499</v>
+        <v>0.2197529351933116</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2757966140161172</v>
+        <v>0.2722148398081157</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2215422638584178</v>
+        <v>0.2234422638584178</v>
       </c>
       <c r="C79">
-        <v>-344.7583521903667</v>
+        <v>-353.3683537537349</v>
       </c>
       <c r="D79">
-        <v>149.2196478096333</v>
+        <v>147.6236462462651</v>
       </c>
       <c r="E79">
-        <v>247.578</v>
+        <v>254.592</v>
       </c>
       <c r="F79">
-        <v>540.078</v>
+        <v>547.092</v>
       </c>
       <c r="G79">
         <v>46.1</v>
@@ -7753,37 +7753,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M79">
-        <v>127.3503924</v>
+        <v>129.0042936</v>
       </c>
       <c r="N79">
-        <v>-92.68372573333333</v>
+        <v>-94.33762693333334</v>
       </c>
       <c r="O79">
-        <v>-23.17093143333333</v>
+        <v>-23.58440673333333</v>
       </c>
       <c r="P79">
-        <v>-69.5127943</v>
+        <v>-70.7532202</v>
       </c>
       <c r="Q79">
-        <v>-43.0127943</v>
+        <v>-44.2532202</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2275326250415993</v>
+        <v>0.2357931989071265</v>
       </c>
       <c r="T79">
-        <v>3.642586943103715</v>
+        <v>3.808159076881157</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06805370995202892</v>
+        <v>0.06718122649110546</v>
       </c>
       <c r="W79">
-        <v>0.2197529351933116</v>
+        <v>0.2199586667933973</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2722148398081157</v>
+        <v>0.2687249059644219</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2234422638584178</v>
+        <v>0.2253422638584178</v>
       </c>
       <c r="C80">
-        <v>-353.3683537537349</v>
+        <v>-361.9445760508152</v>
       </c>
       <c r="D80">
-        <v>147.6236462462651</v>
+        <v>146.0614239491848</v>
       </c>
       <c r="E80">
-        <v>254.592</v>
+        <v>261.606</v>
       </c>
       <c r="F80">
-        <v>547.092</v>
+        <v>554.106</v>
       </c>
       <c r="G80">
         <v>46.1</v>
@@ -7835,37 +7835,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M80">
-        <v>129.0042936</v>
+        <v>130.6581948</v>
       </c>
       <c r="N80">
-        <v>-94.33762693333334</v>
+        <v>-95.99152813333335</v>
       </c>
       <c r="O80">
-        <v>-23.58440673333333</v>
+        <v>-23.99788203333334</v>
       </c>
       <c r="P80">
-        <v>-70.7532202</v>
+        <v>-71.99364610000001</v>
       </c>
       <c r="Q80">
-        <v>-44.2532202</v>
+        <v>-45.49364610000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2357931989071265</v>
+        <v>0.2448404940931802</v>
       </c>
       <c r="T80">
-        <v>3.808159076881157</v>
+        <v>3.98949998530407</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06718122649110546</v>
+        <v>0.06633083121906615</v>
       </c>
       <c r="W80">
-        <v>0.2199586667933973</v>
+        <v>0.2201591899985442</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2687249059644219</v>
+        <v>0.2653233248762646</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2253422638584178</v>
+        <v>0.2272422638584178</v>
       </c>
       <c r="C81">
-        <v>-361.9445760508152</v>
+        <v>-370.4880802556349</v>
       </c>
       <c r="D81">
-        <v>146.0614239491848</v>
+        <v>144.5319197443651</v>
       </c>
       <c r="E81">
-        <v>261.606</v>
+        <v>268.62</v>
       </c>
       <c r="F81">
-        <v>554.106</v>
+        <v>561.12</v>
       </c>
       <c r="G81">
         <v>46.1</v>
@@ -7917,37 +7917,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M81">
-        <v>130.6581948</v>
+        <v>132.312096</v>
       </c>
       <c r="N81">
-        <v>-95.99152813333335</v>
+        <v>-97.64542933333333</v>
       </c>
       <c r="O81">
-        <v>-23.99788203333334</v>
+        <v>-24.41135733333333</v>
       </c>
       <c r="P81">
-        <v>-71.99364610000001</v>
+        <v>-73.234072</v>
       </c>
       <c r="Q81">
-        <v>-45.49364610000001</v>
+        <v>-46.734072</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2448404940931802</v>
+        <v>0.2547925187978392</v>
       </c>
       <c r="T81">
-        <v>3.98949998530407</v>
+        <v>4.188974984569273</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06633083121906615</v>
+        <v>0.06550169582882784</v>
       </c>
       <c r="W81">
-        <v>0.2201591899985442</v>
+        <v>0.2203547001235624</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2653233248762646</v>
+        <v>0.2620067833153114</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2272422638584178</v>
+        <v>0.2291422638584178</v>
       </c>
       <c r="C82">
-        <v>-370.4880802556349</v>
+        <v>-378.999883553877</v>
       </c>
       <c r="D82">
-        <v>144.5319197443651</v>
+        <v>143.034116446123</v>
       </c>
       <c r="E82">
-        <v>268.62</v>
+        <v>275.634</v>
       </c>
       <c r="F82">
-        <v>561.12</v>
+        <v>568.134</v>
       </c>
       <c r="G82">
         <v>46.1</v>
@@ -7999,37 +7999,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M82">
-        <v>132.312096</v>
+        <v>133.9659972</v>
       </c>
       <c r="N82">
-        <v>-97.64542933333333</v>
+        <v>-99.29933053333333</v>
       </c>
       <c r="O82">
-        <v>-24.41135733333333</v>
+        <v>-24.82483263333333</v>
       </c>
       <c r="P82">
-        <v>-73.234072</v>
+        <v>-74.4744979</v>
       </c>
       <c r="Q82">
-        <v>-46.734072</v>
+        <v>-47.9744979</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2547925187978392</v>
+        <v>0.2657921250503571</v>
       </c>
       <c r="T82">
-        <v>4.188974984569273</v>
+        <v>4.409447352178183</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06550169582882784</v>
+        <v>0.06469303291736082</v>
       </c>
       <c r="W82">
-        <v>0.2203547001235624</v>
+        <v>0.2205453828380863</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2620067833153114</v>
+        <v>0.2587721316694432</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2291422638584178</v>
+        <v>0.2310422638584178</v>
       </c>
       <c r="C83">
-        <v>-378.999883553877</v>
+        <v>-387.4809613987868</v>
       </c>
       <c r="D83">
-        <v>143.034116446123</v>
+        <v>141.5670386012133</v>
       </c>
       <c r="E83">
-        <v>275.634</v>
+        <v>282.648</v>
       </c>
       <c r="F83">
-        <v>568.134</v>
+        <v>575.148</v>
       </c>
       <c r="G83">
         <v>46.1</v>
@@ -8081,37 +8081,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M83">
-        <v>133.9659972</v>
+        <v>135.6198984</v>
       </c>
       <c r="N83">
-        <v>-99.29933053333333</v>
+        <v>-100.9532317333333</v>
       </c>
       <c r="O83">
-        <v>-24.82483263333333</v>
+        <v>-25.23830793333333</v>
       </c>
       <c r="P83">
-        <v>-74.4744979</v>
+        <v>-75.71492380000001</v>
       </c>
       <c r="Q83">
-        <v>-47.9744979</v>
+        <v>-49.21492380000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2657921250503571</v>
+        <v>0.2780139097753769</v>
       </c>
       <c r="T83">
-        <v>4.409447352178183</v>
+        <v>4.654416649521416</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06469303291736082</v>
+        <v>0.06390409349153935</v>
       </c>
       <c r="W83">
-        <v>0.2205453828380863</v>
+        <v>0.220731414754695</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2587721316694432</v>
+        <v>0.2556163739661573</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2310422638584178</v>
+        <v>0.2329422638584178</v>
       </c>
       <c r="C84">
-        <v>-387.4809613987868</v>
+        <v>-395.932249629658</v>
       </c>
       <c r="D84">
-        <v>141.5670386012133</v>
+        <v>140.129750370342</v>
       </c>
       <c r="E84">
-        <v>282.648</v>
+        <v>289.662</v>
       </c>
       <c r="F84">
-        <v>575.148</v>
+        <v>582.162</v>
       </c>
       <c r="G84">
         <v>46.1</v>
@@ -8163,37 +8163,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M84">
-        <v>135.6198984</v>
+        <v>137.2737996</v>
       </c>
       <c r="N84">
-        <v>-100.9532317333333</v>
+        <v>-102.6071329333333</v>
       </c>
       <c r="O84">
-        <v>-25.23830793333333</v>
+        <v>-25.65178323333334</v>
       </c>
       <c r="P84">
-        <v>-75.71492380000001</v>
+        <v>-76.95534970000001</v>
       </c>
       <c r="Q84">
-        <v>-49.21492380000001</v>
+        <v>-50.45534970000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2780139097753769</v>
+        <v>0.2916735515268697</v>
       </c>
       <c r="T84">
-        <v>4.654416649521416</v>
+        <v>4.928205864199146</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06390409349153935</v>
+        <v>0.06313416465429188</v>
       </c>
       <c r="W84">
-        <v>0.220731414754695</v>
+        <v>0.220912963974518</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2556163739661573</v>
+        <v>0.2525366586171676</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2329422638584178</v>
+        <v>0.2348422638584178</v>
       </c>
       <c r="C85">
-        <v>-395.932249629658</v>
+        <v>-404.3546464625645</v>
       </c>
       <c r="D85">
-        <v>140.129750370342</v>
+        <v>138.7213535374356</v>
       </c>
       <c r="E85">
-        <v>289.662</v>
+        <v>296.676</v>
       </c>
       <c r="F85">
-        <v>582.162</v>
+        <v>589.176</v>
       </c>
       <c r="G85">
         <v>46.1</v>
@@ -8245,37 +8245,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M85">
-        <v>137.2737996</v>
+        <v>138.9277008</v>
       </c>
       <c r="N85">
-        <v>-102.6071329333333</v>
+        <v>-104.2610341333334</v>
       </c>
       <c r="O85">
-        <v>-25.65178323333334</v>
+        <v>-26.06525853333334</v>
       </c>
       <c r="P85">
-        <v>-76.95534970000001</v>
+        <v>-78.19577560000002</v>
       </c>
       <c r="Q85">
-        <v>-50.45534970000001</v>
+        <v>-51.69577560000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2916735515268697</v>
+        <v>0.3070406484972991</v>
       </c>
       <c r="T85">
-        <v>4.928205864199146</v>
+        <v>5.236218730711593</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06313416465429188</v>
+        <v>0.06238256745602649</v>
       </c>
       <c r="W85">
-        <v>0.220912963974518</v>
+        <v>0.2210901905938689</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2525366586171676</v>
+        <v>0.249530269824106</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2348422638584177</v>
+        <v>0.2367422638584177</v>
       </c>
       <c r="C86">
-        <v>-404.3546464625644</v>
+        <v>-412.7490143622377</v>
       </c>
       <c r="D86">
-        <v>138.7213535374355</v>
+        <v>137.3409856377622</v>
       </c>
       <c r="E86">
-        <v>296.6759999999999</v>
+        <v>303.6899999999999</v>
       </c>
       <c r="F86">
-        <v>589.1759999999999</v>
+        <v>596.1899999999999</v>
       </c>
       <c r="G86">
         <v>46.1</v>
@@ -8327,37 +8327,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M86">
-        <v>138.9277008</v>
+        <v>140.581602</v>
       </c>
       <c r="N86">
-        <v>-104.2610341333333</v>
+        <v>-105.9149353333333</v>
       </c>
       <c r="O86">
-        <v>-26.06525853333333</v>
+        <v>-26.47873383333333</v>
       </c>
       <c r="P86">
-        <v>-78.19577559999999</v>
+        <v>-79.4362015</v>
       </c>
       <c r="Q86">
-        <v>-51.69577559999999</v>
+        <v>-52.9362015</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.307040648497299</v>
+        <v>0.3244566917304522</v>
       </c>
       <c r="T86">
-        <v>5.23621873071159</v>
+        <v>5.585299979425696</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06238256745602651</v>
+        <v>0.06164865489772031</v>
       </c>
       <c r="W86">
-        <v>0.2210901905938689</v>
+        <v>0.2212632471751176</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2495302698241061</v>
+        <v>0.2465946195908812</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2367422638584177</v>
+        <v>0.2386422638584177</v>
       </c>
       <c r="C87">
-        <v>-412.7490143622377</v>
+        <v>-421.1161818032886</v>
       </c>
       <c r="D87">
-        <v>137.3409856377622</v>
+        <v>135.9878181967113</v>
       </c>
       <c r="E87">
-        <v>303.6899999999999</v>
+        <v>310.704</v>
       </c>
       <c r="F87">
-        <v>596.1899999999999</v>
+        <v>603.204</v>
       </c>
       <c r="G87">
         <v>46.1</v>
@@ -8409,37 +8409,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M87">
-        <v>140.581602</v>
+        <v>142.2355032</v>
       </c>
       <c r="N87">
-        <v>-105.9149353333333</v>
+        <v>-107.5688365333333</v>
       </c>
       <c r="O87">
-        <v>-26.47873383333333</v>
+        <v>-26.89220913333333</v>
       </c>
       <c r="P87">
-        <v>-79.4362015</v>
+        <v>-80.67662739999999</v>
       </c>
       <c r="Q87">
-        <v>-52.9362015</v>
+        <v>-54.17662739999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3244566917304522</v>
+        <v>0.3443607411397702</v>
       </c>
       <c r="T87">
-        <v>5.585299979425696</v>
+        <v>5.984249977956103</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06164865489772031</v>
+        <v>0.06093181007332822</v>
       </c>
       <c r="W87">
-        <v>0.2212632471751176</v>
+        <v>0.2214322791847092</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2465946195908812</v>
+        <v>0.2437272402933129</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2386422638584177</v>
+        <v>0.2405422638584177</v>
       </c>
       <c r="C88">
-        <v>-421.1161818032886</v>
+        <v>-429.4569449283266</v>
       </c>
       <c r="D88">
-        <v>135.9878181967113</v>
+        <v>134.6610550716734</v>
       </c>
       <c r="E88">
-        <v>310.704</v>
+        <v>317.718</v>
       </c>
       <c r="F88">
-        <v>603.204</v>
+        <v>610.218</v>
       </c>
       <c r="G88">
         <v>46.1</v>
@@ -8491,37 +8491,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M88">
-        <v>142.2355032</v>
+        <v>143.8894044</v>
       </c>
       <c r="N88">
-        <v>-107.5688365333333</v>
+        <v>-109.2227377333333</v>
       </c>
       <c r="O88">
-        <v>-26.89220913333333</v>
+        <v>-27.30568443333333</v>
       </c>
       <c r="P88">
-        <v>-80.67662739999999</v>
+        <v>-81.91705329999999</v>
       </c>
       <c r="Q88">
-        <v>-54.17662739999999</v>
+        <v>-55.41705329999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3443607411397702</v>
+        <v>0.3673269519966756</v>
       </c>
       <c r="T88">
-        <v>5.984249977956103</v>
+        <v>6.444576899337342</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06093181007332822</v>
+        <v>0.06023144444030146</v>
       </c>
       <c r="W88">
-        <v>0.2214322791847092</v>
+        <v>0.2215974254009769</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2437272402933129</v>
+        <v>0.2409257777612058</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2405422638584177</v>
+        <v>0.2424422638584178</v>
       </c>
       <c r="C89">
-        <v>-429.4569449283266</v>
+        <v>-437.7720691099541</v>
       </c>
       <c r="D89">
-        <v>134.6610550716734</v>
+        <v>133.3599308900458</v>
       </c>
       <c r="E89">
-        <v>317.718</v>
+        <v>324.732</v>
       </c>
       <c r="F89">
-        <v>610.218</v>
+        <v>617.232</v>
       </c>
       <c r="G89">
         <v>46.1</v>
@@ -8573,37 +8573,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M89">
-        <v>143.8894044</v>
+        <v>145.5433056</v>
       </c>
       <c r="N89">
-        <v>-109.2227377333333</v>
+        <v>-110.8766389333333</v>
       </c>
       <c r="O89">
-        <v>-27.30568443333333</v>
+        <v>-27.71915973333333</v>
       </c>
       <c r="P89">
-        <v>-81.91705329999999</v>
+        <v>-83.1574792</v>
       </c>
       <c r="Q89">
-        <v>-55.41705329999999</v>
+        <v>-56.6574792</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3673269519966756</v>
+        <v>0.3941208646630653</v>
       </c>
       <c r="T89">
-        <v>6.444576899337342</v>
+        <v>6.981624974282121</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06023144444030146</v>
+        <v>0.0595469962080253</v>
       </c>
       <c r="W89">
-        <v>0.2215974254009769</v>
+        <v>0.2217588182941476</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2409257777612058</v>
+        <v>0.2381879848321012</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2424422638584178</v>
+        <v>0.2443422638584178</v>
       </c>
       <c r="C90">
-        <v>-437.7720691099541</v>
+        <v>-446.0622904230736</v>
       </c>
       <c r="D90">
-        <v>133.3599308900458</v>
+        <v>132.0837095769264</v>
       </c>
       <c r="E90">
-        <v>324.732</v>
+        <v>331.746</v>
       </c>
       <c r="F90">
-        <v>617.232</v>
+        <v>624.246</v>
       </c>
       <c r="G90">
         <v>46.1</v>
@@ -8655,37 +8655,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M90">
-        <v>145.5433056</v>
+        <v>147.1972068</v>
       </c>
       <c r="N90">
-        <v>-110.8766389333333</v>
+        <v>-112.5305401333333</v>
       </c>
       <c r="O90">
-        <v>-27.71915973333333</v>
+        <v>-28.13263503333333</v>
       </c>
       <c r="P90">
-        <v>-83.1574792</v>
+        <v>-84.3979051</v>
       </c>
       <c r="Q90">
-        <v>-56.6574792</v>
+        <v>-57.8979051</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3941208646630653</v>
+        <v>0.4257863978142531</v>
       </c>
       <c r="T90">
-        <v>6.981624974282121</v>
+        <v>7.616318153762315</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0595469962080253</v>
+        <v>0.05887792883490142</v>
       </c>
       <c r="W90">
-        <v>0.2217588182941476</v>
+        <v>0.2219165843807303</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2381879848321012</v>
+        <v>0.2355117153396057</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2443422638584178</v>
+        <v>0.2462422638584178</v>
       </c>
       <c r="C91">
-        <v>-446.0622904230736</v>
+        <v>-454.3283170334567</v>
       </c>
       <c r="D91">
-        <v>132.0837095769264</v>
+        <v>130.8316829665433</v>
       </c>
       <c r="E91">
-        <v>331.746</v>
+        <v>338.76</v>
       </c>
       <c r="F91">
-        <v>624.246</v>
+        <v>631.26</v>
       </c>
       <c r="G91">
         <v>46.1</v>
@@ -8737,37 +8737,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M91">
-        <v>147.1972068</v>
+        <v>148.851108</v>
       </c>
       <c r="N91">
-        <v>-112.5305401333333</v>
+        <v>-114.1844413333333</v>
       </c>
       <c r="O91">
-        <v>-28.13263503333333</v>
+        <v>-28.54611033333333</v>
       </c>
       <c r="P91">
-        <v>-84.3979051</v>
+        <v>-85.63833100000001</v>
       </c>
       <c r="Q91">
-        <v>-57.8979051</v>
+        <v>-59.13833100000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4257863978142531</v>
+        <v>0.4637850375956785</v>
       </c>
       <c r="T91">
-        <v>7.616318153762315</v>
+        <v>8.377949969138546</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05887792883490142</v>
+        <v>0.05822372962562473</v>
       </c>
       <c r="W91">
-        <v>0.2219165843807303</v>
+        <v>0.2220708445542777</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2355117153396057</v>
+        <v>0.232894918502499</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2462422638584178</v>
+        <v>0.2481422638584178</v>
       </c>
       <c r="C92">
-        <v>-454.3283170334567</v>
+        <v>-462.5708305080827</v>
       </c>
       <c r="D92">
-        <v>130.8316829665433</v>
+        <v>129.6031694919173</v>
       </c>
       <c r="E92">
-        <v>338.76</v>
+        <v>345.774</v>
       </c>
       <c r="F92">
-        <v>631.26</v>
+        <v>638.274</v>
       </c>
       <c r="G92">
         <v>46.1</v>
@@ -8819,37 +8819,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M92">
-        <v>148.851108</v>
+        <v>150.5050092</v>
       </c>
       <c r="N92">
-        <v>-114.1844413333333</v>
+        <v>-115.8383425333333</v>
       </c>
       <c r="O92">
-        <v>-28.54611033333333</v>
+        <v>-28.95958563333334</v>
       </c>
       <c r="P92">
-        <v>-85.63833100000001</v>
+        <v>-86.87875690000001</v>
       </c>
       <c r="Q92">
-        <v>-59.13833100000001</v>
+        <v>-60.37875690000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4637850375956785</v>
+        <v>0.5102278195507539</v>
       </c>
       <c r="T92">
-        <v>8.377949969138546</v>
+        <v>9.308833299042831</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05822372962562473</v>
+        <v>0.05758390842094754</v>
       </c>
       <c r="W92">
-        <v>0.2220708445542777</v>
+        <v>0.2222217143943406</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.232894918502499</v>
+        <v>0.2303356336837902</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2481422638584178</v>
+        <v>0.2500422638584178</v>
       </c>
       <c r="C93">
-        <v>-462.5708305080827</v>
+        <v>-470.7904870523391</v>
       </c>
       <c r="D93">
-        <v>129.6031694919173</v>
+        <v>128.3975129476609</v>
       </c>
       <c r="E93">
-        <v>345.774</v>
+        <v>352.788</v>
       </c>
       <c r="F93">
-        <v>638.274</v>
+        <v>645.288</v>
       </c>
       <c r="G93">
         <v>46.1</v>
@@ -8901,37 +8901,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M93">
-        <v>150.5050092</v>
+        <v>152.1589104</v>
       </c>
       <c r="N93">
-        <v>-115.8383425333333</v>
+        <v>-117.4922437333333</v>
       </c>
       <c r="O93">
-        <v>-28.95958563333334</v>
+        <v>-29.37306093333333</v>
       </c>
       <c r="P93">
-        <v>-86.87875690000001</v>
+        <v>-88.11918279999999</v>
       </c>
       <c r="Q93">
-        <v>-60.37875690000001</v>
+        <v>-61.61918279999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5102278195507539</v>
+        <v>0.5682812969945982</v>
       </c>
       <c r="T93">
-        <v>9.308833299042831</v>
+        <v>10.47243746142319</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05758390842094754</v>
+        <v>0.05695799637289377</v>
       </c>
       <c r="W93">
-        <v>0.2222217143943406</v>
+        <v>0.2223693044552716</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2303356336837902</v>
+        <v>0.2278319854915751</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2500422638584178</v>
+        <v>0.2519422638584178</v>
       </c>
       <c r="C94">
-        <v>-470.7904870523391</v>
+        <v>-478.9879186788013</v>
       </c>
       <c r="D94">
-        <v>128.3975129476609</v>
+        <v>127.2140813211987</v>
       </c>
       <c r="E94">
-        <v>352.788</v>
+        <v>359.802</v>
       </c>
       <c r="F94">
-        <v>645.288</v>
+        <v>652.302</v>
       </c>
       <c r="G94">
         <v>46.1</v>
@@ -8983,37 +8983,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M94">
-        <v>152.1589104</v>
+        <v>153.8128116</v>
       </c>
       <c r="N94">
-        <v>-117.4922437333333</v>
+        <v>-119.1461449333333</v>
       </c>
       <c r="O94">
-        <v>-29.37306093333333</v>
+        <v>-29.78653623333333</v>
       </c>
       <c r="P94">
-        <v>-88.11918279999999</v>
+        <v>-89.3596087</v>
       </c>
       <c r="Q94">
-        <v>-61.61918279999999</v>
+        <v>-62.8596087</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5682812969945982</v>
+        <v>0.6429214822795408</v>
       </c>
       <c r="T94">
-        <v>10.47243746142319</v>
+        <v>11.96849995591221</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05695799637289377</v>
+        <v>0.05634554479899168</v>
       </c>
       <c r="W94">
-        <v>0.2223693044552716</v>
+        <v>0.2225137205363978</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2278319854915751</v>
+        <v>0.2253821791959667</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2519422638584178</v>
+        <v>0.2538422638584177</v>
       </c>
       <c r="C95">
-        <v>-478.9879186788013</v>
+        <v>-487.1637343119688</v>
       </c>
       <c r="D95">
-        <v>127.2140813211987</v>
+        <v>126.0522656880312</v>
       </c>
       <c r="E95">
-        <v>359.802</v>
+        <v>366.816</v>
       </c>
       <c r="F95">
-        <v>652.302</v>
+        <v>659.316</v>
       </c>
       <c r="G95">
         <v>46.1</v>
@@ -9065,37 +9065,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M95">
-        <v>153.8128116</v>
+        <v>155.4667128</v>
       </c>
       <c r="N95">
-        <v>-119.1461449333333</v>
+        <v>-120.8000461333333</v>
       </c>
       <c r="O95">
-        <v>-29.78653623333333</v>
+        <v>-30.20001153333333</v>
       </c>
       <c r="P95">
-        <v>-89.3596087</v>
+        <v>-90.6000346</v>
       </c>
       <c r="Q95">
-        <v>-62.8596087</v>
+        <v>-64.1000346</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6429214822795408</v>
+        <v>0.7424417293261312</v>
       </c>
       <c r="T95">
-        <v>11.96849995591221</v>
+        <v>13.96324994856425</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05634554479899168</v>
+        <v>0.05574612410964071</v>
       </c>
       <c r="W95">
-        <v>0.2225137205363978</v>
+        <v>0.2226550639349467</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2253821791959667</v>
+        <v>0.2229844964385628</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2538422638584177</v>
+        <v>0.2557422638584178</v>
       </c>
       <c r="C96">
-        <v>-487.1637343119688</v>
+        <v>-495.3185208330134</v>
       </c>
       <c r="D96">
-        <v>126.0522656880312</v>
+        <v>124.9114791669866</v>
       </c>
       <c r="E96">
-        <v>366.816</v>
+        <v>373.83</v>
       </c>
       <c r="F96">
-        <v>659.316</v>
+        <v>666.33</v>
       </c>
       <c r="G96">
         <v>46.1</v>
@@ -9147,37 +9147,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M96">
-        <v>155.4667128</v>
+        <v>157.120614</v>
       </c>
       <c r="N96">
-        <v>-120.8000461333333</v>
+        <v>-122.4539473333333</v>
       </c>
       <c r="O96">
-        <v>-30.20001153333333</v>
+        <v>-30.61348683333334</v>
       </c>
       <c r="P96">
-        <v>-90.6000346</v>
+        <v>-91.84046050000001</v>
       </c>
       <c r="Q96">
-        <v>-64.1000346</v>
+        <v>-65.34046050000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7424417293261312</v>
+        <v>0.8817700751913579</v>
       </c>
       <c r="T96">
-        <v>13.96324994856425</v>
+        <v>16.75589993827711</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05574612410964071</v>
+        <v>0.05515932280322344</v>
       </c>
       <c r="W96">
-        <v>0.2226550639349467</v>
+        <v>0.2227934316829999</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2229844964385628</v>
+        <v>0.2206372912128938</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2557422638584178</v>
+        <v>0.2576422638584178</v>
       </c>
       <c r="C97">
-        <v>-495.3185208330134</v>
+        <v>-503.4528440683047</v>
       </c>
       <c r="D97">
-        <v>124.9114791669866</v>
+        <v>123.7911559316954</v>
       </c>
       <c r="E97">
-        <v>373.83</v>
+        <v>380.8440000000001</v>
       </c>
       <c r="F97">
-        <v>666.33</v>
+        <v>673.3440000000001</v>
       </c>
       <c r="G97">
         <v>46.1</v>
@@ -9229,37 +9229,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M97">
-        <v>157.120614</v>
+        <v>158.7745152</v>
       </c>
       <c r="N97">
-        <v>-122.4539473333333</v>
+        <v>-124.1078485333334</v>
       </c>
       <c r="O97">
-        <v>-30.61348683333334</v>
+        <v>-31.02696213333334</v>
       </c>
       <c r="P97">
-        <v>-91.84046050000001</v>
+        <v>-93.08088640000001</v>
       </c>
       <c r="Q97">
-        <v>-65.34046050000001</v>
+        <v>-66.58088640000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8817700751913579</v>
+        <v>1.090762593989198</v>
       </c>
       <c r="T97">
-        <v>16.75589993827711</v>
+        <v>20.9448749228464</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05515932280322344</v>
+        <v>0.05458474652402319</v>
       </c>
       <c r="W97">
-        <v>0.2227934316829999</v>
+        <v>0.2229289167696353</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2206372912128938</v>
+        <v>0.2183389860960927</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2576422638584178</v>
+        <v>0.2595422638584178</v>
       </c>
       <c r="C98">
-        <v>-503.4528440683046</v>
+        <v>-511.5672497252129</v>
       </c>
       <c r="D98">
-        <v>123.7911559316954</v>
+        <v>122.690750274787</v>
       </c>
       <c r="E98">
-        <v>380.8439999999999</v>
+        <v>387.8579999999999</v>
       </c>
       <c r="F98">
-        <v>673.3439999999999</v>
+        <v>680.3579999999999</v>
       </c>
       <c r="G98">
         <v>46.1</v>
@@ -9311,37 +9311,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M98">
-        <v>158.7745152</v>
+        <v>160.4284164</v>
       </c>
       <c r="N98">
-        <v>-124.1078485333333</v>
+        <v>-125.7617497333333</v>
       </c>
       <c r="O98">
-        <v>-31.02696213333333</v>
+        <v>-31.44043743333333</v>
       </c>
       <c r="P98">
-        <v>-93.0808864</v>
+        <v>-94.3213123</v>
       </c>
       <c r="Q98">
-        <v>-66.5808864</v>
+        <v>-67.8213123</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.090762593989195</v>
+        <v>1.43908345865226</v>
       </c>
       <c r="T98">
-        <v>20.94487492284634</v>
+        <v>27.92649989712846</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0545847465240232</v>
+        <v>0.05402201717841471</v>
       </c>
       <c r="W98">
-        <v>0.2229289167696353</v>
+        <v>0.2230616083493298</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2183389860960928</v>
+        <v>0.2160880687136588</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2595422638584178</v>
+        <v>0.2614422638584177</v>
       </c>
       <c r="C99">
-        <v>-511.5672497252129</v>
+        <v>-519.6622642784415</v>
       </c>
       <c r="D99">
-        <v>122.690750274787</v>
+        <v>121.6097357215585</v>
       </c>
       <c r="E99">
-        <v>387.8579999999999</v>
+        <v>394.872</v>
       </c>
       <c r="F99">
-        <v>680.3579999999999</v>
+        <v>687.372</v>
       </c>
       <c r="G99">
         <v>46.1</v>
@@ -9393,37 +9393,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M99">
-        <v>160.4284164</v>
+        <v>162.0823176</v>
       </c>
       <c r="N99">
-        <v>-125.7617497333333</v>
+        <v>-127.4156509333333</v>
       </c>
       <c r="O99">
-        <v>-31.44043743333333</v>
+        <v>-31.85391273333333</v>
       </c>
       <c r="P99">
-        <v>-94.3213123</v>
+        <v>-95.56173820000001</v>
       </c>
       <c r="Q99">
-        <v>-67.8213123</v>
+        <v>-69.06173820000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.43908345865226</v>
+        <v>2.13572518797839</v>
       </c>
       <c r="T99">
-        <v>27.92649989712846</v>
+        <v>41.88974984569268</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05402201717841471</v>
+        <v>0.05347077210516558</v>
       </c>
       <c r="W99">
-        <v>0.2230616083493298</v>
+        <v>0.223191591937602</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2160880687136588</v>
+        <v>0.2138830884206623</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2614422638584177</v>
+        <v>0.2633422638584178</v>
       </c>
       <c r="C100">
-        <v>-519.6622642784415</v>
+        <v>-527.7383958099095</v>
       </c>
       <c r="D100">
-        <v>121.6097357215585</v>
+        <v>120.5476041900904</v>
       </c>
       <c r="E100">
-        <v>394.872</v>
+        <v>401.886</v>
       </c>
       <c r="F100">
-        <v>687.372</v>
+        <v>694.386</v>
       </c>
       <c r="G100">
         <v>46.1</v>
@@ -9475,37 +9475,37 @@
         <v>34.66666666666667</v>
       </c>
       <c r="M100">
-        <v>162.0823176</v>
+        <v>163.7362188</v>
       </c>
       <c r="N100">
-        <v>-127.4156509333333</v>
+        <v>-129.0695521333333</v>
       </c>
       <c r="O100">
-        <v>-31.85391273333333</v>
+        <v>-32.26738803333333</v>
       </c>
       <c r="P100">
-        <v>-95.56173820000001</v>
+        <v>-96.8021641</v>
       </c>
       <c r="Q100">
-        <v>-69.06173820000001</v>
+        <v>-70.3021641</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.13572518797839</v>
+        <v>4.22565037595678</v>
       </c>
       <c r="T100">
-        <v>41.88974984569268</v>
+        <v>83.77949969138538</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05347077210516558</v>
+        <v>0.05293066329602249</v>
       </c>
       <c r="W100">
-        <v>0.223191591937602</v>
+        <v>0.2233189495947979</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2138830884206623</v>
+        <v>0.2117226531840899</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2633422638584178</v>
-      </c>
-      <c r="C101">
-        <v>-527.7383958099095</v>
-      </c>
-      <c r="D101">
-        <v>120.5476041900904</v>
-      </c>
-      <c r="E101">
-        <v>401.886</v>
-      </c>
-      <c r="F101">
-        <v>694.386</v>
-      </c>
-      <c r="G101">
-        <v>46.1</v>
-      </c>
-      <c r="H101">
-        <v>408.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>61.16666666666667</v>
-      </c>
-      <c r="K101">
-        <v>26.5</v>
-      </c>
-      <c r="L101">
-        <v>34.66666666666667</v>
-      </c>
-      <c r="M101">
-        <v>163.7362188</v>
-      </c>
-      <c r="N101">
-        <v>-129.0695521333333</v>
-      </c>
-      <c r="O101">
-        <v>-32.26738803333333</v>
-      </c>
-      <c r="P101">
-        <v>-96.8021641</v>
-      </c>
-      <c r="Q101">
-        <v>-70.3021641</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.22565037595678</v>
-      </c>
-      <c r="T101">
-        <v>83.77949969138538</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05293066329602249</v>
-      </c>
-      <c r="W101">
-        <v>0.2233189495947979</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2117226531840899</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
